--- a/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
+++ b/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="223">
   <si>
     <t>pathway</t>
   </si>
@@ -52,13 +52,13 @@
     <t>C21-steroid hormone biosynthesis and metabolism</t>
   </si>
   <si>
-    <t>E2263,E1036,E2398,E1116,E2274,E423,E422,E2141,E1295,E2269,E1163,E1164,E1954,E2399,E2648,E1691,E2457,E2669</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,C04042/C01953/C03681,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C00410,dhea/C03772/C01227/C00674/C00535,dhea/C03772/C01227/C00674/C00535,C03917/C05293/C00523/C04373/C04295,C05490,andrstndn/C00280,C05487/C05475/C05478,C05487/C05475/C05478,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,17ahprgstrn/C03205/C05498/C01176,C01124/C05469/C00735/C05473,CE1352,C05472,C05489/C05471/C05474</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Progesterone; 4-Pregnene-3,20-dione$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$11-Dehydrocorticosterone$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$18-Hydroxycorticosterone/17alpha,21-Dihydroxy-5beta-pregnane-3,11,20-trione; 5beta-Pregnane-17alpha,21-diol-3,11,20-trione; 4,5beta-Dihydrocortisone/Cortisol; Hydrocortisone; 11beta,17alpha,21-Trihydroxy-4-pregnene-3,20-dione; Kendall's compound F; Reichstein's substance M/11beta,21-Dihydroxy-3,20-oxo-5beta-pregnan-18-al$17alpha-hydroxypregnenolone sulfate$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al</t>
+    <t>E2263,E1036,E2398,E1116,E2274,E423,E1295,E2141,E1163,E2269,E422,E1164,E1954,E2399,E2648,E1691,E2457,E2669</t>
+  </si>
+  <si>
+    <t>C18045/C14497/C18075/C05294/C05139,C04042/C01953/C03681,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C00410,dhea/C03772/C01227/C00674/C00535,C05490,C03917/C05293/C00523/C04373/C04295,C05487/C05475/C05478,andrstndn/C00280,dhea/C03772/C01227/C00674/C00535,C05487/C05475/C05478,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,17ahprgstrn/C03205/C05498/C01176,C01124/C05469/C00735/C05473,CE1352,C05472,C05489/C05471/C05474</t>
+  </si>
+  <si>
+    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Progesterone; 4-Pregnene-3,20-dione$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$11-Dehydrocorticosterone$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$18-Hydroxycorticosterone/17alpha,21-Dihydroxy-5beta-pregnane-3,11,20-trione; 5beta-Pregnane-17alpha,21-diol-3,11,20-trione; 4,5beta-Dihydrocortisone/Cortisol; Hydrocortisone; 11beta,17alpha,21-Trihydroxy-4-pregnene-3,20-dione; Kendall's compound F; Reichstein's substance M/11beta,21-Dihydroxy-3,20-oxo-5beta-pregnan-18-al$17alpha-hydroxypregnenolone sulfate$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al</t>
   </si>
   <si>
     <t>Phosphatidylinositol phosphate metabolism</t>
@@ -151,13 +151,13 @@
     <t>Sialic acid metabolism</t>
   </si>
   <si>
-    <t>E2558,E33,E35,E2970</t>
-  </si>
-  <si>
-    <t>C00055,,,</t>
-  </si>
-  <si>
-    <t>CMP$$$</t>
+    <t>E35,E2558,E33,E2970</t>
+  </si>
+  <si>
+    <t>,C00055,,</t>
+  </si>
+  <si>
+    <t>$CMP$$</t>
   </si>
   <si>
     <t>Leukotriene metabolism</t>
@@ -232,13 +232,13 @@
     <t>Aminosugars metabolism</t>
   </si>
   <si>
-    <t>E2558,E33,E35</t>
-  </si>
-  <si>
-    <t>C00055,,</t>
-  </si>
-  <si>
-    <t>CMP$$</t>
+    <t>E35,E2558,E33</t>
+  </si>
+  <si>
+    <t>,C00055,</t>
+  </si>
+  <si>
+    <t>$CMP$</t>
   </si>
   <si>
     <t>Hyaluronan Metabolism</t>
@@ -383,12 +383,6 @@
   </si>
   <si>
     <t>E445,E2558,E1039</t>
-  </si>
-  <si>
-    <t>,C00055,</t>
-  </si>
-  <si>
-    <t>$CMP$</t>
   </si>
   <si>
     <t>Vitamin D3 (cholecalciferol) metabolism</t>
@@ -1057,7 +1051,7 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>0.02210046889968236</v>
+        <v>0.02077276012167863</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1080,7 +1074,7 @@
         <v>62</v>
       </c>
       <c r="D3">
-        <v>0.037411135947295</v>
+        <v>0.03620107225088654</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1103,7 +1097,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.04124300431925514</v>
+        <v>0.03983126334011193</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1126,7 +1120,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>0.0525369321524008</v>
+        <v>0.05173022302146182</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1149,7 +1143,7 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>0.05821750894942942</v>
+        <v>0.05641921984504462</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1172,7 +1166,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>0.06578040705198232</v>
+        <v>0.06344431186030487</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1195,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>0.0784524629838154</v>
+        <v>0.07717517352649535</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1218,7 +1212,7 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>0.0784524629838154</v>
+        <v>0.07717517352649535</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1241,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0.0784524629838154</v>
+        <v>0.07717517352649535</v>
       </c>
       <c r="E10" t="s">
         <v>36</v>
@@ -1264,7 +1258,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>0.08043562293070705</v>
+        <v>0.07893984975042437</v>
       </c>
       <c r="E11" t="s">
         <v>41</v>
@@ -1287,7 +1281,7 @@
         <v>12</v>
       </c>
       <c r="D12">
-        <v>0.1002336095191678</v>
+        <v>0.09695635367472816</v>
       </c>
       <c r="E12" t="s">
         <v>45</v>
@@ -1310,7 +1304,7 @@
         <v>41</v>
       </c>
       <c r="D13">
-        <v>0.1106872153409186</v>
+        <v>0.1082838943883296</v>
       </c>
       <c r="E13" t="s">
         <v>49</v>
@@ -1333,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>0.1225861750222685</v>
+        <v>0.1192921127376011</v>
       </c>
       <c r="E14" t="s">
         <v>51</v>
@@ -1356,7 +1350,7 @@
         <v>9</v>
       </c>
       <c r="D15">
-        <v>0.1271575267642561</v>
+        <v>0.1233592712727517</v>
       </c>
       <c r="E15" t="s">
         <v>55</v>
@@ -1379,7 +1373,7 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>0.1271911396447118</v>
+        <v>0.1234264970336633</v>
       </c>
       <c r="E16" t="s">
         <v>57</v>
@@ -1402,7 +1396,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>0.1516949294969832</v>
+        <v>0.1483168350111763</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
@@ -1425,7 +1419,7 @@
         <v>2</v>
       </c>
       <c r="D18">
-        <v>0.1558125073528176</v>
+        <v>0.1516613166165275</v>
       </c>
       <c r="E18" t="s">
         <v>63</v>
@@ -1442,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="D19">
-        <v>0.157039377489454</v>
+        <v>0.1529386060738475</v>
       </c>
       <c r="E19" t="s">
         <v>65</v>
@@ -1465,7 +1459,7 @@
         <v>6</v>
       </c>
       <c r="D20">
-        <v>0.157039377489454</v>
+        <v>0.1529386060738475</v>
       </c>
       <c r="E20" t="s">
         <v>67</v>
@@ -1488,7 +1482,7 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>0.157039377489454</v>
+        <v>0.1529386060738475</v>
       </c>
       <c r="E21" t="s">
         <v>69</v>
@@ -1511,7 +1505,7 @@
         <v>11</v>
       </c>
       <c r="D22">
-        <v>0.187223744138754</v>
+        <v>0.1838288432127191</v>
       </c>
       <c r="E22" t="s">
         <v>28</v>
@@ -1534,7 +1528,7 @@
         <v>11</v>
       </c>
       <c r="D23">
-        <v>0.187223744138754</v>
+        <v>0.1838288432127191</v>
       </c>
       <c r="E23" t="s">
         <v>72</v>
@@ -1557,7 +1551,7 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>0.2087023747500042</v>
+        <v>0.2038621199643703</v>
       </c>
       <c r="E24" t="s">
         <v>65</v>
@@ -1580,7 +1574,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>0.2087023747500042</v>
+        <v>0.2038621199643703</v>
       </c>
       <c r="E25" t="s">
         <v>65</v>
@@ -1603,7 +1597,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>0.2367355170501336</v>
+        <v>0.2320297137863229</v>
       </c>
       <c r="E26" t="s">
         <v>36</v>
@@ -1626,7 +1620,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>0.2367355170501336</v>
+        <v>0.2320297137863229</v>
       </c>
       <c r="E27" t="s">
         <v>36</v>
@@ -1649,7 +1643,7 @@
         <v>3</v>
       </c>
       <c r="D28">
-        <v>0.2367355170501336</v>
+        <v>0.2320297137863229</v>
       </c>
       <c r="E28" t="s">
         <v>36</v>
@@ -1672,7 +1666,7 @@
         <v>3</v>
       </c>
       <c r="D29">
-        <v>0.2367355170501336</v>
+        <v>0.2320297137863229</v>
       </c>
       <c r="E29" t="s">
         <v>81</v>
@@ -1689,7 +1683,7 @@
         <v>22</v>
       </c>
       <c r="D30">
-        <v>0.2519789583368347</v>
+        <v>0.2475084452362145</v>
       </c>
       <c r="E30" t="s">
         <v>83</v>
@@ -1712,7 +1706,7 @@
         <v>8</v>
       </c>
       <c r="D31">
-        <v>0.2542478277676005</v>
+        <v>0.2496932824658409</v>
       </c>
       <c r="E31" t="s">
         <v>87</v>
@@ -1735,7 +1729,7 @@
         <v>8</v>
       </c>
       <c r="D32">
-        <v>0.2542478277676005</v>
+        <v>0.2496932824658409</v>
       </c>
       <c r="E32" t="s">
         <v>89</v>
@@ -1758,7 +1752,7 @@
         <v>13</v>
       </c>
       <c r="D33">
-        <v>0.2666845935362431</v>
+        <v>0.2618947580712929</v>
       </c>
       <c r="E33" t="s">
         <v>93</v>
@@ -1781,7 +1775,7 @@
         <v>152</v>
       </c>
       <c r="D34">
-        <v>0.2723987832137275</v>
+        <v>0.2661467874489504</v>
       </c>
       <c r="E34" t="s">
         <v>95</v>
@@ -1804,7 +1798,7 @@
         <v>18</v>
       </c>
       <c r="D35">
-        <v>0.2802978101208383</v>
+        <v>0.2723315574528159</v>
       </c>
       <c r="E35" t="s">
         <v>99</v>
@@ -1827,7 +1821,7 @@
         <v>9</v>
       </c>
       <c r="D36">
-        <v>0.313255239407741</v>
+        <v>0.3054570511419976</v>
       </c>
       <c r="E36" t="s">
         <v>101</v>
@@ -1850,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="D37">
-        <v>0.313255239407741</v>
+        <v>0.3054570511419976</v>
       </c>
       <c r="E37" t="s">
         <v>65</v>
@@ -1873,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="D38">
-        <v>0.316801398295827</v>
+        <v>0.309893951362162</v>
       </c>
       <c r="E38" t="s">
         <v>32</v>
@@ -1896,7 +1890,7 @@
         <v>4</v>
       </c>
       <c r="D39">
-        <v>0.316801398295827</v>
+        <v>0.309893951362162</v>
       </c>
       <c r="E39" t="s">
         <v>105</v>
@@ -1913,7 +1907,7 @@
         <v>19</v>
       </c>
       <c r="D40">
-        <v>0.3171879464210686</v>
+        <v>0.3101292415253525</v>
       </c>
       <c r="E40" t="s">
         <v>107</v>
@@ -1936,7 +1930,7 @@
         <v>10</v>
       </c>
       <c r="D41">
-        <v>0.3423976067629115</v>
+        <v>0.3359103208349439</v>
       </c>
       <c r="E41" t="s">
         <v>109</v>
@@ -1959,7 +1953,7 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>0.3423976067629115</v>
+        <v>0.3359103208349439</v>
       </c>
       <c r="E42" t="s">
         <v>111</v>
@@ -1982,7 +1976,7 @@
         <v>5</v>
       </c>
       <c r="D43">
-        <v>0.3605653686492664</v>
+        <v>0.3535906959546898</v>
       </c>
       <c r="E43" t="s">
         <v>113</v>
@@ -1999,7 +1993,7 @@
         <v>5</v>
       </c>
       <c r="D44">
-        <v>0.3605653686492664</v>
+        <v>0.3535906959546898</v>
       </c>
       <c r="E44" t="s">
         <v>36</v>
@@ -2022,7 +2016,7 @@
         <v>5</v>
       </c>
       <c r="D45">
-        <v>0.3605653686492664</v>
+        <v>0.3535906959546898</v>
       </c>
       <c r="E45" t="s">
         <v>116</v>
@@ -2039,7 +2033,7 @@
         <v>11</v>
       </c>
       <c r="D46">
-        <v>0.3749348750441169</v>
+        <v>0.368178686072503</v>
       </c>
       <c r="E46" t="s">
         <v>118</v>
@@ -2062,7 +2056,7 @@
         <v>27</v>
       </c>
       <c r="D47">
-        <v>0.3808339355641082</v>
+        <v>0.3748676492832053</v>
       </c>
       <c r="E47" t="s">
         <v>120</v>
@@ -2085,21 +2079,21 @@
         <v>17</v>
       </c>
       <c r="D48">
-        <v>0.3932370884522949</v>
+        <v>0.3853212551049562</v>
       </c>
       <c r="E48" t="s">
         <v>122</v>
       </c>
       <c r="F48" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="G48" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -2108,15 +2102,15 @@
         <v>6</v>
       </c>
       <c r="D49">
-        <v>0.4077074334885128</v>
+        <v>0.3996739550595788</v>
       </c>
       <c r="E49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -2125,15 +2119,15 @@
         <v>6</v>
       </c>
       <c r="D50">
-        <v>0.4077074334885128</v>
+        <v>0.3996739550595788</v>
       </c>
       <c r="E50" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -2142,10 +2136,10 @@
         <v>12</v>
       </c>
       <c r="D51">
-        <v>0.4114888825397893</v>
+        <v>0.4031865010672089</v>
       </c>
       <c r="E51" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F51" t="s">
         <v>52</v>
@@ -2156,7 +2150,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B52">
         <v>4</v>
@@ -2165,10 +2159,10 @@
         <v>24</v>
       </c>
       <c r="D52">
-        <v>0.4381607031814591</v>
+        <v>0.429673450866372</v>
       </c>
       <c r="E52" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F52" t="s">
         <v>58</v>
@@ -2179,7 +2173,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B53">
         <v>7</v>
@@ -2188,21 +2182,21 @@
         <v>40</v>
       </c>
       <c r="D53">
-        <v>0.4418413135913682</v>
+        <v>0.4330683517924068</v>
       </c>
       <c r="E53" t="s">
+        <v>132</v>
+      </c>
+      <c r="F53" t="s">
+        <v>133</v>
+      </c>
+      <c r="G53" t="s">
         <v>134</v>
-      </c>
-      <c r="F53" t="s">
-        <v>135</v>
-      </c>
-      <c r="G53" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B54">
         <v>6</v>
@@ -2211,21 +2205,21 @@
         <v>35</v>
       </c>
       <c r="D54">
-        <v>0.4459420850069747</v>
+        <v>0.4370010588057344</v>
       </c>
       <c r="E54" t="s">
+        <v>136</v>
+      </c>
+      <c r="F54" t="s">
+        <v>137</v>
+      </c>
+      <c r="G54" t="s">
         <v>138</v>
-      </c>
-      <c r="F54" t="s">
-        <v>139</v>
-      </c>
-      <c r="G54" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B55">
         <v>23</v>
@@ -2234,21 +2228,21 @@
         <v>120</v>
       </c>
       <c r="D55">
-        <v>0.4504294045478227</v>
+        <v>0.4407152820960992</v>
       </c>
       <c r="E55" t="s">
+        <v>140</v>
+      </c>
+      <c r="F55" t="s">
+        <v>141</v>
+      </c>
+      <c r="G55" t="s">
         <v>142</v>
-      </c>
-      <c r="F55" t="s">
-        <v>143</v>
-      </c>
-      <c r="G55" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -2257,7 +2251,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>0.4522108872119796</v>
+        <v>0.4427152484832187</v>
       </c>
       <c r="E56" t="s">
         <v>36</v>
@@ -2271,7 +2265,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2280,15 +2274,15 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>0.4522108872119796</v>
+        <v>0.4427152484832187</v>
       </c>
       <c r="E57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -2297,10 +2291,10 @@
         <v>14</v>
       </c>
       <c r="D58">
-        <v>0.4745802591553083</v>
+        <v>0.4664459420850069</v>
       </c>
       <c r="E58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F58" t="s">
         <v>52</v>
@@ -2311,7 +2305,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -2320,10 +2314,10 @@
         <v>14</v>
       </c>
       <c r="D59">
-        <v>0.4745802591553083</v>
+        <v>0.4664459420850069</v>
       </c>
       <c r="E59" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F59" t="s">
         <v>52</v>
@@ -2334,7 +2328,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -2343,10 +2337,10 @@
         <v>14</v>
       </c>
       <c r="D60">
-        <v>0.4745802591553083</v>
+        <v>0.4664459420850069</v>
       </c>
       <c r="E60" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F60" t="s">
         <v>52</v>
@@ -2357,7 +2351,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B61">
         <v>7</v>
@@ -2366,21 +2360,21 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.4935883430530579</v>
+        <v>0.484428833128855</v>
       </c>
       <c r="E61" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F61" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G61" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B62">
         <v>8</v>
@@ -2389,21 +2383,21 @@
         <v>51</v>
       </c>
       <c r="D62">
-        <v>0.5256046116871985</v>
+        <v>0.5193021966017378</v>
       </c>
       <c r="E62" t="s">
+        <v>155</v>
+      </c>
+      <c r="F62" t="s">
+        <v>156</v>
+      </c>
+      <c r="G62" t="s">
         <v>157</v>
-      </c>
-      <c r="F62" t="s">
-        <v>158</v>
-      </c>
-      <c r="G62" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B63">
         <v>2</v>
@@ -2412,10 +2406,10 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>0.5336044772356767</v>
+        <v>0.5276381909547738</v>
       </c>
       <c r="E63" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F63" t="s">
         <v>52</v>
@@ -2426,7 +2420,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -2435,7 +2429,7 @@
         <v>10</v>
       </c>
       <c r="D64">
-        <v>0.534209509083881</v>
+        <v>0.5286129644879918</v>
       </c>
       <c r="E64" t="s">
         <v>36</v>
@@ -2449,7 +2443,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -2458,15 +2452,15 @@
         <v>10</v>
       </c>
       <c r="D65">
-        <v>0.534209509083881</v>
+        <v>0.5286129644879918</v>
       </c>
       <c r="E65" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -2475,15 +2469,15 @@
         <v>11</v>
       </c>
       <c r="D66">
-        <v>0.5495705954521772</v>
+        <v>0.5441253088183392</v>
       </c>
       <c r="E66" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -2492,7 +2486,7 @@
         <v>11</v>
       </c>
       <c r="D67">
-        <v>0.5495705954521772</v>
+        <v>0.5441253088183392</v>
       </c>
       <c r="E67" t="s">
         <v>32</v>
@@ -2506,7 +2500,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -2515,15 +2509,15 @@
         <v>14</v>
       </c>
       <c r="D68">
-        <v>0.5846288297675669</v>
+        <v>0.5812675417219879</v>
       </c>
       <c r="E68" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -2532,7 +2526,7 @@
         <v>15</v>
       </c>
       <c r="D69">
-        <v>0.5906455353691534</v>
+        <v>0.5869649249592443</v>
       </c>
       <c r="E69" t="s">
         <v>116</v>
@@ -2540,7 +2534,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -2549,15 +2543,15 @@
         <v>17</v>
       </c>
       <c r="D70">
-        <v>0.5999563032554075</v>
+        <v>0.5960067898018521</v>
       </c>
       <c r="E70" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -2566,15 +2560,15 @@
         <v>18</v>
       </c>
       <c r="D71">
-        <v>0.603720945866456</v>
+        <v>0.5999394968151796</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -2583,10 +2577,10 @@
         <v>29</v>
       </c>
       <c r="D72">
-        <v>0.6081914589670762</v>
+        <v>0.6045948807583066</v>
       </c>
       <c r="E72" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>52</v>
@@ -2597,7 +2591,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2606,12 +2600,12 @@
         <v>8</v>
       </c>
       <c r="D73">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2620,12 +2614,12 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2634,12 +2628,12 @@
         <v>2</v>
       </c>
       <c r="D75">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2648,12 +2642,12 @@
         <v>1</v>
       </c>
       <c r="D76">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -2662,12 +2656,12 @@
         <v>2</v>
       </c>
       <c r="D77">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -2676,12 +2670,12 @@
         <v>4</v>
       </c>
       <c r="D78">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2690,12 +2684,12 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2704,12 +2698,12 @@
         <v>6</v>
       </c>
       <c r="D80">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2718,12 +2712,12 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2732,12 +2726,12 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2746,12 +2740,12 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2760,12 +2754,12 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2774,12 +2768,12 @@
         <v>3</v>
       </c>
       <c r="D85">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2788,12 +2782,12 @@
         <v>5</v>
       </c>
       <c r="D86">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2802,12 +2796,12 @@
         <v>5</v>
       </c>
       <c r="D87">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2816,12 +2810,12 @@
         <v>3</v>
       </c>
       <c r="D88">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2830,12 +2824,12 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2844,12 +2838,12 @@
         <v>1</v>
       </c>
       <c r="D90">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -2858,12 +2852,12 @@
         <v>2</v>
       </c>
       <c r="D91">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -2872,12 +2866,12 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -2886,12 +2880,12 @@
         <v>3</v>
       </c>
       <c r="D93">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2900,12 +2894,12 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -2914,12 +2908,12 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2928,12 +2922,12 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2942,12 +2936,12 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2956,12 +2950,12 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2970,12 +2964,12 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2984,12 +2978,12 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -2998,12 +2992,12 @@
         <v>10</v>
       </c>
       <c r="D101">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3012,12 +3006,12 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3026,12 +3020,12 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3040,12 +3034,12 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3054,12 +3048,12 @@
         <v>1</v>
       </c>
       <c r="D105">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3068,12 +3062,12 @@
         <v>1</v>
       </c>
       <c r="D106">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3082,12 +3076,12 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3096,12 +3090,12 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3110,12 +3104,12 @@
         <v>3</v>
       </c>
       <c r="D109">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3124,12 +3118,12 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3138,12 +3132,12 @@
         <v>1</v>
       </c>
       <c r="D111">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3152,12 +3146,12 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3166,12 +3160,12 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3180,12 +3174,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3194,12 +3188,12 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3208,12 +3202,12 @@
         <v>3</v>
       </c>
       <c r="D116">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3222,12 +3216,12 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3236,12 +3230,12 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3250,12 +3244,12 @@
         <v>2</v>
       </c>
       <c r="D119">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3264,7 +3258,7 @@
         <v>9</v>
       </c>
       <c r="D120">
-        <v>0.614493874052537</v>
+        <v>0.6108468765230837</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
+++ b/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="252">
   <si>
     <t>pathway</t>
   </si>
@@ -37,6 +37,18 @@
     <t>overlap_features (name)</t>
   </si>
   <si>
+    <t>De novo fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E2345,E92,E256,E2525,E270</t>
+  </si>
+  <si>
+    <t>C00249,C06426/C06427,C00219,C00020/C00362,C00712</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$arachidonic acid$AMP/dGMP$(9Z)-Octadecenoic acid; (Z)-Octadec-9-enoic acid; Oleate; Oleic acid</t>
+  </si>
+  <si>
     <t>Glycosphingolipid metabolism</t>
   </si>
   <si>
@@ -49,58 +61,445 @@
     <t>Hexadecanoate (n-C16:0)$CMP$Psychosine sulfate$Sphinganine$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$Phytosphingosine; 4-D-Hydroxysphinganine</t>
   </si>
   <si>
+    <t>Vitamin B2 (riboflavin) metabolism</t>
+  </si>
+  <si>
+    <t>E276,E1373,E3036,E2525</t>
+  </si>
+  <si>
+    <t>C01847,C00255,C00061,C00020/C00362</t>
+  </si>
+  <si>
+    <t>Reduced FMN; FMNH2$Riboflavin$FMN$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Omega-3 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2325,E2525</t>
+  </si>
+  <si>
+    <t>C06426/C06427,C16300,C00020/C00362</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Omega-6 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E2525,E256</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C00219</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$arachidonic acid</t>
+  </si>
+  <si>
+    <t>Linoleate metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2348,E113,E2350,E480,E2321,E492,E2084,E2639,E2085,E2640</t>
+  </si>
+  <si>
+    <t>C06426/C06427,C14762/C14826/C14825,CE2061,C14762/C14826/C14825,CE2006/CE6506,CE5526/CE5527/C14765,C04717/C14827,CE2306/CE2305/CE2304/CE2303,CE6504,CE2306/CE2305/CE2304/CE2303,CE6504</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$/$//13-OxoODE; 13-KODE; (9Z,11E)-13-Oxooctadeca-9,11-dienoic acid$(9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoic acid; (9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoate; 13(S)-HPODE; 13S-Hydroperoxy-9Z,11E-octadecadienoic acid/9(S)-HPODE; 9(S)-HPOD; (10E,12Z)-(9S)-9-Hydroperoxyoctadeca-10,12-dienoic acid$12-O-D-glucuronoside-13-hydroxyoctadec-9Z-enoate/12-hydroxy-13-O-D-glucuronoside-octadec-9Z-enoate/10-hydroxy-octadec-12Z-enoate-9-beta-D-glucuronide/9-hydroxy-10-O-D-glucuronoside-12Z-octadecenoate$$12-O-D-glucuronoside-13-hydroxyoctadec-9Z-enoate/12-hydroxy-13-O-D-glucuronoside-octadec-9Z-enoate/10-hydroxy-octadec-12Z-enoate-9-beta-D-glucuronide/9-hydroxy-10-O-D-glucuronoside-12Z-octadecenoate$</t>
+  </si>
+  <si>
+    <t>Vitamin A (retinol) metabolism</t>
+  </si>
+  <si>
+    <t>E2525,E2283,E2485,E3147,E2278,E2513</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C16679/C16677/C16680,CE5594/CE1617,CE2962,CE5014,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$all-trans-18-Hydroxyretinoic acid/all-trans-4-Hydroxyretinoic acid/all-trans-5,6-Epoxyretinoic acid; all-trans-5,6-Epoxy-5,6-dihydroretinoic acid$9,13-cis-retinoate/9-cis-retinoate$rac-4-hydroxy-4-O-(beta-D-glucuronide)-all-trans-retinyl acetate$anhydroretinol$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
+  </si>
+  <si>
+    <t>Bile acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E2173,E3074,E3077,E1895,E3075,E2525,E2941</t>
+  </si>
+  <si>
+    <t>C05122/C15516,C05463/C05465,C05463/C05465,CE2202/C17335,C05463/C05465,C00020/C00362,C00695</t>
+  </si>
+  <si>
+    <t>taurocholic acid/Taurohyocholate; N-(3alpha,6alpha,7alpha-Trihydroxy-5beta-cholan-24-oyl)taurine$Taurodeoxycholate/Taurochenodeoxycholate; Chenodeoxycholoyltaurine$Taurodeoxycholate/Taurochenodeoxycholate; Chenodeoxycholoyltaurine$23S,25,26-trihydroxyvitamin D3/$Taurodeoxycholate/Taurochenodeoxycholate; Chenodeoxycholoyltaurine$AMP/dGMP$Cholate</t>
+  </si>
+  <si>
+    <t>CoA Catabolism</t>
+  </si>
+  <si>
+    <t>E2192,E2525,E2191</t>
+  </si>
+  <si>
+    <t>C00831,C00020/C00362,C00831</t>
+  </si>
+  <si>
+    <t>Pantetheine; (R)-Pantetheine$AMP/dGMP$Pantetheine; (R)-Pantetheine</t>
+  </si>
+  <si>
+    <t>Glycerophospholipid metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2383,E2558,E1351,E256,E468,E2985,E2513</t>
+  </si>
+  <si>
+    <t>C06426/C06427,C00836,C00055,,C00219,C00588/C05594,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Sphinganine$CMP$$arachidonic acid$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
+  </si>
+  <si>
+    <t>Fatty Acid Metabolism</t>
+  </si>
+  <si>
+    <t>E2345,E2634</t>
+  </si>
+  <si>
+    <t>C00249,</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$</t>
+  </si>
+  <si>
+    <t>Saturated fatty acids beta-oxidation</t>
+  </si>
+  <si>
+    <t>E2345</t>
+  </si>
+  <si>
+    <t>C00249</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)</t>
+  </si>
+  <si>
+    <t>Keratan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>E2558</t>
+  </si>
+  <si>
+    <t>C00055</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>O-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Fatty acid activation</t>
+  </si>
+  <si>
+    <t>E2345,E92,E2525</t>
+  </si>
+  <si>
+    <t>C00249,C06426/C06427,C00020/C00362</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Porphyrin metabolism</t>
+  </si>
+  <si>
+    <t>E2511,E1520,E2728,E354</t>
+  </si>
+  <si>
+    <t>,,,</t>
+  </si>
+  <si>
+    <t>$$$</t>
+  </si>
+  <si>
     <t>C21-steroid hormone biosynthesis and metabolism</t>
   </si>
   <si>
-    <t>E2263,E1036,E2398,E1116,E2274,E423,E1295,E2141,E1163,E2269,E422,E1164,E1954,E2399,E2648,E1691,E2457,E2669</t>
-  </si>
-  <si>
-    <t>C18045/C14497/C18075/C05294/C05139,C04042/C01953/C03681,17ahprgstrn/C03205/C05498/C01176,C05488/C05497/C05477/C02140,C00410,dhea/C03772/C01227/C00674/C00535,C05490,C03917/C05293/C00523/C04373/C04295,C05487/C05475/C05478,andrstndn/C00280,dhea/C03772/C01227/C00674/C00535,C05487/C05475/C05478,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,17ahprgstrn/C03205/C05498/C01176,C01124/C05469/C00735/C05473,CE1352,C05472,C05489/C05471/C05474</t>
-  </si>
-  <si>
-    <t>/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$11-Deoxycortisol; Cortodoxone/21-Deoxycortisol; 4-Pregnene-11beta,17alpha-diol-3,20-dione; 11beta,17alpha-Dihydroxyprogesterone/21-Hydroxy-5beta-pregnane-3,11,20-trione/Corticosterone; 11beta,21-Dihydroxy-4-pregnene-3,20-dione; Kendall's compound B; Reichstein's substance H$Progesterone; 4-Pregnene-3,20-dione$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$11-Dehydrocorticosterone$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$17alpha,21-Dihydroxypregnenolone/11beta,21-Dihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,21-diol-3,20-dione/3alpha,21-Dihydroxy-5beta-pregnane-11,20-dione; 5beta-Pregnane-3alpha,21-diol-11,20-dione$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$17alpha-Hydroxyprogesterone/11-Deoxycorticosterone; Deoxycorticosterone; Cortexone; 21-Hydroxy-4-pregnene-3,20-dione; Desoxycortone; DOC/11beta-Hydroxyprogesterone/17alpha-Hydroxyprogesterone; 17alpha-Hydroxy-4-pregnene-3,20-dione; Pregn-4-ene-3,20-dione-17-ol; 17alpha-Hydroxy-progesterone$18-Hydroxycorticosterone/17alpha,21-Dihydroxy-5beta-pregnane-3,11,20-trione; 5beta-Pregnane-17alpha,21-diol-3,11,20-trione; 4,5beta-Dihydrocortisone/Cortisol; Hydrocortisone; 11beta,17alpha,21-Trihydroxy-4-pregnene-3,20-dione; Kendall's compound F; Reichstein's substance M/11beta,21-Dihydroxy-3,20-oxo-5beta-pregnan-18-al$17alpha-hydroxypregnenolone sulfate$Urocortisol; 5beta-Pregnane-3alpha,11beta,17alpha,21-tetrol-20-one$11beta,17alpha,21-Trihydroxypregnenolone/11beta,17alpha,21-Trihydroxy-5beta-pregnane-3,20-dione; 5beta-Pregnane-11beta,17alpha,21-triol-3,20-dione/3alpha,11beta,21-Trihydroxy-20-oxo-5beta-pregnan-18-al</t>
+    <t>E2263,E1295,E2398,E1116,E2274,E1163,E422,E2141,E1164,E2269,E1954,E2399,E2648,E2457,E2669</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2108,E2525</t>
+  </si>
+  <si>
+    <t>,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Drug metabolism - other enzymes</t>
+  </si>
+  <si>
+    <t>E2179,E1536</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Tyrosine metabolism</t>
+  </si>
+  <si>
+    <t>E918,E227,E412,E190,E1975,E889,E413,E191,E890,E680,E432,E1222,E175,E632,E912,E209,E46,E336,E1059,E830,E931,E166,E1735,E914,E178,E468,E2525,E186,E281,E65,E168,E901,E66,E170</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,,,,,,,,,,,,,C00588/C05594,C00020/C00362,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$$$$$$$$$$$$$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$AMP/dGMP$$$$$$$</t>
+  </si>
+  <si>
+    <t>Histidine metabolism</t>
+  </si>
+  <si>
+    <t>E1488,E1403,E347,E2525</t>
+  </si>
+  <si>
+    <t>,,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Butanoate metabolism</t>
+  </si>
+  <si>
+    <t>E1044,E2525,E1045</t>
+  </si>
+  <si>
+    <t>,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP$</t>
   </si>
   <si>
     <t>Phosphatidylinositol phosphate metabolism</t>
   </si>
   <si>
-    <t>E2345,E2558,E1063</t>
-  </si>
-  <si>
-    <t>C00249,C00055,C15658</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)$CMP$6-(alpha-D-Glucosaminyl)-1D-myo-inositol</t>
-  </si>
-  <si>
-    <t>De novo fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E2345,E92,E256,E270</t>
-  </si>
-  <si>
-    <t>C00249,,,</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)$$$</t>
-  </si>
-  <si>
-    <t>Linoleate metabolism</t>
-  </si>
-  <si>
-    <t>E92,E2348,E113,E2350,E2321,E492,E2349,E2084,E2639,E2085,E2640</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>CoA Catabolism</t>
-  </si>
-  <si>
-    <t>E2192,E1107,E2191</t>
+    <t>E2345,E2558</t>
+  </si>
+  <si>
+    <t>C00249,C00055</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$CMP</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E1403,E347</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2525,E256,E1395,E2513,E2295</t>
+  </si>
+  <si>
+    <t>C06426/C06427,C00020/C00362,C00219,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP$arachidonic acid$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$</t>
+  </si>
+  <si>
+    <t>Valine, leucine and isoleucine degradation</t>
+  </si>
+  <si>
+    <t>E2525</t>
+  </si>
+  <si>
+    <t>C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Mono-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E1074</t>
+  </si>
+  <si>
+    <t>Phytanic acid peroxisomal oxidation</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
+    <t>Lysine metabolism</t>
+  </si>
+  <si>
+    <t>E2108,E2525,E1926</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>E2558,E35,E2970</t>
+  </si>
+  <si>
+    <t>C00055,,</t>
+  </si>
+  <si>
+    <t>CMP$$</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E1900,E1301,E1286,E2899,E1666,E256,E1899,E2525,E2295</t>
+  </si>
+  <si>
+    <t>,,,,,C00219,,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$$$$$arachidonic acid$$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>E445,E2558,E2525,E1039</t>
+  </si>
+  <si>
+    <t>,C00055,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$CMP$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E1353,E1475,E2525,E1074</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - lactoseries</t>
+  </si>
+  <si>
+    <t>Blood Group Biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
+  </si>
+  <si>
+    <t>Biopterin metabolism</t>
+  </si>
+  <si>
+    <t>E912,E1455,E1459,E1735</t>
+  </si>
+  <si>
+    <t>D4&amp;E4-neuroprostanes formation</t>
+  </si>
+  <si>
+    <t>E2895,E1408</t>
+  </si>
+  <si>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Selenoamino acid metabolism</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>E1129,E3004,E3062,E1128,E3153</t>
+  </si>
+  <si>
+    <t>,,,,</t>
+  </si>
+  <si>
+    <t>$$$$</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - globoseries</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin H (biotin) metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
+  </si>
+  <si>
+    <t>Aminosugars metabolism</t>
+  </si>
+  <si>
+    <t>E2558,E35</t>
+  </si>
+  <si>
+    <t>C00055,</t>
+  </si>
+  <si>
+    <t>CMP$</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E830,E227,E2525</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Vitamin B6 (pyridoxine) metabolism</t>
+  </si>
+  <si>
+    <t>E383,E384</t>
+  </si>
+  <si>
+    <t>Drug metabolism - cytochrome P450</t>
+  </si>
+  <si>
+    <t>E521,E2919,E2568,E2336,E178,E1274,E940</t>
+  </si>
+  <si>
+    <t>,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$</t>
+  </si>
+  <si>
+    <t>Hexose phosphorylation</t>
+  </si>
+  <si>
+    <t>E785,E830,E784</t>
   </si>
   <si>
     <t>,,</t>
@@ -109,507 +508,201 @@
     <t>$$</t>
   </si>
   <si>
-    <t>Saturated fatty acids beta-oxidation</t>
-  </si>
-  <si>
-    <t>E2345</t>
-  </si>
-  <si>
-    <t>C00249</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)</t>
-  </si>
-  <si>
-    <t>Keratan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>E2558</t>
-  </si>
-  <si>
-    <t>C00055</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>O-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycerophospholipid metabolism</t>
-  </si>
-  <si>
-    <t>E92,E2383,E2558,E586,E1351,E256,E468,E2985</t>
-  </si>
-  <si>
-    <t>,C00836,C00055,,,,C00588/C05594,</t>
-  </si>
-  <si>
-    <t>$Sphinganine$CMP$$$$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E35,E2558,E33,E2970</t>
-  </si>
-  <si>
-    <t>,C00055,,</t>
-  </si>
-  <si>
-    <t>$CMP$$</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E1900,E1301,E1286,E2899,E1901,E1287,E256,E1666,E1899,E1820,E2295</t>
-  </si>
-  <si>
-    <t>Drug metabolism - other enzymes</t>
-  </si>
-  <si>
-    <t>E2179,E1536</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>D4&amp;E4-neuroprostanes formation</t>
-  </si>
-  <si>
-    <t>E2895,E2995,E1408</t>
-  </si>
-  <si>
-    <t>Porphyrin metabolism</t>
-  </si>
-  <si>
-    <t>E2511,E1520,E2728,E354</t>
-  </si>
-  <si>
-    <t>,,,</t>
-  </si>
-  <si>
-    <t>$$$</t>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>E1895</t>
+  </si>
+  <si>
+    <t>CE2202/C17335</t>
+  </si>
+  <si>
+    <t>23S,25,26-trihydroxyvitamin D3/</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>E3034</t>
+  </si>
+  <si>
+    <t>Keratan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E35</t>
+  </si>
+  <si>
+    <t>Hyaluronan Metabolism</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+  </si>
+  <si>
+    <t>Heparan sulfate degradation</t>
+  </si>
+  <si>
+    <t>Alanine and Aspartate Metabolism</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>E1239,E2525</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>E26,E2525</t>
+  </si>
+  <si>
+    <t>Glycolysis and Gluconeogenesis</t>
+  </si>
+  <si>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E3065,E1331,E2525,E256</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362,C00219</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP$arachidonic acid</t>
+  </si>
+  <si>
+    <t>Tryptophan metabolism</t>
+  </si>
+  <si>
+    <t>E666,E877,E889,E760,E890,E2103,E1186,E126,E632,E1187,E737,E2747,E846,E738,E1735,E2525,E651,E705,E2750,E767</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,,,C00020/C00362,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$$$AMP/dGMP$$$$</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
   </si>
   <si>
     <t>Limonene and pinene degradation</t>
   </si>
   <si>
-    <t>E263,E265,E93</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>E1074</t>
-  </si>
-  <si>
-    <t>Keratan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E35,E33</t>
+    <t>E265</t>
+  </si>
+  <si>
+    <t>Arginine and Proline Metabolism</t>
+  </si>
+  <si>
+    <t>E26</t>
+  </si>
+  <si>
+    <t>Urea cycle/amino group metabolism</t>
+  </si>
+  <si>
+    <t>E26,E412,E1529,E175,E1535,E413</t>
+  </si>
+  <si>
+    <t>,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
+  </si>
+  <si>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E2442</t>
+  </si>
+  <si>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2263,E2141,E2269,E3018,E1954,E422</t>
+  </si>
+  <si>
+    <t>Purine metabolism</t>
+  </si>
+  <si>
+    <t>E1671,E2525,E1677</t>
+  </si>
+  <si>
+    <t>R Group Synthesis</t>
+  </si>
+  <si>
+    <t>C5-Branched dibasic acid metabolism</t>
+  </si>
+  <si>
+    <t>Pyruvate Metabolism</t>
+  </si>
+  <si>
+    <t>Chondroitin sulfate degradation</t>
+  </si>
+  <si>
+    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
+  </si>
+  <si>
+    <t>Glycerolipid metabolism</t>
+  </si>
+  <si>
+    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
+  </si>
+  <si>
+    <t>Parathio degradation</t>
+  </si>
+  <si>
+    <t>Electron transport chain</t>
+  </si>
+  <si>
+    <t>Caffeine metabolism</t>
   </si>
   <si>
     <t>Lipoate metabolism</t>
   </si>
   <si>
-    <t>E744,E2412</t>
-  </si>
-  <si>
-    <t>Omega-3 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E92,E2325</t>
-  </si>
-  <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>Aminosugars metabolism</t>
-  </si>
-  <si>
-    <t>E35,E2558,E33</t>
-  </si>
-  <si>
-    <t>,C00055,</t>
-  </si>
-  <si>
-    <t>$CMP$</t>
-  </si>
-  <si>
-    <t>Hyaluronan Metabolism</t>
-  </si>
-  <si>
-    <t>Heparan sulfate degradation</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - lactoseries</t>
-  </si>
-  <si>
-    <t>Blood Group Biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
-  </si>
-  <si>
-    <t>Omega-6 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>E256</t>
-  </si>
-  <si>
-    <t>Bile acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E2173,E3074,E3077,E1895,E2941</t>
-  </si>
-  <si>
-    <t>,,,,</t>
-  </si>
-  <si>
-    <t>$$$$</t>
-  </si>
-  <si>
-    <t>Vitamin B2 (riboflavin) metabolism</t>
-  </si>
-  <si>
-    <t>E276,E1373</t>
-  </si>
-  <si>
-    <t>Fatty acid activation</t>
-  </si>
-  <si>
-    <t>E2345,E92</t>
-  </si>
-  <si>
-    <t>C00249,</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)$</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>E35,E850,E33</t>
-  </si>
-  <si>
-    <t>Tyrosine metabolism</t>
-  </si>
-  <si>
-    <t>E918,E412,E190,E1975,E285,E889,E413,E191,E890,E680,E432,E1222,E219,E175,E632,E912,E336,E1059,E830,E931,E166,E1735,E178,E468,E119,E186,E281,E65,E1439,E168,E901,E66,E170</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,,,,,,,,,,C00588/C05594,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$$$$$$$$$$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Hexose phosphorylation</t>
-  </si>
-  <si>
-    <t>E785,E850,E830,E784</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>E310,E315</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>Fatty Acid Metabolism</t>
-  </si>
-  <si>
-    <t>Selenoamino acid metabolism</t>
-  </si>
-  <si>
-    <t>E1844</t>
-  </si>
-  <si>
-    <t>Biopterin metabolism</t>
-  </si>
-  <si>
-    <t>E912,E1455,E1439,E1735</t>
-  </si>
-  <si>
-    <t>Butanoate metabolism</t>
-  </si>
-  <si>
-    <t>E1046,E137</t>
-  </si>
-  <si>
-    <t>Arginine and Proline Metabolism</t>
-  </si>
-  <si>
-    <t>E442,E26</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>E2108</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - globoseries</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>E744</t>
-  </si>
-  <si>
-    <t>Lysine metabolism</t>
-  </si>
-  <si>
-    <t>E2108,E1926</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E1129,E3004,E1119,E2859,E1128</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>E445,E2558,E1039</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>E1895</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E1403</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (pyridoxine) metabolism</t>
-  </si>
-  <si>
-    <t>E383,E384</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E92,E1395,E256,E2295</t>
-  </si>
-  <si>
-    <t>Drug metabolism - cytochrome P450</t>
-  </si>
-  <si>
-    <t>E521,E2919,E2568,E2336,E178,E1274,E940</t>
-  </si>
-  <si>
-    <t>,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$</t>
-  </si>
-  <si>
-    <t>Purine metabolism</t>
-  </si>
-  <si>
-    <t>E116,E1495,E1844,E959,E1671,E1677</t>
-  </si>
-  <si>
-    <t>,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$</t>
-  </si>
-  <si>
-    <t>Tryptophan metabolism</t>
-  </si>
-  <si>
-    <t>E666,E877,E889,E760,E890,E647,E598,E126,E1138,E632,E1187,E737,E2747,E846,E738,E1735,E588,E651,E2750,E1439,E959,E706,E500</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
-  </si>
-  <si>
-    <t>Alanine and Aspartate Metabolism</t>
-  </si>
-  <si>
-    <t>E442</t>
-  </si>
-  <si>
-    <t>Histidine metabolism</t>
-  </si>
-  <si>
-    <t>E1488,E1403</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E2442,E850</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E1844,E26</t>
-  </si>
-  <si>
-    <t>Urea cycle/amino group metabolism</t>
-  </si>
-  <si>
-    <t>E26,E1528,E412,E175,E1535,E442,E413</t>
-  </si>
-  <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E1036,E2263,E423,E2141,E2269,E3018,E1954,E422</t>
-  </si>
-  <si>
-    <t>C04042/C01953/C03681,C18045/C14497/C18075/C05294/C05139,dhea/C03772/C01227/C00674/C00535,C03917/C05293/C00523/C04373/C04295,andrstndn/C00280,,andrstrnglc/C11135/C11136/5adtststeroneglc/ahandrostanglc,dhea/C03772/C01227/C00674/C00535</t>
-  </si>
-  <si>
-    <t>20alpha-Hydroxy-4-pregnen-3-one; 20alpha-Hydroxypregn-4-en-3-one; 20alpha-Hydroxyprogesterone/Pregnenolone; 5-Pregnen-3beta-ol-20-one; 3beta-Hydroxypregn-5-en-20-one/5alpha-Pregnane-3,20-dione$/6beta-Hydroxytestosterone; 6beta,17beta-Dihydroxyandrost-4-en-3-one//19-Hydroxytestosterone; 17beta,19-Dihydroxyandrost-4-en-3-one/16alpha-Hydroxydehydroepiandrosterone; 5-Androstene-3beta,16alpha-diol-17-one$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone$5alpha-Dihydrotestosterone/5beta-Dihydrotestosterone/Androsterone/3alpha-Hydroxy-5beta-androstan-17-one; Etiocholan-3alpha-ol-17-one; 3alpha-Hydroxyetiocholan-17-one/Androst-5-ene-3beta,17beta-diol; 3beta,17beta-Dihydroxyandrost-5-ene; 3beta,17beta-Dihydroxy-5-androstene; Androstenediol$Androstenedione/Androst-4-ene-3,17-dione; Androstenedione; 4-Androstene-3,17-dione$$androsterone glucuronide/androsterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide/5alpha-Dihydrotestosterone glucuronide/Etiocholan-3alpha-ol-17-one 3-glucuronide$Dehydroepiandrosterone/5beta-Androstane-3,17-dione/3beta-Hydroxyandrost-5-en-17-one; Dehydroepiandrosterone; Dehydroisoandrosterone; DHA; DHEA/5alpha-Androstane-3,17-dione; Androstanedione/Testosterone</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E1353,E1074</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
-  </si>
-  <si>
-    <t>E959</t>
+    <t>Heparan sulfate biosynthesis</t>
   </si>
   <si>
     <t>Vitamin B9 (folate) metabolism</t>
   </si>
   <si>
-    <t>E2050</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>E1239</t>
+    <t>Glyoxylate and Dicarboxylate Metabolism</t>
+  </si>
+  <si>
+    <t>Glycosaminoglycan degradation</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation</t>
+  </si>
+  <si>
+    <t>ROS Detoxification</t>
   </si>
   <si>
     <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
   </si>
   <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E830</t>
-  </si>
-  <si>
-    <t>Vitamin A (retinol) metabolism</t>
-  </si>
-  <si>
-    <t>E2278</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E3065,E256</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>R Group Synthesis</t>
-  </si>
-  <si>
-    <t>C5-Branched dibasic acid metabolism</t>
-  </si>
-  <si>
-    <t>Pyruvate Metabolism</t>
-  </si>
-  <si>
-    <t>Chondroitin sulfate degradation</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycerolipid metabolism</t>
-  </si>
-  <si>
-    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
-  </si>
-  <si>
-    <t>Parathio degradation</t>
-  </si>
-  <si>
-    <t>Electron transport chain</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
-  </si>
-  <si>
-    <t>Caffeine metabolism</t>
-  </si>
-  <si>
-    <t>Heparan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>Glyoxylate and Dicarboxylate Metabolism</t>
-  </si>
-  <si>
-    <t>Valine, leucine and isoleucine degradation</t>
-  </si>
-  <si>
-    <t>Glycosaminoglycan degradation</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation</t>
-  </si>
-  <si>
-    <t>ROS Detoxification</t>
-  </si>
-  <si>
-    <t>Mono-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
     <t>Geraniol degradation</t>
   </si>
   <si>
@@ -677,12 +770,6 @@
   </si>
   <si>
     <t>Trihydroxycoprostanoyl-CoA beta-oxidation</t>
-  </si>
-  <si>
-    <t>Phytanic acid peroxisomal oxidation</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
   </si>
 </sst>
 </file>
@@ -1045,13 +1132,13 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>0.02077276012167863</v>
+        <v>0.01178131459975463</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1068,13 +1155,13 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>0.03620107225088654</v>
+        <v>0.01455437723735735</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1091,13 +1178,13 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>0.03983126334011193</v>
+        <v>0.0190753096586612</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1114,13 +1201,13 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>0.05173022302146182</v>
+        <v>0.03282297776507958</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1137,13 +1224,13 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>0.05641921984504462</v>
+        <v>0.03410026722239962</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1160,13 +1247,13 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="D7">
-        <v>0.06344431186030487</v>
+        <v>0.03574729836473337</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1183,13 +1270,13 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>0.07717517352649535</v>
+        <v>0.04489000184870842</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1206,13 +1293,13 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>0.07717517352649535</v>
+        <v>0.0449740340498479</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1229,27 +1316,27 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>0.07717517352649535</v>
+        <v>0.04954538579183543</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -1258,481 +1345,487 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>0.07893984975042437</v>
+        <v>0.05441925345792507</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
         <v>4</v>
       </c>
-      <c r="C12">
-        <v>12</v>
-      </c>
       <c r="D12">
-        <v>0.09695635367472816</v>
+        <v>0.06426782743147175</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>0.1082838943883296</v>
+        <v>0.07041898455488144</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>0.1192921127376011</v>
+        <v>0.07041898455488144</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>0.1233592712727517</v>
+        <v>0.07041898455488144</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>0.1234264970336633</v>
+        <v>0.07288953126838205</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D17">
-        <v>0.1483168350111763</v>
+        <v>0.0986201912572898</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18">
         <v>62</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
       <c r="D18">
-        <v>0.1516613166165275</v>
+        <v>0.1003008352800793</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>0.1529386060738475</v>
+        <v>0.1026201240315289</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>0.1529386060738475</v>
+        <v>0.1026201240315289</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>152</v>
       </c>
       <c r="D21">
-        <v>0.1529386060738475</v>
+        <v>0.1123510529234803</v>
       </c>
       <c r="E21" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D22">
-        <v>0.1838288432127191</v>
+        <v>0.1225861750222685</v>
       </c>
       <c r="E22" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B23">
         <v>3</v>
       </c>
       <c r="C23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>0.1838288432127191</v>
+        <v>0.1296112670375288</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>0.2038621199643703</v>
+        <v>0.1372413909009933</v>
       </c>
       <c r="E24" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>0.2038621199643703</v>
+        <v>0.1372413909009933</v>
       </c>
       <c r="E25" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D26">
-        <v>0.2320297137863229</v>
+        <v>0.1403841952236097</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="G26" t="s">
-        <v>38</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>0.2320297137863229</v>
+        <v>0.1417455168820692</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="G27" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>0.2320297137863229</v>
+        <v>0.1417455168820692</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>0.2320297137863229</v>
+        <v>0.1417455168820692</v>
       </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>0.2475084452362145</v>
+        <v>0.1417455168820692</v>
       </c>
       <c r="E30" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D31">
-        <v>0.2496932824658409</v>
+        <v>0.1540814440093444</v>
       </c>
       <c r="E31" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G31" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D32">
-        <v>0.2496932824658409</v>
+        <v>0.1540814440093444</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="F32" t="s">
         <v>90</v>
@@ -1743,162 +1836,168 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D33">
-        <v>0.2618947580712929</v>
+        <v>0.1881312919110603</v>
       </c>
       <c r="E33" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="F33" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="G33" t="s">
-        <v>30</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="B34">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C34">
-        <v>152</v>
+        <v>41</v>
       </c>
       <c r="D34">
-        <v>0.2661467874489504</v>
+        <v>0.1944000941160653</v>
       </c>
       <c r="E34" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="G34" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D35">
-        <v>0.2723315574528159</v>
+        <v>0.1969714794709333</v>
       </c>
       <c r="E35" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="G35" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D36">
-        <v>0.3054570511419976</v>
+        <v>0.1969714794709333</v>
       </c>
       <c r="E36" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="G36" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>0.3054570511419976</v>
+        <v>0.2163661114939245</v>
       </c>
       <c r="E37" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G37" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>0.309893951362162</v>
+        <v>0.2163661114939245</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F38" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G38" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>0.309893951362162</v>
+        <v>0.2163661114939245</v>
       </c>
       <c r="E39" t="s">
-        <v>105</v>
+        <v>56</v>
+      </c>
+      <c r="F39" t="s">
+        <v>57</v>
+      </c>
+      <c r="G39" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -1907,107 +2006,113 @@
         <v>19</v>
       </c>
       <c r="D40">
-        <v>0.3101292415253525</v>
+        <v>0.2580124703786491</v>
       </c>
       <c r="E40" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="F40" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D41">
-        <v>0.3359103208349439</v>
+        <v>0.26750810910741</v>
       </c>
       <c r="E41" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="F41" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>0.3359103208349439</v>
+        <v>0.2861968706408295</v>
       </c>
       <c r="E42" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F42" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="G42" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>0.3535906959546898</v>
+        <v>0.2861968706408295</v>
       </c>
       <c r="E43" t="s">
-        <v>113</v>
+        <v>103</v>
+      </c>
+      <c r="F43" t="s">
+        <v>104</v>
+      </c>
+      <c r="G43" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D44">
-        <v>0.3535906959546898</v>
+        <v>0.3342128703719265</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="F44" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="G44" t="s">
-        <v>38</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -2016,118 +2121,136 @@
         <v>5</v>
       </c>
       <c r="D45">
-        <v>0.3535906959546898</v>
+        <v>0.3380615451841146</v>
       </c>
       <c r="E45" t="s">
-        <v>116</v>
+        <v>56</v>
+      </c>
+      <c r="F45" t="s">
+        <v>57</v>
+      </c>
+      <c r="G45" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D46">
-        <v>0.368178686072503</v>
+        <v>0.3380615451841146</v>
       </c>
       <c r="E46" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="F46" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="G46" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
         <v>5</v>
       </c>
-      <c r="C47">
-        <v>27</v>
-      </c>
       <c r="D47">
-        <v>0.3748676492832053</v>
+        <v>0.3380615451841146</v>
       </c>
       <c r="E47" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="F47" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="G47" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D48">
-        <v>0.3853212551049562</v>
+        <v>0.3380615451841146</v>
       </c>
       <c r="E48" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="G48" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D49">
-        <v>0.3996739550595788</v>
+        <v>0.3430530579317995</v>
       </c>
       <c r="E49" t="s">
-        <v>124</v>
+        <v>147</v>
+      </c>
+      <c r="F49" t="s">
+        <v>148</v>
+      </c>
+      <c r="G49" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D50">
-        <v>0.3996739550595788</v>
+        <v>0.3527671803835229</v>
       </c>
       <c r="E50" t="s">
-        <v>126</v>
+        <v>151</v>
+      </c>
+      <c r="F50" t="s">
+        <v>152</v>
+      </c>
+      <c r="G50" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -2136,136 +2259,124 @@
         <v>12</v>
       </c>
       <c r="D51">
-        <v>0.4031865010672089</v>
+        <v>0.37283407001563</v>
       </c>
       <c r="E51" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="F51" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C52">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D52">
-        <v>0.429673450866372</v>
+        <v>0.3744979075981916</v>
       </c>
       <c r="E52" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="F52" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="G52" t="s">
-        <v>59</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="B53">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D53">
-        <v>0.4330683517924068</v>
+        <v>0.3771869380346549</v>
       </c>
       <c r="E53" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="F53" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="G53" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
         <v>6</v>
       </c>
-      <c r="C54">
-        <v>35</v>
-      </c>
       <c r="D54">
-        <v>0.4370010588057344</v>
+        <v>0.378766743416077</v>
       </c>
       <c r="E54" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="F54" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="G54" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="B55">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="D55">
-        <v>0.4407152820960992</v>
+        <v>0.378766743416077</v>
       </c>
       <c r="E55" t="s">
-        <v>140</v>
-      </c>
-      <c r="F55" t="s">
-        <v>141</v>
-      </c>
-      <c r="G55" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56">
-        <v>0.4427152484832187</v>
+        <v>0.378766743416077</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
-      </c>
-      <c r="F56" t="s">
-        <v>37</v>
-      </c>
-      <c r="G56" t="s">
-        <v>38</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2274,478 +2385,532 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>0.4427152484832187</v>
+        <v>0.4232197778188602</v>
       </c>
       <c r="E57" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D58">
-        <v>0.4664459420850069</v>
+        <v>0.4232197778188602</v>
       </c>
       <c r="E58" t="s">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="F58" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G58" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D59">
-        <v>0.4664459420850069</v>
+        <v>0.4232197778188602</v>
       </c>
       <c r="E59" t="s">
-        <v>149</v>
-      </c>
-      <c r="F59" t="s">
-        <v>52</v>
-      </c>
-      <c r="G59" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D60">
-        <v>0.4664459420850069</v>
+        <v>0.4232197778188602</v>
       </c>
       <c r="E60" t="s">
-        <v>151</v>
+        <v>103</v>
       </c>
       <c r="F60" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="G60" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="B61">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D61">
-        <v>0.484428833128855</v>
+        <v>0.4370010588057344</v>
       </c>
       <c r="E61" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="F61" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="G61" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="B62">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D62">
-        <v>0.5193021966017378</v>
+        <v>0.4370010588057344</v>
       </c>
       <c r="E62" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="F62" t="s">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="G62" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D63">
-        <v>0.5276381909547738</v>
+        <v>0.4591687534663283</v>
       </c>
       <c r="E63" t="s">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="F63" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="G63" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D64">
-        <v>0.5286129644879918</v>
+        <v>0.4904287322902136</v>
       </c>
       <c r="E64" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="F64" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="G64" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D65">
-        <v>0.5286129644879918</v>
+        <v>0.4904287322902136</v>
       </c>
       <c r="E65" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D66">
-        <v>0.5441253088183392</v>
+        <v>0.4904287322902136</v>
       </c>
       <c r="E66" t="s">
-        <v>164</v>
+        <v>103</v>
+      </c>
+      <c r="F66" t="s">
+        <v>104</v>
+      </c>
+      <c r="G66" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C67">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D67">
-        <v>0.5441253088183392</v>
+        <v>0.4921766020739147</v>
       </c>
       <c r="E67" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="F67" t="s">
-        <v>33</v>
+        <v>186</v>
       </c>
       <c r="G67" t="s">
-        <v>34</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C68">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="D68">
-        <v>0.5812675417219879</v>
+        <v>0.5053864640930404</v>
       </c>
       <c r="E68" t="s">
-        <v>167</v>
+        <v>189</v>
+      </c>
+      <c r="F68" t="s">
+        <v>190</v>
+      </c>
+      <c r="G68" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D69">
-        <v>0.5869649249592443</v>
+        <v>0.5138569099678997</v>
       </c>
       <c r="E69" t="s">
-        <v>116</v>
+        <v>56</v>
+      </c>
+      <c r="F69" t="s">
+        <v>57</v>
+      </c>
+      <c r="G69" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D70">
-        <v>0.5960067898018521</v>
+        <v>0.5138569099678997</v>
       </c>
       <c r="E70" t="s">
-        <v>170</v>
+        <v>103</v>
+      </c>
+      <c r="F70" t="s">
+        <v>104</v>
+      </c>
+      <c r="G70" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D71">
-        <v>0.5999394968151796</v>
+        <v>0.5138569099678997</v>
       </c>
       <c r="E71" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D72">
-        <v>0.6045948807583066</v>
+        <v>0.5138569099678997</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
-      </c>
-      <c r="F72" t="s">
-        <v>52</v>
-      </c>
-      <c r="G72" t="s">
-        <v>53</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C73">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D73">
-        <v>0.6108468765230837</v>
+        <v>0.5169156820893767</v>
+      </c>
+      <c r="E73" t="s">
+        <v>199</v>
+      </c>
+      <c r="F73" t="s">
+        <v>200</v>
+      </c>
+      <c r="G73" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D74">
-        <v>0.6108468765230837</v>
+        <v>0.5308986403589856</v>
+      </c>
+      <c r="E74" t="s">
+        <v>52</v>
+      </c>
+      <c r="F74" t="s">
+        <v>53</v>
+      </c>
+      <c r="G74" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D75">
-        <v>0.6108468765230837</v>
+        <v>0.5598561368716493</v>
+      </c>
+      <c r="E75" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D76">
-        <v>0.6108468765230837</v>
+        <v>0.5715870321507202</v>
+      </c>
+      <c r="E76" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D77">
-        <v>0.6108468765230837</v>
+        <v>0.5793852204164636</v>
+      </c>
+      <c r="E77" t="s">
+        <v>207</v>
+      </c>
+      <c r="F77" t="s">
+        <v>200</v>
+      </c>
+      <c r="G77" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D78">
-        <v>0.6108468765230837</v>
+        <v>0.5951496613502294</v>
+      </c>
+      <c r="E78" t="s">
+        <v>209</v>
+      </c>
+      <c r="F78" t="s">
+        <v>90</v>
+      </c>
+      <c r="G78" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D80">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="B82">
         <v>0</v>
       </c>
       <c r="C82">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D83">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2754,54 +2919,54 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D85">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
       <c r="C86">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2810,82 +2975,82 @@
         <v>3</v>
       </c>
       <c r="D88">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D89">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D90">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D92">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D93">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -2894,26 +3059,26 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D95">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2922,26 +3087,26 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D97">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2950,12 +3115,12 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2964,12 +3129,12 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -2978,26 +3143,26 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="B101">
         <v>0</v>
       </c>
       <c r="C101">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3006,26 +3171,26 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D103">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3034,82 +3199,82 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="B106">
         <v>0</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3118,26 +3283,26 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D111">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3146,26 +3311,26 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3174,12 +3339,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3188,77 +3353,77 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>218</v>
+        <v>247</v>
       </c>
       <c r="B116">
         <v>0</v>
       </c>
       <c r="C116">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D118">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="B119">
         <v>0</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="B120">
         <v>0</v>
       </c>
       <c r="C120">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>0.6108468765230837</v>
+        <v>0.6116199727735668</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
+++ b/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
@@ -1138,7 +1138,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.01178131459975463</v>
+        <v>0.0111594763113225</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1161,7 +1161,7 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>0.01455437723735735</v>
+        <v>0.01447034503621788</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1184,7 +1184,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>0.0190753096586612</v>
+        <v>0.01805011680475958</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1207,7 +1207,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>0.03282297776507958</v>
+        <v>0.03191542999277323</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1230,7 +1230,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>0.03410026722239962</v>
+        <v>0.03329355809146065</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1253,7 +1253,7 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>0.03574729836473337</v>
+        <v>0.03499100855447808</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1276,7 +1276,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>0.04489000184870842</v>
+        <v>0.04441942152232736</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1299,7 +1299,7 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>0.0449740340498479</v>
+        <v>0.04443622796255525</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1322,7 +1322,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>0.04954538579183543</v>
+        <v>0.0496462244332028</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1345,7 +1345,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>0.05441925345792507</v>
+        <v>0.05452009209929245</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1368,7 +1368,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>0.06426782743147175</v>
+        <v>0.06354515050167224</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1391,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0.07041898455488144</v>
+        <v>0.0691080822171056</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1414,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0.07041898455488144</v>
+        <v>0.0691080822171056</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1437,7 +1437,7 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>0.07041898455488144</v>
+        <v>0.0691080822171056</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
@@ -1460,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="D16">
-        <v>0.07288953126838205</v>
+        <v>0.07149459672946673</v>
       </c>
       <c r="E16" t="s">
         <v>61</v>
@@ -1483,7 +1483,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.0986201912572898</v>
+        <v>0.09625048318515655</v>
       </c>
       <c r="E17" t="s">
         <v>65</v>
@@ -1506,7 +1506,7 @@
         <v>62</v>
       </c>
       <c r="D18">
-        <v>0.1003008352800793</v>
+        <v>0.09865380413774559</v>
       </c>
       <c r="E18" t="s">
         <v>69</v>
@@ -1529,7 +1529,7 @@
         <v>5</v>
       </c>
       <c r="D19">
-        <v>0.1026201240315289</v>
+        <v>0.101477286096032</v>
       </c>
       <c r="E19" t="s">
         <v>73</v>
@@ -1552,7 +1552,7 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>0.1026201240315289</v>
+        <v>0.101477286096032</v>
       </c>
       <c r="E20" t="s">
         <v>77</v>
@@ -1575,7 +1575,7 @@
         <v>152</v>
       </c>
       <c r="D21">
-        <v>0.1123510529234803</v>
+        <v>0.1101326028133981</v>
       </c>
       <c r="E21" t="s">
         <v>81</v>
@@ -1598,7 +1598,7 @@
         <v>14</v>
       </c>
       <c r="D22">
-        <v>0.1225861750222685</v>
+        <v>0.1205189828742374</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
@@ -1621,7 +1621,7 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>0.1296112670375288</v>
+        <v>0.1267373657585587</v>
       </c>
       <c r="E23" t="s">
         <v>89</v>
@@ -1644,7 +1644,7 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>0.1372413909009933</v>
+        <v>0.1342498445404279</v>
       </c>
       <c r="E24" t="s">
         <v>93</v>
@@ -1667,7 +1667,7 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>0.1372413909009933</v>
+        <v>0.1342498445404279</v>
       </c>
       <c r="E25" t="s">
         <v>97</v>
@@ -1690,7 +1690,7 @@
         <v>24</v>
       </c>
       <c r="D26">
-        <v>0.1403841952236097</v>
+        <v>0.1372918102216769</v>
       </c>
       <c r="E26" t="s">
         <v>99</v>
@@ -1713,7 +1713,7 @@
         <v>2</v>
       </c>
       <c r="D27">
-        <v>0.1417455168820692</v>
+        <v>0.1383674223962622</v>
       </c>
       <c r="E27" t="s">
         <v>103</v>
@@ -1736,7 +1736,7 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>0.1417455168820692</v>
+        <v>0.1383674223962622</v>
       </c>
       <c r="E28" t="s">
         <v>103</v>
@@ -1759,7 +1759,7 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <v>0.1417455168820692</v>
+        <v>0.1383674223962622</v>
       </c>
       <c r="E29" t="s">
         <v>108</v>
@@ -1776,7 +1776,7 @@
         <v>2</v>
       </c>
       <c r="D30">
-        <v>0.1417455168820692</v>
+        <v>0.1383674223962622</v>
       </c>
       <c r="E30" t="s">
         <v>103</v>
@@ -1799,7 +1799,7 @@
         <v>11</v>
       </c>
       <c r="D31">
-        <v>0.1540814440093444</v>
+        <v>0.1497958017512311</v>
       </c>
       <c r="E31" t="s">
         <v>40</v>
@@ -1822,7 +1822,7 @@
         <v>11</v>
       </c>
       <c r="D32">
-        <v>0.1540814440093444</v>
+        <v>0.1497958017512311</v>
       </c>
       <c r="E32" t="s">
         <v>112</v>
@@ -1845,7 +1845,7 @@
         <v>12</v>
       </c>
       <c r="D33">
-        <v>0.1881312919110603</v>
+        <v>0.1830221340817801</v>
       </c>
       <c r="E33" t="s">
         <v>114</v>
@@ -1868,7 +1868,7 @@
         <v>41</v>
       </c>
       <c r="D34">
-        <v>0.1944000941160653</v>
+        <v>0.1891564847649619</v>
       </c>
       <c r="E34" t="s">
         <v>118</v>
@@ -1891,7 +1891,7 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0.1969714794709333</v>
+        <v>0.1917950958807415</v>
       </c>
       <c r="E35" t="s">
         <v>122</v>
@@ -1914,7 +1914,7 @@
         <v>17</v>
       </c>
       <c r="D36">
-        <v>0.1969714794709333</v>
+        <v>0.1917950958807415</v>
       </c>
       <c r="E36" t="s">
         <v>126</v>
@@ -1937,7 +1937,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>0.2163661114939245</v>
+        <v>0.2094082452395758</v>
       </c>
       <c r="E37" t="s">
         <v>56</v>
@@ -1960,7 +1960,7 @@
         <v>3</v>
       </c>
       <c r="D38">
-        <v>0.2163661114939245</v>
+        <v>0.2094082452395758</v>
       </c>
       <c r="E38" t="s">
         <v>56</v>
@@ -1983,7 +1983,7 @@
         <v>3</v>
       </c>
       <c r="D39">
-        <v>0.2163661114939245</v>
+        <v>0.2094082452395758</v>
       </c>
       <c r="E39" t="s">
         <v>56</v>
@@ -2006,7 +2006,7 @@
         <v>19</v>
       </c>
       <c r="D40">
-        <v>0.2580124703786491</v>
+        <v>0.2501302499117662</v>
       </c>
       <c r="E40" t="s">
         <v>133</v>
@@ -2029,7 +2029,7 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>0.26750810910741</v>
+        <v>0.2611888875817213</v>
       </c>
       <c r="E41" t="s">
         <v>135</v>
@@ -2052,7 +2052,7 @@
         <v>4</v>
       </c>
       <c r="D42">
-        <v>0.2861968706408295</v>
+        <v>0.2799616813162804</v>
       </c>
       <c r="E42" t="s">
         <v>103</v>
@@ -2075,7 +2075,7 @@
         <v>4</v>
       </c>
       <c r="D43">
-        <v>0.2861968706408295</v>
+        <v>0.2799616813162804</v>
       </c>
       <c r="E43" t="s">
         <v>103</v>
@@ -2098,7 +2098,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>0.3342128703719265</v>
+        <v>0.3255239407741046</v>
       </c>
       <c r="E44" t="s">
         <v>139</v>
@@ -2121,7 +2121,7 @@
         <v>5</v>
       </c>
       <c r="D45">
-        <v>0.3380615451841146</v>
+        <v>0.3292717769449253</v>
       </c>
       <c r="E45" t="s">
         <v>56</v>
@@ -2144,7 +2144,7 @@
         <v>5</v>
       </c>
       <c r="D46">
-        <v>0.3380615451841146</v>
+        <v>0.3292717769449253</v>
       </c>
       <c r="E46" t="s">
         <v>103</v>
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="D47">
-        <v>0.3380615451841146</v>
+        <v>0.3292717769449253</v>
       </c>
       <c r="E47" t="s">
         <v>103</v>
@@ -2190,7 +2190,7 @@
         <v>5</v>
       </c>
       <c r="D48">
-        <v>0.3380615451841146</v>
+        <v>0.3292717769449253</v>
       </c>
       <c r="E48" t="s">
         <v>103</v>
@@ -2213,7 +2213,7 @@
         <v>11</v>
       </c>
       <c r="D49">
-        <v>0.3430530579317995</v>
+        <v>0.3345321927362565</v>
       </c>
       <c r="E49" t="s">
         <v>147</v>
@@ -2236,7 +2236,7 @@
         <v>17</v>
       </c>
       <c r="D50">
-        <v>0.3527671803835229</v>
+        <v>0.3450026049982353</v>
       </c>
       <c r="E50" t="s">
         <v>151</v>
@@ -2259,7 +2259,7 @@
         <v>12</v>
       </c>
       <c r="D51">
-        <v>0.37283407001563</v>
+        <v>0.3638762373741618</v>
       </c>
       <c r="E51" t="s">
         <v>155</v>
@@ -2282,7 +2282,7 @@
         <v>40</v>
       </c>
       <c r="D52">
-        <v>0.3744979075981916</v>
+        <v>0.3654728491958119</v>
       </c>
       <c r="E52" t="s">
         <v>157</v>
@@ -2305,7 +2305,7 @@
         <v>18</v>
       </c>
       <c r="D53">
-        <v>0.3771869380346549</v>
+        <v>0.3682459118334145</v>
       </c>
       <c r="E53" t="s">
         <v>161</v>
@@ -2328,7 +2328,7 @@
         <v>6</v>
       </c>
       <c r="D54">
-        <v>0.378766743416077</v>
+        <v>0.3699097494159762</v>
       </c>
       <c r="E54" t="s">
         <v>165</v>
@@ -2351,7 +2351,7 @@
         <v>6</v>
       </c>
       <c r="D55">
-        <v>0.378766743416077</v>
+        <v>0.3699097494159762</v>
       </c>
       <c r="E55" t="s">
         <v>169</v>
@@ -2368,7 +2368,7 @@
         <v>6</v>
       </c>
       <c r="D56">
-        <v>0.378766743416077</v>
+        <v>0.3699097494159762</v>
       </c>
       <c r="E56" t="s">
         <v>171</v>
@@ -2385,7 +2385,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>0.4232197778188602</v>
+        <v>0.4157745247979026</v>
       </c>
       <c r="E57" t="s">
         <v>171</v>
@@ -2402,7 +2402,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>0.4232197778188602</v>
+        <v>0.4157745247979026</v>
       </c>
       <c r="E58" t="s">
         <v>56</v>
@@ -2425,7 +2425,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>0.4232197778188602</v>
+        <v>0.4157745247979026</v>
       </c>
       <c r="E59" t="s">
         <v>171</v>
@@ -2442,7 +2442,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>0.4232197778188602</v>
+        <v>0.4157745247979026</v>
       </c>
       <c r="E60" t="s">
         <v>103</v>
@@ -2465,7 +2465,7 @@
         <v>14</v>
       </c>
       <c r="D61">
-        <v>0.4370010588057344</v>
+        <v>0.4280936454849498</v>
       </c>
       <c r="E61" t="s">
         <v>177</v>
@@ -2488,7 +2488,7 @@
         <v>14</v>
       </c>
       <c r="D62">
-        <v>0.4370010588057344</v>
+        <v>0.4280936454849498</v>
       </c>
       <c r="E62" t="s">
         <v>179</v>
@@ -2511,7 +2511,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>0.4591687534663283</v>
+        <v>0.4527654997395002</v>
       </c>
       <c r="E63" t="s">
         <v>103</v>
@@ -2534,7 +2534,7 @@
         <v>9</v>
       </c>
       <c r="D64">
-        <v>0.4904287322902136</v>
+        <v>0.4839078334817902</v>
       </c>
       <c r="E64" t="s">
         <v>103</v>
@@ -2557,7 +2557,7 @@
         <v>9</v>
       </c>
       <c r="D65">
-        <v>0.4904287322902136</v>
+        <v>0.4839078334817902</v>
       </c>
       <c r="E65" t="s">
         <v>171</v>
@@ -2574,7 +2574,7 @@
         <v>9</v>
       </c>
       <c r="D66">
-        <v>0.4904287322902136</v>
+        <v>0.4839078334817902</v>
       </c>
       <c r="E66" t="s">
         <v>103</v>
@@ -2597,7 +2597,7 @@
         <v>29</v>
       </c>
       <c r="D67">
-        <v>0.4921766020739147</v>
+        <v>0.4856220903850356</v>
       </c>
       <c r="E67" t="s">
         <v>185</v>
@@ -2620,7 +2620,7 @@
         <v>120</v>
       </c>
       <c r="D68">
-        <v>0.5053864640930404</v>
+        <v>0.4998739516982908</v>
       </c>
       <c r="E68" t="s">
         <v>189</v>
@@ -2643,7 +2643,7 @@
         <v>10</v>
       </c>
       <c r="D69">
-        <v>0.5138569099678997</v>
+        <v>0.5098065578729769</v>
       </c>
       <c r="E69" t="s">
         <v>56</v>
@@ -2666,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="D70">
-        <v>0.5138569099678997</v>
+        <v>0.5098065578729769</v>
       </c>
       <c r="E70" t="s">
         <v>103</v>
@@ -2689,7 +2689,7 @@
         <v>10</v>
       </c>
       <c r="D71">
-        <v>0.5138569099678997</v>
+        <v>0.5098065578729769</v>
       </c>
       <c r="E71" t="s">
         <v>195</v>
@@ -2706,7 +2706,7 @@
         <v>10</v>
       </c>
       <c r="D72">
-        <v>0.5138569099678997</v>
+        <v>0.5098065578729769</v>
       </c>
       <c r="E72" t="s">
         <v>197</v>
@@ -2723,7 +2723,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.5169156820893767</v>
+        <v>0.513167845918556</v>
       </c>
       <c r="E73" t="s">
         <v>199</v>
@@ -2746,7 +2746,7 @@
         <v>11</v>
       </c>
       <c r="D74">
-        <v>0.5308986403589856</v>
+        <v>0.5272180299490765</v>
       </c>
       <c r="E74" t="s">
         <v>52</v>
@@ -2769,7 +2769,7 @@
         <v>13</v>
       </c>
       <c r="D75">
-        <v>0.5598561368716493</v>
+        <v>0.5564612359456144</v>
       </c>
       <c r="E75" t="s">
         <v>171</v>
@@ -2786,7 +2786,7 @@
         <v>14</v>
       </c>
       <c r="D76">
-        <v>0.5715870321507202</v>
+        <v>0.5693013562797264</v>
       </c>
       <c r="E76" t="s">
         <v>205</v>
@@ -2803,7 +2803,7 @@
         <v>51</v>
       </c>
       <c r="D77">
-        <v>0.5793852204164636</v>
+        <v>0.5769314801431908</v>
       </c>
       <c r="E77" t="s">
         <v>207</v>
@@ -2826,7 +2826,7 @@
         <v>35</v>
       </c>
       <c r="D78">
-        <v>0.5951496613502294</v>
+        <v>0.5927799532780962</v>
       </c>
       <c r="E78" t="s">
         <v>209</v>
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2863,7 +2863,7 @@
         <v>2</v>
       </c>
       <c r="D80">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2877,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="D81">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2891,7 +2891,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2905,7 +2905,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2933,7 +2933,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2947,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2975,7 +2975,7 @@
         <v>3</v>
       </c>
       <c r="D88">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2989,7 +2989,7 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3003,7 +3003,7 @@
         <v>6</v>
       </c>
       <c r="D90">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3031,7 +3031,7 @@
         <v>11</v>
       </c>
       <c r="D92">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3045,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3073,7 +3073,7 @@
         <v>3</v>
       </c>
       <c r="D95">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3101,7 +3101,7 @@
         <v>15</v>
       </c>
       <c r="D97">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3185,7 +3185,7 @@
         <v>10</v>
       </c>
       <c r="D103">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3241,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3255,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3297,7 +3297,7 @@
         <v>3</v>
       </c>
       <c r="D111">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3325,7 +3325,7 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3353,7 +3353,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3395,7 +3395,7 @@
         <v>3</v>
       </c>
       <c r="D118">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3409,7 +3409,7 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3423,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0.6116199727735668</v>
+        <v>0.6097376514680426</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
+++ b/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="250">
   <si>
     <t>pathway</t>
   </si>
@@ -139,10 +139,10 @@
     <t>E2192,E2525,E2191</t>
   </si>
   <si>
-    <t>C00831,C00020/C00362,C00831</t>
-  </si>
-  <si>
-    <t>Pantetheine; (R)-Pantetheine$AMP/dGMP$Pantetheine; (R)-Pantetheine</t>
+    <t>,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP$</t>
   </si>
   <si>
     <t>Glycerophospholipid metabolism</t>
@@ -286,12 +286,6 @@
     <t>E1044,E2525,E1045</t>
   </si>
   <si>
-    <t>,C00020/C00362,</t>
-  </si>
-  <si>
-    <t>$AMP/dGMP$</t>
-  </si>
-  <si>
     <t>Phosphatidylinositol phosphate metabolism</t>
   </si>
   <si>
@@ -358,13 +352,13 @@
     <t>Sialic acid metabolism</t>
   </si>
   <si>
-    <t>E2558,E35,E2970</t>
-  </si>
-  <si>
-    <t>C00055,,</t>
-  </si>
-  <si>
-    <t>CMP$$</t>
+    <t>E35,E2558,E2970</t>
+  </si>
+  <si>
+    <t>,C00055,</t>
+  </si>
+  <si>
+    <t>$CMP$</t>
   </si>
   <si>
     <t>Leukotriene metabolism</t>
@@ -457,13 +451,13 @@
     <t>Aminosugars metabolism</t>
   </si>
   <si>
-    <t>E2558,E35</t>
-  </si>
-  <si>
-    <t>C00055,</t>
-  </si>
-  <si>
-    <t>CMP$</t>
+    <t>E35,E2558</t>
+  </si>
+  <si>
+    <t>,C00055</t>
+  </si>
+  <si>
+    <t>$CMP</t>
   </si>
   <si>
     <t>Ubiquinone Biosynthesis</t>
@@ -1138,7 +1132,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.0111594763113225</v>
+        <v>0.01206702408362885</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1161,7 +1155,7 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>0.01447034503621788</v>
+        <v>0.01578124737399371</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1184,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>0.01805011680475958</v>
+        <v>0.01957950286549806</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1207,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>0.03191542999277323</v>
+        <v>0.0334952353741954</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1230,7 +1224,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>0.03329355809146065</v>
+        <v>0.03483975059242702</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1253,7 +1247,7 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>0.03499100855447808</v>
+        <v>0.03641955597384918</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1276,7 +1270,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>0.04441942152232736</v>
+        <v>0.04668829095309322</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1299,7 +1293,7 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>0.04443622796255525</v>
+        <v>0.04680593603468849</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1322,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>0.0496462244332028</v>
+        <v>0.05203273894556394</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1345,7 +1339,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>0.05452009209929245</v>
+        <v>0.05725954185643939</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1368,7 +1362,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>0.06354515050167224</v>
+        <v>0.06756188971613923</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1391,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0.0691080822171056</v>
+        <v>0.07408278852456261</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1414,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0.0691080822171056</v>
+        <v>0.07408278852456261</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1437,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>0.0691080822171056</v>
+        <v>0.07408278852456261</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
@@ -1460,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="D16">
-        <v>0.07149459672946673</v>
+        <v>0.07672139964034218</v>
       </c>
       <c r="E16" t="s">
         <v>61</v>
@@ -1483,7 +1477,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.09625048318515655</v>
+        <v>0.1025024789499336</v>
       </c>
       <c r="E17" t="s">
         <v>65</v>
@@ -1506,7 +1500,7 @@
         <v>62</v>
       </c>
       <c r="D18">
-        <v>0.09865380413774559</v>
+        <v>0.1046705097393321</v>
       </c>
       <c r="E18" t="s">
         <v>69</v>
@@ -1529,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="D19">
-        <v>0.101477286096032</v>
+        <v>0.1068049276482748</v>
       </c>
       <c r="E19" t="s">
         <v>73</v>
@@ -1552,7 +1546,7 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>0.101477286096032</v>
+        <v>0.1068049276482748</v>
       </c>
       <c r="E20" t="s">
         <v>77</v>
@@ -1575,7 +1569,7 @@
         <v>152</v>
       </c>
       <c r="D21">
-        <v>0.1101326028133981</v>
+        <v>0.1155946958874641</v>
       </c>
       <c r="E21" t="s">
         <v>81</v>
@@ -1598,7 +1592,7 @@
         <v>14</v>
       </c>
       <c r="D22">
-        <v>0.1205189828742374</v>
+        <v>0.1258130115460245</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
@@ -1621,21 +1615,21 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>0.1267373657585587</v>
+        <v>0.1323171039142199</v>
       </c>
       <c r="E23" t="s">
         <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -1644,21 +1638,21 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>0.1342498445404279</v>
+        <v>0.1392581637283407</v>
       </c>
       <c r="E24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" t="s">
         <v>93</v>
-      </c>
-      <c r="F24" t="s">
-        <v>94</v>
-      </c>
-      <c r="G24" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -1667,10 +1661,10 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>0.1342498445404279</v>
+        <v>0.1392581637283407</v>
       </c>
       <c r="E25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F25" t="s">
         <v>78</v>
@@ -1681,7 +1675,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -1690,21 +1684,21 @@
         <v>24</v>
       </c>
       <c r="D26">
-        <v>0.1372918102216769</v>
+        <v>0.1419471941648039</v>
       </c>
       <c r="E26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" t="s">
         <v>99</v>
-      </c>
-      <c r="F26" t="s">
-        <v>100</v>
-      </c>
-      <c r="G26" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -1713,21 +1707,21 @@
         <v>2</v>
       </c>
       <c r="D27">
-        <v>0.1383674223962622</v>
+        <v>0.1431068385405287</v>
       </c>
       <c r="E27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" t="s">
         <v>103</v>
-      </c>
-      <c r="F27" t="s">
-        <v>104</v>
-      </c>
-      <c r="G27" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1736,21 +1730,21 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>0.1383674223962622</v>
+        <v>0.1431068385405287</v>
       </c>
       <c r="E28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" t="s">
         <v>103</v>
-      </c>
-      <c r="F28" t="s">
-        <v>104</v>
-      </c>
-      <c r="G28" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1759,15 +1753,15 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <v>0.1383674223962622</v>
+        <v>0.1431068385405287</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -1776,21 +1770,21 @@
         <v>2</v>
       </c>
       <c r="D30">
-        <v>0.1383674223962622</v>
+        <v>0.1431068385405287</v>
       </c>
       <c r="E30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" t="s">
         <v>103</v>
-      </c>
-      <c r="F30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G30" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B31">
         <v>3</v>
@@ -1799,7 +1793,7 @@
         <v>11</v>
       </c>
       <c r="D31">
-        <v>0.1497958017512311</v>
+        <v>0.1550226046621065</v>
       </c>
       <c r="E31" t="s">
         <v>40</v>
@@ -1813,7 +1807,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -1822,21 +1816,21 @@
         <v>11</v>
       </c>
       <c r="D32">
-        <v>0.1497958017512311</v>
+        <v>0.1550226046621065</v>
       </c>
       <c r="E32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="G32" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -1845,21 +1839,21 @@
         <v>12</v>
       </c>
       <c r="D33">
-        <v>0.1830221340817801</v>
+        <v>0.1889380010419993</v>
       </c>
       <c r="E33" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" t="s">
         <v>114</v>
-      </c>
-      <c r="F33" t="s">
-        <v>115</v>
-      </c>
-      <c r="G33" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B34">
         <v>9</v>
@@ -1868,21 +1862,21 @@
         <v>41</v>
       </c>
       <c r="D34">
-        <v>0.1891564847649619</v>
+        <v>0.1945345456378884</v>
       </c>
       <c r="E34" t="s">
+        <v>116</v>
+      </c>
+      <c r="F34" t="s">
+        <v>117</v>
+      </c>
+      <c r="G34" t="s">
         <v>118</v>
-      </c>
-      <c r="F34" t="s">
-        <v>119</v>
-      </c>
-      <c r="G34" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B35">
         <v>4</v>
@@ -1891,21 +1885,21 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0.1917950958807415</v>
+        <v>0.1970555116720727</v>
       </c>
       <c r="E35" t="s">
+        <v>120</v>
+      </c>
+      <c r="F35" t="s">
+        <v>121</v>
+      </c>
+      <c r="G35" t="s">
         <v>122</v>
-      </c>
-      <c r="F35" t="s">
-        <v>123</v>
-      </c>
-      <c r="G35" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1914,21 +1908,21 @@
         <v>17</v>
       </c>
       <c r="D36">
-        <v>0.1917950958807415</v>
+        <v>0.1970555116720727</v>
       </c>
       <c r="E36" t="s">
+        <v>124</v>
+      </c>
+      <c r="F36" t="s">
+        <v>125</v>
+      </c>
+      <c r="G36" t="s">
         <v>126</v>
-      </c>
-      <c r="F36" t="s">
-        <v>127</v>
-      </c>
-      <c r="G36" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1937,7 +1931,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>0.2094082452395758</v>
+        <v>0.2162316599721013</v>
       </c>
       <c r="E37" t="s">
         <v>56</v>
@@ -1951,7 +1945,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -1960,7 +1954,7 @@
         <v>3</v>
       </c>
       <c r="D38">
-        <v>0.2094082452395758</v>
+        <v>0.2162316599721013</v>
       </c>
       <c r="E38" t="s">
         <v>56</v>
@@ -1974,7 +1968,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -1983,7 +1977,7 @@
         <v>3</v>
       </c>
       <c r="D39">
-        <v>0.2094082452395758</v>
+        <v>0.2162316599721013</v>
       </c>
       <c r="E39" t="s">
         <v>56</v>
@@ -1997,7 +1991,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -2006,10 +2000,10 @@
         <v>19</v>
       </c>
       <c r="D40">
-        <v>0.2501302499117662</v>
+        <v>0.2571049226063428</v>
       </c>
       <c r="E40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F40" t="s">
         <v>66</v>
@@ -2020,7 +2014,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -2029,10 +2023,10 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>0.2611888875817213</v>
+        <v>0.2671887867430799</v>
       </c>
       <c r="E41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F41" t="s">
         <v>78</v>
@@ -2043,7 +2037,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -2052,21 +2046,21 @@
         <v>4</v>
       </c>
       <c r="D42">
-        <v>0.2799616813162804</v>
+        <v>0.2873229021360986</v>
       </c>
       <c r="E42" t="s">
+        <v>101</v>
+      </c>
+      <c r="F42" t="s">
+        <v>102</v>
+      </c>
+      <c r="G42" t="s">
         <v>103</v>
-      </c>
-      <c r="F42" t="s">
-        <v>104</v>
-      </c>
-      <c r="G42" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -2075,21 +2069,21 @@
         <v>4</v>
       </c>
       <c r="D43">
-        <v>0.2799616813162804</v>
+        <v>0.2873229021360986</v>
       </c>
       <c r="E43" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" t="s">
+        <v>102</v>
+      </c>
+      <c r="G43" t="s">
         <v>103</v>
-      </c>
-      <c r="F43" t="s">
-        <v>104</v>
-      </c>
-      <c r="G43" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B44">
         <v>5</v>
@@ -2098,21 +2092,21 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>0.3255239407741046</v>
+        <v>0.3343473218937497</v>
       </c>
       <c r="E44" t="s">
+        <v>137</v>
+      </c>
+      <c r="F44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" t="s">
         <v>139</v>
-      </c>
-      <c r="F44" t="s">
-        <v>140</v>
-      </c>
-      <c r="G44" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -2121,7 +2115,7 @@
         <v>5</v>
       </c>
       <c r="D45">
-        <v>0.3292717769449253</v>
+        <v>0.3377422228197846</v>
       </c>
       <c r="E45" t="s">
         <v>56</v>
@@ -2135,7 +2129,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -2144,21 +2138,21 @@
         <v>5</v>
       </c>
       <c r="D46">
-        <v>0.3292717769449253</v>
+        <v>0.3377422228197846</v>
       </c>
       <c r="E46" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" t="s">
+        <v>102</v>
+      </c>
+      <c r="G46" t="s">
         <v>103</v>
-      </c>
-      <c r="F46" t="s">
-        <v>104</v>
-      </c>
-      <c r="G46" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -2167,21 +2161,21 @@
         <v>5</v>
       </c>
       <c r="D47">
-        <v>0.3292717769449253</v>
+        <v>0.3377422228197846</v>
       </c>
       <c r="E47" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" t="s">
+        <v>102</v>
+      </c>
+      <c r="G47" t="s">
         <v>103</v>
-      </c>
-      <c r="F47" t="s">
-        <v>104</v>
-      </c>
-      <c r="G47" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -2190,21 +2184,21 @@
         <v>5</v>
       </c>
       <c r="D48">
-        <v>0.3292717769449253</v>
+        <v>0.3377422228197846</v>
       </c>
       <c r="E48" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" t="s">
+        <v>102</v>
+      </c>
+      <c r="G48" t="s">
         <v>103</v>
-      </c>
-      <c r="F48" t="s">
-        <v>104</v>
-      </c>
-      <c r="G48" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B49">
         <v>2</v>
@@ -2213,21 +2207,21 @@
         <v>11</v>
       </c>
       <c r="D49">
-        <v>0.3345321927362565</v>
+        <v>0.3430362514915716</v>
       </c>
       <c r="E49" t="s">
+        <v>145</v>
+      </c>
+      <c r="F49" t="s">
+        <v>146</v>
+      </c>
+      <c r="G49" t="s">
         <v>147</v>
-      </c>
-      <c r="F49" t="s">
-        <v>148</v>
-      </c>
-      <c r="G49" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B50">
         <v>3</v>
@@ -2236,21 +2230,21 @@
         <v>17</v>
       </c>
       <c r="D50">
-        <v>0.3450026049982353</v>
+        <v>0.3525823095410161</v>
       </c>
       <c r="E50" t="s">
+        <v>149</v>
+      </c>
+      <c r="F50" t="s">
+        <v>150</v>
+      </c>
+      <c r="G50" t="s">
         <v>151</v>
-      </c>
-      <c r="F50" t="s">
-        <v>152</v>
-      </c>
-      <c r="G50" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -2259,10 +2253,10 @@
         <v>12</v>
       </c>
       <c r="D51">
-        <v>0.3638762373741618</v>
+        <v>0.3735735533856574</v>
       </c>
       <c r="E51" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F51" t="s">
         <v>78</v>
@@ -2273,7 +2267,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B52">
         <v>7</v>
@@ -2282,21 +2276,21 @@
         <v>40</v>
       </c>
       <c r="D52">
-        <v>0.3654728491958119</v>
+        <v>0.3758424228164233</v>
       </c>
       <c r="E52" t="s">
+        <v>155</v>
+      </c>
+      <c r="F52" t="s">
+        <v>156</v>
+      </c>
+      <c r="G52" t="s">
         <v>157</v>
-      </c>
-      <c r="F52" t="s">
-        <v>158</v>
-      </c>
-      <c r="G52" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B53">
         <v>3</v>
@@ -2305,21 +2299,21 @@
         <v>18</v>
       </c>
       <c r="D53">
-        <v>0.3682459118334145</v>
+        <v>0.3783633888506076</v>
       </c>
       <c r="E53" t="s">
+        <v>159</v>
+      </c>
+      <c r="F53" t="s">
+        <v>160</v>
+      </c>
+      <c r="G53" t="s">
         <v>161</v>
-      </c>
-      <c r="F53" t="s">
-        <v>162</v>
-      </c>
-      <c r="G53" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -2328,21 +2322,21 @@
         <v>6</v>
       </c>
       <c r="D54">
-        <v>0.3699097494159762</v>
+        <v>0.3799768071124855</v>
       </c>
       <c r="E54" t="s">
+        <v>163</v>
+      </c>
+      <c r="F54" t="s">
+        <v>164</v>
+      </c>
+      <c r="G54" t="s">
         <v>165</v>
-      </c>
-      <c r="F54" t="s">
-        <v>166</v>
-      </c>
-      <c r="G54" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -2351,15 +2345,15 @@
         <v>6</v>
       </c>
       <c r="D55">
-        <v>0.3699097494159762</v>
+        <v>0.3799768071124855</v>
       </c>
       <c r="E55" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -2368,15 +2362,15 @@
         <v>6</v>
       </c>
       <c r="D56">
-        <v>0.3699097494159762</v>
+        <v>0.3799768071124855</v>
       </c>
       <c r="E56" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -2385,15 +2379,15 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>0.4157745247979026</v>
+        <v>0.4235054873027344</v>
       </c>
       <c r="E57" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -2402,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>0.4157745247979026</v>
+        <v>0.4235054873027344</v>
       </c>
       <c r="E58" t="s">
         <v>56</v>
@@ -2416,7 +2410,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -2425,15 +2419,15 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>0.4157745247979026</v>
+        <v>0.4235054873027344</v>
       </c>
       <c r="E59" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -2442,21 +2436,21 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>0.4157745247979026</v>
+        <v>0.4235054873027344</v>
       </c>
       <c r="E60" t="s">
+        <v>101</v>
+      </c>
+      <c r="F60" t="s">
+        <v>102</v>
+      </c>
+      <c r="G60" t="s">
         <v>103</v>
-      </c>
-      <c r="F60" t="s">
-        <v>104</v>
-      </c>
-      <c r="G60" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -2465,10 +2459,10 @@
         <v>14</v>
       </c>
       <c r="D61">
-        <v>0.4280936454849498</v>
+        <v>0.4363624140770743</v>
       </c>
       <c r="E61" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F61" t="s">
         <v>74</v>
@@ -2479,7 +2473,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -2488,10 +2482,10 @@
         <v>14</v>
       </c>
       <c r="D62">
-        <v>0.4280936454849498</v>
+        <v>0.4363624140770743</v>
       </c>
       <c r="E62" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F62" t="s">
         <v>74</v>
@@ -2502,7 +2496,7 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -2511,21 +2505,21 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>0.4527654997395002</v>
+        <v>0.460496462244332</v>
       </c>
       <c r="E63" t="s">
+        <v>101</v>
+      </c>
+      <c r="F63" t="s">
+        <v>102</v>
+      </c>
+      <c r="G63" t="s">
         <v>103</v>
-      </c>
-      <c r="F63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G63" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -2534,21 +2528,21 @@
         <v>9</v>
       </c>
       <c r="D64">
-        <v>0.4839078334817902</v>
+        <v>0.4904791516108973</v>
       </c>
       <c r="E64" t="s">
+        <v>101</v>
+      </c>
+      <c r="F64" t="s">
+        <v>102</v>
+      </c>
+      <c r="G64" t="s">
         <v>103</v>
-      </c>
-      <c r="F64" t="s">
-        <v>104</v>
-      </c>
-      <c r="G64" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -2557,15 +2551,15 @@
         <v>9</v>
       </c>
       <c r="D65">
-        <v>0.4839078334817902</v>
+        <v>0.4904791516108973</v>
       </c>
       <c r="E65" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -2574,21 +2568,21 @@
         <v>9</v>
       </c>
       <c r="D66">
-        <v>0.4839078334817902</v>
+        <v>0.4904791516108973</v>
       </c>
       <c r="E66" t="s">
+        <v>101</v>
+      </c>
+      <c r="F66" t="s">
+        <v>102</v>
+      </c>
+      <c r="G66" t="s">
         <v>103</v>
-      </c>
-      <c r="F66" t="s">
-        <v>104</v>
-      </c>
-      <c r="G66" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B67">
         <v>4</v>
@@ -2597,21 +2591,21 @@
         <v>29</v>
       </c>
       <c r="D67">
-        <v>0.4856220903850356</v>
+        <v>0.4920589569923194</v>
       </c>
       <c r="E67" t="s">
+        <v>183</v>
+      </c>
+      <c r="F67" t="s">
+        <v>184</v>
+      </c>
+      <c r="G67" t="s">
         <v>185</v>
-      </c>
-      <c r="F67" t="s">
-        <v>186</v>
-      </c>
-      <c r="G67" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B68">
         <v>20</v>
@@ -2620,21 +2614,21 @@
         <v>120</v>
       </c>
       <c r="D68">
-        <v>0.4998739516982908</v>
+        <v>0.5068486243928674</v>
       </c>
       <c r="E68" t="s">
+        <v>187</v>
+      </c>
+      <c r="F68" t="s">
+        <v>188</v>
+      </c>
+      <c r="G68" t="s">
         <v>189</v>
-      </c>
-      <c r="F68" t="s">
-        <v>190</v>
-      </c>
-      <c r="G68" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -2643,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="D69">
-        <v>0.5098065578729769</v>
+        <v>0.5152854573872708</v>
       </c>
       <c r="E69" t="s">
         <v>56</v>
@@ -2657,7 +2651,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -2666,21 +2660,21 @@
         <v>10</v>
       </c>
       <c r="D70">
-        <v>0.5098065578729769</v>
+        <v>0.5152854573872708</v>
       </c>
       <c r="E70" t="s">
+        <v>101</v>
+      </c>
+      <c r="F70" t="s">
+        <v>102</v>
+      </c>
+      <c r="G70" t="s">
         <v>103</v>
-      </c>
-      <c r="F70" t="s">
-        <v>104</v>
-      </c>
-      <c r="G70" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -2689,15 +2683,15 @@
         <v>10</v>
       </c>
       <c r="D71">
-        <v>0.5098065578729769</v>
+        <v>0.5152854573872708</v>
       </c>
       <c r="E71" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -2706,15 +2700,15 @@
         <v>10</v>
       </c>
       <c r="D72">
-        <v>0.5098065578729769</v>
+        <v>0.5152854573872708</v>
       </c>
       <c r="E72" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B73">
         <v>6</v>
@@ -2723,21 +2717,21 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.513167845918556</v>
+        <v>0.5184954874707988</v>
       </c>
       <c r="E73" t="s">
+        <v>197</v>
+      </c>
+      <c r="F73" t="s">
+        <v>198</v>
+      </c>
+      <c r="G73" t="s">
         <v>199</v>
-      </c>
-      <c r="F73" t="s">
-        <v>200</v>
-      </c>
-      <c r="G73" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -2746,7 +2740,7 @@
         <v>11</v>
       </c>
       <c r="D74">
-        <v>0.5272180299490765</v>
+        <v>0.5332851548713466</v>
       </c>
       <c r="E74" t="s">
         <v>52</v>
@@ -2760,7 +2754,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -2769,15 +2763,15 @@
         <v>13</v>
       </c>
       <c r="D75">
-        <v>0.5564612359456144</v>
+        <v>0.5618897161392246</v>
       </c>
       <c r="E75" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -2786,15 +2780,15 @@
         <v>14</v>
       </c>
       <c r="D76">
-        <v>0.5693013562797264</v>
+        <v>0.5743096754676392</v>
       </c>
       <c r="E76" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B77">
         <v>6</v>
@@ -2803,21 +2797,21 @@
         <v>51</v>
       </c>
       <c r="D77">
-        <v>0.5769314801431908</v>
+        <v>0.5821414766138384</v>
       </c>
       <c r="E77" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F77" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G77" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B78">
         <v>3</v>
@@ -2826,21 +2820,21 @@
         <v>35</v>
       </c>
       <c r="D78">
-        <v>0.5927799532780962</v>
+        <v>0.5978218853464647</v>
       </c>
       <c r="E78" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F78" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="G78" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2849,12 +2843,12 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2863,12 +2857,12 @@
         <v>2</v>
       </c>
       <c r="D80">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -2877,12 +2871,12 @@
         <v>1</v>
       </c>
       <c r="D81">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2891,12 +2885,12 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -2905,12 +2899,12 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2919,12 +2913,12 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2933,12 +2927,12 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2947,12 +2941,12 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2961,12 +2955,12 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -2975,12 +2969,12 @@
         <v>3</v>
       </c>
       <c r="D88">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -2989,12 +2983,12 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -3003,12 +2997,12 @@
         <v>6</v>
       </c>
       <c r="D90">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -3017,12 +3011,12 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -3031,12 +3025,12 @@
         <v>11</v>
       </c>
       <c r="D92">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -3045,12 +3039,12 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -3059,12 +3053,12 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -3073,12 +3067,12 @@
         <v>3</v>
       </c>
       <c r="D95">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -3087,12 +3081,12 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -3101,12 +3095,12 @@
         <v>15</v>
       </c>
       <c r="D97">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -3115,12 +3109,12 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -3129,12 +3123,12 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -3143,12 +3137,12 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3157,12 +3151,12 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3171,12 +3165,12 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3185,12 +3179,12 @@
         <v>10</v>
       </c>
       <c r="D103">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3199,12 +3193,12 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3213,12 +3207,12 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3227,12 +3221,12 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3241,12 +3235,12 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3255,12 +3249,12 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3269,12 +3263,12 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3283,12 +3277,12 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3297,12 +3291,12 @@
         <v>3</v>
       </c>
       <c r="D111">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3311,12 +3305,12 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3325,12 +3319,12 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3339,12 +3333,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3353,12 +3347,12 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3367,12 +3361,12 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3381,12 +3375,12 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3395,12 +3389,12 @@
         <v>3</v>
       </c>
       <c r="D118">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3409,12 +3403,12 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3423,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0.6097376514680426</v>
+        <v>0.6136031327204585</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
+++ b/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
@@ -64,13 +64,13 @@
     <t>Vitamin B2 (riboflavin) metabolism</t>
   </si>
   <si>
-    <t>E276,E1373,E3036,E2525</t>
-  </si>
-  <si>
-    <t>C01847,C00255,C00061,C00020/C00362</t>
-  </si>
-  <si>
-    <t>Reduced FMN; FMNH2$Riboflavin$FMN$AMP/dGMP</t>
+    <t>E276,E2525,E1373,E3036</t>
+  </si>
+  <si>
+    <t>C01847,C00020/C00362,C00255,C00061</t>
+  </si>
+  <si>
+    <t>Reduced FMN; FMNH2$AMP/dGMP$Riboflavin$FMN</t>
   </si>
   <si>
     <t>Omega-3 fatty acid metabolism</t>
@@ -1132,7 +1132,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.01206702408362885</v>
+        <v>0.0114956051158804</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1155,7 +1155,7 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>0.01578124737399371</v>
+        <v>0.01470563519940841</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1178,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="D4">
-        <v>0.01957950286549806</v>
+        <v>0.0187223744138754</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1201,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>0.0334952353741954</v>
+        <v>0.03307507436849801</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1224,7 +1224,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>0.03483975059242702</v>
+        <v>0.03457084754878069</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1247,7 +1247,7 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>0.03641955597384918</v>
+        <v>0.03621787869111444</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1270,7 +1270,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>0.04668829095309322</v>
+        <v>0.04566309809919161</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1293,7 +1293,7 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>0.04680593603468849</v>
+        <v>0.04574713030033109</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1316,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>0.05203273894556394</v>
+        <v>0.05099073965143443</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1339,7 +1339,7 @@
         <v>27</v>
       </c>
       <c r="D11">
-        <v>0.05725954185643939</v>
+        <v>0.05616712324162619</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1362,7 +1362,7 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>0.06756188971613923</v>
+        <v>0.06564595553015916</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1385,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0.07408278852456261</v>
+        <v>0.07231811230063361</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1408,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0.07408278852456261</v>
+        <v>0.07231811230063361</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1431,7 +1431,7 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>0.07408278852456261</v>
+        <v>0.07231811230063361</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
@@ -1454,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="D16">
-        <v>0.07672139964034218</v>
+        <v>0.07477185257390633</v>
       </c>
       <c r="E16" t="s">
         <v>61</v>
@@ -1477,7 +1477,7 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.1025024789499336</v>
+        <v>0.1006033512041814</v>
       </c>
       <c r="E17" t="s">
         <v>65</v>
@@ -1500,7 +1500,7 @@
         <v>62</v>
       </c>
       <c r="D18">
-        <v>0.1046705097393321</v>
+        <v>0.1029562528360868</v>
       </c>
       <c r="E18" t="s">
         <v>69</v>
@@ -1523,7 +1523,7 @@
         <v>5</v>
       </c>
       <c r="D19">
-        <v>0.1068049276482748</v>
+        <v>0.1053763802289037</v>
       </c>
       <c r="E19" t="s">
         <v>73</v>
@@ -1546,7 +1546,7 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>0.1068049276482748</v>
+        <v>0.1053763802289037</v>
       </c>
       <c r="E20" t="s">
         <v>77</v>
@@ -1569,7 +1569,7 @@
         <v>152</v>
       </c>
       <c r="D21">
-        <v>0.1155946958874641</v>
+        <v>0.1154266314851851</v>
       </c>
       <c r="E21" t="s">
         <v>81</v>
@@ -1592,7 +1592,7 @@
         <v>14</v>
       </c>
       <c r="D22">
-        <v>0.1258130115460245</v>
+        <v>0.1251743668173644</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
@@ -1615,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>0.1323171039142199</v>
+        <v>0.1313087175005462</v>
       </c>
       <c r="E23" t="s">
         <v>89</v>
@@ -1638,7 +1638,7 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>0.1392581637283407</v>
+        <v>0.1389556478042386</v>
       </c>
       <c r="E24" t="s">
         <v>91</v>
@@ -1661,7 +1661,7 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>0.1392581637283407</v>
+        <v>0.1389556478042386</v>
       </c>
       <c r="E25" t="s">
         <v>95</v>
@@ -1684,7 +1684,7 @@
         <v>24</v>
       </c>
       <c r="D26">
-        <v>0.1419471941648039</v>
+        <v>0.1419303877245761</v>
       </c>
       <c r="E26" t="s">
         <v>97</v>
@@ -1707,7 +1707,7 @@
         <v>2</v>
       </c>
       <c r="D27">
-        <v>0.1431068385405287</v>
+        <v>0.143224483622124</v>
       </c>
       <c r="E27" t="s">
         <v>101</v>
@@ -1730,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>0.1431068385405287</v>
+        <v>0.143224483622124</v>
       </c>
       <c r="E28" t="s">
         <v>101</v>
@@ -1753,7 +1753,7 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <v>0.1431068385405287</v>
+        <v>0.143224483622124</v>
       </c>
       <c r="E29" t="s">
         <v>106</v>
@@ -1770,7 +1770,7 @@
         <v>2</v>
       </c>
       <c r="D30">
-        <v>0.1431068385405287</v>
+        <v>0.143224483622124</v>
       </c>
       <c r="E30" t="s">
         <v>101</v>
@@ -1793,7 +1793,7 @@
         <v>11</v>
       </c>
       <c r="D31">
-        <v>0.1550226046621065</v>
+        <v>0.1556444429505386</v>
       </c>
       <c r="E31" t="s">
         <v>40</v>
@@ -1816,7 +1816,7 @@
         <v>11</v>
       </c>
       <c r="D32">
-        <v>0.1550226046621065</v>
+        <v>0.1556444429505386</v>
       </c>
       <c r="E32" t="s">
         <v>110</v>
@@ -1839,7 +1839,7 @@
         <v>12</v>
       </c>
       <c r="D33">
-        <v>0.1889380010419993</v>
+        <v>0.1899968067763567</v>
       </c>
       <c r="E33" t="s">
         <v>112</v>
@@ -1862,7 +1862,7 @@
         <v>41</v>
       </c>
       <c r="D34">
-        <v>0.1945345456378884</v>
+        <v>0.1956269642527016</v>
       </c>
       <c r="E34" t="s">
         <v>116</v>
@@ -1885,7 +1885,7 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0.1970555116720727</v>
+        <v>0.1982319624880254</v>
       </c>
       <c r="E35" t="s">
         <v>120</v>
@@ -1908,7 +1908,7 @@
         <v>17</v>
       </c>
       <c r="D36">
-        <v>0.1970555116720727</v>
+        <v>0.1982319624880254</v>
       </c>
       <c r="E36" t="s">
         <v>124</v>
@@ -1931,7 +1931,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>0.2162316599721013</v>
+        <v>0.2163493050536966</v>
       </c>
       <c r="E37" t="s">
         <v>56</v>
@@ -1954,7 +1954,7 @@
         <v>3</v>
       </c>
       <c r="D38">
-        <v>0.2162316599721013</v>
+        <v>0.2163493050536966</v>
       </c>
       <c r="E38" t="s">
         <v>56</v>
@@ -1977,7 +1977,7 @@
         <v>3</v>
       </c>
       <c r="D39">
-        <v>0.2162316599721013</v>
+        <v>0.2163493050536966</v>
       </c>
       <c r="E39" t="s">
         <v>56</v>
@@ -2000,7 +2000,7 @@
         <v>19</v>
       </c>
       <c r="D40">
-        <v>0.2571049226063428</v>
+        <v>0.2578107930959144</v>
       </c>
       <c r="E40" t="s">
         <v>131</v>
@@ -2023,7 +2023,7 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>0.2671887867430799</v>
+        <v>0.2676929799499168</v>
       </c>
       <c r="E41" t="s">
         <v>133</v>
@@ -2046,7 +2046,7 @@
         <v>4</v>
       </c>
       <c r="D42">
-        <v>0.2873229021360986</v>
+        <v>0.2885497722727349</v>
       </c>
       <c r="E42" t="s">
         <v>101</v>
@@ -2069,7 +2069,7 @@
         <v>4</v>
       </c>
       <c r="D43">
-        <v>0.2873229021360986</v>
+        <v>0.2885497722727349</v>
       </c>
       <c r="E43" t="s">
         <v>101</v>
@@ -2092,7 +2092,7 @@
         <v>27</v>
       </c>
       <c r="D44">
-        <v>0.3343473218937497</v>
+        <v>0.3359943530360834</v>
       </c>
       <c r="E44" t="s">
         <v>137</v>
@@ -2115,7 +2115,7 @@
         <v>5</v>
       </c>
       <c r="D45">
-        <v>0.3377422228197846</v>
+        <v>0.3395573183643972</v>
       </c>
       <c r="E45" t="s">
         <v>56</v>
@@ -2138,7 +2138,7 @@
         <v>5</v>
       </c>
       <c r="D46">
-        <v>0.3377422228197846</v>
+        <v>0.3395573183643972</v>
       </c>
       <c r="E46" t="s">
         <v>101</v>
@@ -2161,7 +2161,7 @@
         <v>5</v>
       </c>
       <c r="D47">
-        <v>0.3377422228197846</v>
+        <v>0.3395573183643972</v>
       </c>
       <c r="E47" t="s">
         <v>101</v>
@@ -2184,7 +2184,7 @@
         <v>5</v>
       </c>
       <c r="D48">
-        <v>0.3377422228197846</v>
+        <v>0.3395573183643972</v>
       </c>
       <c r="E48" t="s">
         <v>101</v>
@@ -2207,7 +2207,7 @@
         <v>11</v>
       </c>
       <c r="D49">
-        <v>0.3430362514915716</v>
+        <v>0.3451538629602864</v>
       </c>
       <c r="E49" t="s">
         <v>145</v>
@@ -2230,7 +2230,7 @@
         <v>17</v>
       </c>
       <c r="D50">
-        <v>0.3525823095410161</v>
+        <v>0.3557587267440883</v>
       </c>
       <c r="E50" t="s">
         <v>149</v>
@@ -2253,7 +2253,7 @@
         <v>12</v>
       </c>
       <c r="D51">
-        <v>0.3735735533856574</v>
+        <v>0.3759768743382464</v>
       </c>
       <c r="E51" t="s">
         <v>153</v>
@@ -2276,7 +2276,7 @@
         <v>40</v>
       </c>
       <c r="D52">
-        <v>0.3758424228164233</v>
+        <v>0.3780608729265054</v>
       </c>
       <c r="E52" t="s">
         <v>155</v>
@@ -2299,7 +2299,7 @@
         <v>18</v>
       </c>
       <c r="D53">
-        <v>0.3783633888506076</v>
+        <v>0.3804641938790945</v>
       </c>
       <c r="E53" t="s">
         <v>159</v>
@@ -2322,7 +2322,7 @@
         <v>6</v>
       </c>
       <c r="D54">
-        <v>0.3799768071124855</v>
+        <v>0.381657451135275</v>
       </c>
       <c r="E54" t="s">
         <v>163</v>
@@ -2345,7 +2345,7 @@
         <v>6</v>
       </c>
       <c r="D55">
-        <v>0.3799768071124855</v>
+        <v>0.381657451135275</v>
       </c>
       <c r="E55" t="s">
         <v>167</v>
@@ -2362,7 +2362,7 @@
         <v>6</v>
       </c>
       <c r="D56">
-        <v>0.3799768071124855</v>
+        <v>0.381657451135275</v>
       </c>
       <c r="E56" t="s">
         <v>169</v>
@@ -2379,7 +2379,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>0.4235054873027344</v>
+        <v>0.4250516798037008</v>
       </c>
       <c r="E57" t="s">
         <v>169</v>
@@ -2396,7 +2396,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>0.4235054873027344</v>
+        <v>0.4250516798037008</v>
       </c>
       <c r="E58" t="s">
         <v>56</v>
@@ -2419,7 +2419,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>0.4235054873027344</v>
+        <v>0.4250516798037008</v>
       </c>
       <c r="E59" t="s">
         <v>169</v>
@@ -2436,7 +2436,7 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>0.4235054873027344</v>
+        <v>0.4250516798037008</v>
       </c>
       <c r="E60" t="s">
         <v>101</v>
@@ -2459,7 +2459,7 @@
         <v>14</v>
       </c>
       <c r="D61">
-        <v>0.4363624140770743</v>
+        <v>0.4383119611435102</v>
       </c>
       <c r="E61" t="s">
         <v>175</v>
@@ -2482,7 +2482,7 @@
         <v>14</v>
       </c>
       <c r="D62">
-        <v>0.4363624140770743</v>
+        <v>0.4383119611435102</v>
       </c>
       <c r="E62" t="s">
         <v>177</v>
@@ -2505,7 +2505,7 @@
         <v>8</v>
       </c>
       <c r="D63">
-        <v>0.460496462244332</v>
+        <v>0.4624628157509958</v>
       </c>
       <c r="E63" t="s">
         <v>101</v>
@@ -2528,7 +2528,7 @@
         <v>9</v>
       </c>
       <c r="D64">
-        <v>0.4904791516108973</v>
+        <v>0.4921261827532311</v>
       </c>
       <c r="E64" t="s">
         <v>101</v>
@@ -2551,7 +2551,7 @@
         <v>9</v>
       </c>
       <c r="D65">
-        <v>0.4904791516108973</v>
+        <v>0.4921261827532311</v>
       </c>
       <c r="E65" t="s">
         <v>169</v>
@@ -2568,7 +2568,7 @@
         <v>9</v>
       </c>
       <c r="D66">
-        <v>0.4904791516108973</v>
+        <v>0.4921261827532311</v>
       </c>
       <c r="E66" t="s">
         <v>101</v>
@@ -2591,7 +2591,7 @@
         <v>29</v>
       </c>
       <c r="D67">
-        <v>0.4920589569923194</v>
+        <v>0.4939916976185274</v>
       </c>
       <c r="E67" t="s">
         <v>183</v>
@@ -2614,7 +2614,7 @@
         <v>120</v>
       </c>
       <c r="D68">
-        <v>0.5068486243928674</v>
+        <v>0.5082939782524664</v>
       </c>
       <c r="E68" t="s">
         <v>187</v>
@@ -2637,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="D69">
-        <v>0.5152854573872708</v>
+        <v>0.5164787146434514</v>
       </c>
       <c r="E69" t="s">
         <v>56</v>
@@ -2660,7 +2660,7 @@
         <v>10</v>
       </c>
       <c r="D70">
-        <v>0.5152854573872708</v>
+        <v>0.5164787146434514</v>
       </c>
       <c r="E70" t="s">
         <v>101</v>
@@ -2683,7 +2683,7 @@
         <v>10</v>
       </c>
       <c r="D71">
-        <v>0.5152854573872708</v>
+        <v>0.5164787146434514</v>
       </c>
       <c r="E71" t="s">
         <v>193</v>
@@ -2700,7 +2700,7 @@
         <v>10</v>
       </c>
       <c r="D72">
-        <v>0.5152854573872708</v>
+        <v>0.5164787146434514</v>
       </c>
       <c r="E72" t="s">
         <v>195</v>
@@ -2717,7 +2717,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.5184954874707988</v>
+        <v>0.5193190030419657</v>
       </c>
       <c r="E73" t="s">
         <v>197</v>
@@ -2740,7 +2740,7 @@
         <v>11</v>
       </c>
       <c r="D74">
-        <v>0.5332851548713466</v>
+        <v>0.5333859935127141</v>
       </c>
       <c r="E74" t="s">
         <v>52</v>
@@ -2763,7 +2763,7 @@
         <v>13</v>
       </c>
       <c r="D75">
-        <v>0.5618897161392246</v>
+        <v>0.5621586191828709</v>
       </c>
       <c r="E75" t="s">
         <v>169</v>
@@ -2780,7 +2780,7 @@
         <v>14</v>
       </c>
       <c r="D76">
-        <v>0.5743096754676392</v>
+        <v>0.5751668039192619</v>
       </c>
       <c r="E76" t="s">
         <v>203</v>
@@ -2797,7 +2797,7 @@
         <v>51</v>
       </c>
       <c r="D77">
-        <v>0.5821414766138384</v>
+        <v>0.5826624762609032</v>
       </c>
       <c r="E77" t="s">
         <v>205</v>
@@ -2820,7 +2820,7 @@
         <v>35</v>
       </c>
       <c r="D78">
-        <v>0.5978218853464647</v>
+        <v>0.5977378531453252</v>
       </c>
       <c r="E78" t="s">
         <v>207</v>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2857,7 +2857,7 @@
         <v>2</v>
       </c>
       <c r="D80">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2871,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="D81">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2885,7 +2885,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2899,7 +2899,7 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2913,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2927,7 +2927,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2969,7 +2969,7 @@
         <v>3</v>
       </c>
       <c r="D88">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2983,7 +2983,7 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2997,7 +2997,7 @@
         <v>6</v>
       </c>
       <c r="D90">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3025,7 +3025,7 @@
         <v>11</v>
       </c>
       <c r="D92">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3039,7 +3039,7 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3067,7 +3067,7 @@
         <v>3</v>
       </c>
       <c r="D95">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3081,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3095,7 +3095,7 @@
         <v>15</v>
       </c>
       <c r="D97">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3179,7 +3179,7 @@
         <v>10</v>
       </c>
       <c r="D103">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3235,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3249,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3291,7 +3291,7 @@
         <v>3</v>
       </c>
       <c r="D111">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3319,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3347,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3389,7 +3389,7 @@
         <v>3</v>
       </c>
       <c r="D118">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3403,7 +3403,7 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3417,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0.6136031327204585</v>
+        <v>0.6136535520411421</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
+++ b/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="277">
   <si>
     <t>pathway</t>
   </si>
@@ -52,13 +52,25 @@
     <t>Glycosphingolipid metabolism</t>
   </si>
   <si>
-    <t>E2345,E2558,E3164,E2383,E468,E2657</t>
-  </si>
-  <si>
-    <t>C00249,C00055,C02744,C00836,C00588/C05594,C12144</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)$CMP$Psychosine sulfate$Sphinganine$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$Phytosphingosine; 4-D-Hydroxysphinganine</t>
+    <t>E2345,E2558,E3164,E2383,E740,E2657</t>
+  </si>
+  <si>
+    <t>C00249,C00055,C02744,C00836,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C12144</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$CMP$Psychosine sulfate$Sphinganine$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$Phytosphingosine; 4-D-Hydroxysphinganine</t>
+  </si>
+  <si>
+    <t>Bile acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E2173,E2525,E3074,E3077,E1895,E3075,E2991,E2941</t>
+  </si>
+  <si>
+    <t>C05122/C15516,C00020/C00362,C05463/C05465,C05463/C05465,CE2202/C17335,C05463/C05465,C01921,C00695</t>
+  </si>
+  <si>
+    <t>taurocholic acid/Taurohyocholate; N-(3alpha,6alpha,7alpha-Trihydroxy-5beta-cholan-24-oyl)taurine$AMP/dGMP$Taurodeoxycholate/Taurochenodeoxycholate; Chenodeoxycholoyltaurine$Taurodeoxycholate/Taurochenodeoxycholate; Chenodeoxycholoyltaurine$23S,25,26-trihydroxyvitamin D3/$Taurodeoxycholate/Taurochenodeoxycholate; Chenodeoxycholoyltaurine$glycocholate$Cholate</t>
   </si>
   <si>
     <t>Vitamin B2 (riboflavin) metabolism</t>
@@ -73,6 +85,18 @@
     <t>Reduced FMN; FMNH2$AMP/dGMP$Riboflavin$FMN</t>
   </si>
   <si>
+    <t>Glycerophospholipid metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2383,E2558,E740,E2796,E1351,E256,E2985,E2513</t>
+  </si>
+  <si>
+    <t>C06426/C06427,C00836,C00055,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00021,C00670,C00219,C15646,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Sphinganine$CMP$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$S-Adenosyl-L-homocysteine$sn-Glycero-3-phosphocholine$arachidonic acid$1-(1-Alkenyl)-sn-glycero-3-phosphate$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
+  </si>
+  <si>
     <t>Omega-3 fatty acid metabolism</t>
   </si>
   <si>
@@ -85,6 +109,30 @@
     <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid$AMP/dGMP</t>
   </si>
   <si>
+    <t>Phosphatidylinositol phosphate metabolism</t>
+  </si>
+  <si>
+    <t>E740,E2345,E2558</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00249,C00055</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$Hexadecanoate (n-C16:0)$CMP</t>
+  </si>
+  <si>
+    <t>Linoleate metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2348,E113,E2350,E480,E2321,E492,E2084,E2639,E2085,E2640</t>
+  </si>
+  <si>
+    <t>C06426/C06427,C14762/C14826/C14825,CE2061,C14762/C14826/C14825,CE2006/CE6506,CE5526/CE5527/C14765,C04717/C14827,CE2306/CE2305/CE2304/CE2303,CE6504,CE2306/CE2305/CE2304/CE2303,CE6504</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$/$//13-OxoODE; 13-KODE; (9Z,11E)-13-Oxooctadeca-9,11-dienoic acid$(9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoic acid; (9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoate; 13(S)-HPODE; 13S-Hydroperoxy-9Z,11E-octadecadienoic acid/9(S)-HPODE; 9(S)-HPOD; (10E,12Z)-(9S)-9-Hydroperoxyoctadeca-10,12-dienoic acid$12-O-D-glucuronoside-13-hydroxyoctadec-9Z-enoate/12-hydroxy-13-O-D-glucuronoside-octadec-9Z-enoate/10-hydroxy-octadec-12Z-enoate-9-beta-D-glucuronide/9-hydroxy-10-O-D-glucuronoside-12Z-octadecenoate$$12-O-D-glucuronoside-13-hydroxyoctadec-9Z-enoate/12-hydroxy-13-O-D-glucuronoside-octadec-9Z-enoate/10-hydroxy-octadec-12Z-enoate-9-beta-D-glucuronide/9-hydroxy-10-O-D-glucuronoside-12Z-octadecenoate$</t>
+  </si>
+  <si>
     <t>Omega-6 fatty acid metabolism</t>
   </si>
   <si>
@@ -97,46 +145,181 @@
     <t>AMP/dGMP$arachidonic acid</t>
   </si>
   <si>
-    <t>Linoleate metabolism</t>
-  </si>
-  <si>
-    <t>E92,E2348,E113,E2350,E480,E2321,E492,E2084,E2639,E2085,E2640</t>
-  </si>
-  <si>
-    <t>C06426/C06427,C14762/C14826/C14825,CE2061,C14762/C14826/C14825,CE2006/CE6506,CE5526/CE5527/C14765,C04717/C14827,CE2306/CE2305/CE2304/CE2303,CE6504,CE2306/CE2305/CE2304/CE2303,CE6504</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$$13(S)-HODE; (13S)-Hydroxyoctadecadienoic acid; (9Z, 11E)-(13S)-13-Hydroxyoctadeca-9,11-dienoic acid/12(13)-EpOME; (12R,13S)-(9Z)-12,13-Epoxyoctadecenoic acid/9(10)-EpOME; (9R,10S)-(12Z)-9,10-Epoxyoctadecenoic acid$/$//13-OxoODE; 13-KODE; (9Z,11E)-13-Oxooctadeca-9,11-dienoic acid$(9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoic acid; (9Z,11E)-(13S)-13-Hydroperoxyoctadeca-9,11-dienoate; 13(S)-HPODE; 13S-Hydroperoxy-9Z,11E-octadecadienoic acid/9(S)-HPODE; 9(S)-HPOD; (10E,12Z)-(9S)-9-Hydroperoxyoctadeca-10,12-dienoic acid$12-O-D-glucuronoside-13-hydroxyoctadec-9Z-enoate/12-hydroxy-13-O-D-glucuronoside-octadec-9Z-enoate/10-hydroxy-octadec-12Z-enoate-9-beta-D-glucuronide/9-hydroxy-10-O-D-glucuronoside-12Z-octadecenoate$$12-O-D-glucuronoside-13-hydroxyoctadec-9Z-enoate/12-hydroxy-13-O-D-glucuronoside-octadec-9Z-enoate/10-hydroxy-octadec-12Z-enoate-9-beta-D-glucuronide/9-hydroxy-10-O-D-glucuronoside-12Z-octadecenoate$</t>
+    <t>Histidine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1403,E347,E1488,E2525</t>
+  </si>
+  <si>
+    <t>C00021,C06486/C00386,C00135,CE2065,C00020/C00362</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$(6R)-6-(L-erythro-1,2-Dihydroxypropyl)-5,6,7,8-tetrahydro-4a-/Carnosine; Nalpha-(beta-alanyl)-L-histidine$L-Histidine$acetylcarnosine$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>CoA Catabolism</t>
+  </si>
+  <si>
+    <t>E2192,E2525,E2191</t>
+  </si>
+  <si>
+    <t>C00831,C00020/C00362,C00831</t>
+  </si>
+  <si>
+    <t>Pantetheine; (R)-Pantetheine$AMP/dGMP$Pantetheine; (R)-Pantetheine</t>
+  </si>
+  <si>
+    <t>Lysine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E2525,E2108,E1926</t>
+  </si>
+  <si>
+    <t>C00021,C00020/C00362,,</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$AMP/dGMP$$</t>
+  </si>
+  <si>
+    <t>Fatty Acid Metabolism</t>
+  </si>
+  <si>
+    <t>E2345,E2634</t>
+  </si>
+  <si>
+    <t>C00249,</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$</t>
+  </si>
+  <si>
+    <t>Saturated fatty acids beta-oxidation</t>
+  </si>
+  <si>
+    <t>E2345</t>
+  </si>
+  <si>
+    <t>C00249</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)</t>
+  </si>
+  <si>
+    <t>Keratan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>E2558</t>
+  </si>
+  <si>
+    <t>C00055</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>O-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2796</t>
+  </si>
+  <si>
+    <t>C00021</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Fatty acid activation</t>
+  </si>
+  <si>
+    <t>E2345,E92,E2525</t>
+  </si>
+  <si>
+    <t>C00249,C06426/C06427,C00020/C00362</t>
+  </si>
+  <si>
+    <t>Hexadecanoate (n-C16:0)$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>C21-steroid hormone biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2263,E1295,E2398,E1116,E2274,E1163,E422,E2141,E1164,E2269,E1954,E2399,E2648,E2457,E2669</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Porphyrin metabolism</t>
+  </si>
+  <si>
+    <t>E2511,E1520,E2728,E354</t>
+  </si>
+  <si>
+    <t>,,,</t>
+  </si>
+  <si>
+    <t>$$$</t>
+  </si>
+  <si>
+    <t>Tyrosine metabolism</t>
+  </si>
+  <si>
+    <t>E918,E227,E412,E190,E1975,E889,E145,E413,E191,E890,E680,E2796,E1222,E432,E175,E160,E632,E912,E209,E336,E1059,E830,E931,E166,E1735,E178,E914,E2525,E186,E281,E65,E168,E66,E170</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,C00021,,,,,,,,,,,,,,,,C00020/C00362,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$S-Adenosyl-L-homocysteine$$$$$$$$$$$$$$$$AMP/dGMP$$$$$$</t>
+  </si>
+  <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2108,E2525</t>
+  </si>
+  <si>
+    <t>,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - globoseries</t>
+  </si>
+  <si>
+    <t>E740,E2558</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00055</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$CMP</t>
   </si>
   <si>
     <t>Vitamin A (retinol) metabolism</t>
   </si>
   <si>
-    <t>E2525,E2283,E2485,E3147,E2278,E2513</t>
-  </si>
-  <si>
-    <t>C00020/C00362,C16679/C16677/C16680,CE5594/CE1617,CE2962,CE5014,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
-  </si>
-  <si>
-    <t>AMP/dGMP$all-trans-18-Hydroxyretinoic acid/all-trans-4-Hydroxyretinoic acid/all-trans-5,6-Epoxyretinoic acid; all-trans-5,6-Epoxy-5,6-dihydroretinoic acid$9,13-cis-retinoate/9-cis-retinoate$rac-4-hydroxy-4-O-(beta-D-glucuronide)-all-trans-retinyl acetate$anhydroretinol$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
-  </si>
-  <si>
-    <t>Bile acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E2173,E3074,E3077,E1895,E3075,E2525,E2941</t>
-  </si>
-  <si>
-    <t>C05122/C15516,C05463/C05465,C05463/C05465,CE2202/C17335,C05463/C05465,C00020/C00362,C00695</t>
-  </si>
-  <si>
-    <t>taurocholic acid/Taurohyocholate; N-(3alpha,6alpha,7alpha-Trihydroxy-5beta-cholan-24-oyl)taurine$Taurodeoxycholate/Taurochenodeoxycholate; Chenodeoxycholoyltaurine$Taurodeoxycholate/Taurochenodeoxycholate; Chenodeoxycholoyltaurine$23S,25,26-trihydroxyvitamin D3/$Taurodeoxycholate/Taurochenodeoxycholate; Chenodeoxycholoyltaurine$AMP/dGMP$Cholate</t>
-  </si>
-  <si>
-    <t>CoA Catabolism</t>
-  </si>
-  <si>
-    <t>E2192,E2525,E2191</t>
+    <t>E2283,E2485,E2513,E3147,E2525</t>
+  </si>
+  <si>
+    <t>,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Butanoate metabolism</t>
+  </si>
+  <si>
+    <t>E1044,E2525,E1045</t>
   </si>
   <si>
     <t>,C00020/C00362,</t>
@@ -145,567 +328,471 @@
     <t>$AMP/dGMP$</t>
   </si>
   <si>
-    <t>Glycerophospholipid metabolism</t>
-  </si>
-  <si>
-    <t>E92,E2383,E2558,E1351,E256,E468,E2985,E2513</t>
-  </si>
-  <si>
-    <t>C06426/C06427,C00836,C00055,,C00219,C00588/C05594,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Sphinganine$CMP$$arachidonic acid$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
-  </si>
-  <si>
-    <t>Fatty Acid Metabolism</t>
-  </si>
-  <si>
-    <t>E2345,E2634</t>
-  </si>
-  <si>
-    <t>C00249,</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)$</t>
-  </si>
-  <si>
-    <t>Saturated fatty acids beta-oxidation</t>
-  </si>
-  <si>
-    <t>E2345</t>
-  </si>
-  <si>
-    <t>C00249</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)</t>
-  </si>
-  <si>
-    <t>Keratan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>E2558</t>
-  </si>
-  <si>
-    <t>C00055</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>O-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Fatty acid activation</t>
-  </si>
-  <si>
-    <t>E2345,E92,E2525</t>
-  </si>
-  <si>
-    <t>C00249,C06426/C06427,C00020/C00362</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Porphyrin metabolism</t>
-  </si>
-  <si>
-    <t>E2511,E1520,E2728,E354</t>
-  </si>
-  <si>
-    <t>,,,</t>
-  </si>
-  <si>
-    <t>$$$</t>
-  </si>
-  <si>
-    <t>C21-steroid hormone biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2263,E1295,E2398,E1116,E2274,E1163,E422,E2141,E1164,E2269,E1954,E2399,E2648,E2457,E2669</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>E2108,E2525</t>
-  </si>
-  <si>
-    <t>,C00020/C00362</t>
-  </si>
-  <si>
-    <t>$AMP/dGMP</t>
+    <t>Lipoate metabolism</t>
+  </si>
+  <si>
+    <t>E2411,E2412</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E1403,E347</t>
+  </si>
+  <si>
+    <t>C06486/C00386,C00135</t>
+  </si>
+  <si>
+    <t>(6R)-6-(L-erythro-1,2-Dihydroxypropyl)-5,6,7,8-tetrahydro-4a-/Carnosine; Nalpha-(beta-alanyl)-L-histidine$L-Histidine</t>
+  </si>
+  <si>
+    <t>Valine, leucine and isoleucine degradation</t>
+  </si>
+  <si>
+    <t>E2525</t>
+  </si>
+  <si>
+    <t>C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Mono-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E1074</t>
+  </si>
+  <si>
+    <t>Phytanic acid peroxisomal oxidation</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>E740,E2558,E2970</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00055,</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$CMP$</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E1900,E1301,E1286,E2899,E1666,E256,E1899,E2525,E2295</t>
+  </si>
+  <si>
+    <t>,,,,,C00219,,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$$$$$arachidonic acid$$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E830,E2796,E227,E2525</t>
+  </si>
+  <si>
+    <t>,C00021,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$S-Adenosyl-L-homocysteine$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>E445,E2558,E2525,E1039</t>
+  </si>
+  <si>
+    <t>,C00055,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$CMP$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E1353,E1475,E2525,E1074</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>E1129,E3004,E3062,E2859,E1128,E3153</t>
+  </si>
+  <si>
+    <t>,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - lactoseries</t>
+  </si>
+  <si>
+    <t>Blood Group Biosynthesis</t>
+  </si>
+  <si>
+    <t>Caffeine metabolism</t>
+  </si>
+  <si>
+    <t>E740</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
+  </si>
+  <si>
+    <t>Starch and Sucrose Metabolism</t>
+  </si>
+  <si>
+    <t>Glycolysis and Gluconeogenesis</t>
+  </si>
+  <si>
+    <t>E740,E2525</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00020/C00362</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Hexose phosphorylation</t>
+  </si>
+  <si>
+    <t>E740,E785,E830,E784</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,,,</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$$$</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2525,E256,E2513,E2295</t>
+  </si>
+  <si>
+    <t>C06426/C06427,C00020/C00362,C00219,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP$arachidonic acid$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$</t>
+  </si>
+  <si>
+    <t>Biopterin metabolism</t>
+  </si>
+  <si>
+    <t>E912,E1455,E1459,E1735</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1239,E2525</t>
+  </si>
+  <si>
+    <t>C00021,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>E26,E2796,E2525</t>
+  </si>
+  <si>
+    <t>,C00021,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$S-Adenosyl-L-homocysteine$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>E315,E2525</t>
+  </si>
+  <si>
+    <t>D4&amp;E4-neuroprostanes formation</t>
+  </si>
+  <si>
+    <t>E2895,E1408</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Selenoamino acid metabolism</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E2525</t>
+  </si>
+  <si>
+    <t>C00021,C00020/C00362</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Tryptophan metabolism</t>
+  </si>
+  <si>
+    <t>E666,E877,E889,E760,E890,E2103,E2796,E700,E610,E1186,E126,E632,E693,E737,E2747,E846,E1735,E2525,E651,E705,E2750,E767,E706</t>
+  </si>
+  <si>
+    <t>,,,,,,C00021,,,,,,,,,,,C00020/C00362,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$S-Adenosyl-L-homocysteine$$$$$$$$$$$AMP/dGMP$$$$$</t>
+  </si>
+  <si>
+    <t>Urea cycle/amino group metabolism</t>
+  </si>
+  <si>
+    <t>E26,E2796,E412,E1529,E175,E1535,E145,E413</t>
+  </si>
+  <si>
+    <t>,C00021,,,,,,</t>
+  </si>
+  <si>
+    <t>$S-Adenosyl-L-homocysteine$$$$$$</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin H (biotin) metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
   </si>
   <si>
     <t>Drug metabolism - other enzymes</t>
   </si>
   <si>
-    <t>E2179,E1536</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>Tyrosine metabolism</t>
-  </si>
-  <si>
-    <t>E918,E227,E412,E190,E1975,E889,E413,E191,E890,E680,E432,E1222,E175,E632,E912,E209,E46,E336,E1059,E830,E931,E166,E1735,E914,E178,E468,E2525,E186,E281,E65,E168,E901,E66,E170</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,,,,,,,,,,,,C00588/C05594,C00020/C00362,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$$$$$$$$$$$$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$AMP/dGMP$$$$$$$</t>
-  </si>
-  <si>
-    <t>Histidine metabolism</t>
-  </si>
-  <si>
-    <t>E1488,E1403,E347,E2525</t>
-  </si>
-  <si>
-    <t>,,,C00020/C00362</t>
-  </si>
-  <si>
-    <t>$$$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Butanoate metabolism</t>
-  </si>
-  <si>
-    <t>E1044,E2525,E1045</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol phosphate metabolism</t>
-  </si>
-  <si>
-    <t>E2345,E2558</t>
-  </si>
-  <si>
-    <t>C00249,C00055</t>
-  </si>
-  <si>
-    <t>Hexadecanoate (n-C16:0)$CMP</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E1403,E347</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E92,E2525,E256,E1395,E2513,E2295</t>
-  </si>
-  <si>
-    <t>C06426/C06427,C00020/C00362,C00219,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP$arachidonic acid$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$</t>
-  </si>
-  <si>
-    <t>Valine, leucine and isoleucine degradation</t>
-  </si>
-  <si>
-    <t>E2525</t>
-  </si>
-  <si>
-    <t>C00020/C00362</t>
-  </si>
-  <si>
-    <t>AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Mono-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>E1074</t>
-  </si>
-  <si>
-    <t>Phytanic acid peroxisomal oxidation</t>
-  </si>
-  <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>Lysine metabolism</t>
-  </si>
-  <si>
-    <t>E2108,E2525,E1926</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E35,E2558,E2970</t>
-  </si>
-  <si>
-    <t>,C00055,</t>
-  </si>
-  <si>
-    <t>$CMP$</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E1900,E1301,E1286,E2899,E1666,E256,E1899,E2525,E2295</t>
-  </si>
-  <si>
-    <t>,,,,,C00219,,C00020/C00362,</t>
-  </si>
-  <si>
-    <t>$$$$$arachidonic acid$$AMP/dGMP$</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>E445,E2558,E2525,E1039</t>
-  </si>
-  <si>
-    <t>,C00055,C00020/C00362,</t>
-  </si>
-  <si>
-    <t>$CMP$AMP/dGMP$</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E1353,E1475,E2525,E1074</t>
-  </si>
-  <si>
-    <t>,,C00020/C00362,</t>
-  </si>
-  <si>
-    <t>$$AMP/dGMP$</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - lactoseries</t>
-  </si>
-  <si>
-    <t>Blood Group Biosynthesis</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
-  </si>
-  <si>
-    <t>Biopterin metabolism</t>
-  </si>
-  <si>
-    <t>E912,E1455,E1459,E1735</t>
-  </si>
-  <si>
-    <t>D4&amp;E4-neuroprostanes formation</t>
-  </si>
-  <si>
-    <t>E2895,E1408</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Selenoamino acid metabolism</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E1129,E3004,E3062,E1128,E3153</t>
-  </si>
-  <si>
-    <t>,,,,</t>
-  </si>
-  <si>
-    <t>$$$$</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - globoseries</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
+    <t>E1536</t>
+  </si>
+  <si>
+    <t>Drug metabolism - cytochrome P450</t>
+  </si>
+  <si>
+    <t>E521,E2919,E2568,E2336,E178,E1274,E940</t>
+  </si>
+  <si>
+    <t>,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$</t>
+  </si>
+  <si>
+    <t>Vitamin B6 (pyridoxine) metabolism</t>
+  </si>
+  <si>
+    <t>E383,E384</t>
+  </si>
+  <si>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>E1895</t>
+  </si>
+  <si>
+    <t>CE2202/C17335</t>
+  </si>
+  <si>
+    <t>23S,25,26-trihydroxyvitamin D3/</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>E3034</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+  </si>
+  <si>
+    <t>Alanine and Aspartate Metabolism</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E2442,E740</t>
+  </si>
+  <si>
+    <t>,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480</t>
+  </si>
+  <si>
+    <t>$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>Limonene and pinene degradation</t>
+  </si>
+  <si>
+    <t>E265</t>
+  </si>
+  <si>
+    <t>Arginine and Proline Metabolism</t>
+  </si>
+  <si>
+    <t>E26</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
   </si>
   <si>
     <t>Aminosugars metabolism</t>
   </si>
   <si>
-    <t>E35,E2558</t>
-  </si>
-  <si>
-    <t>,C00055</t>
-  </si>
-  <si>
-    <t>$CMP</t>
-  </si>
-  <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E830,E227,E2525</t>
-  </si>
-  <si>
-    <t>,,C00020/C00362</t>
-  </si>
-  <si>
-    <t>$$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (pyridoxine) metabolism</t>
-  </si>
-  <si>
-    <t>E383,E384</t>
-  </si>
-  <si>
-    <t>Drug metabolism - cytochrome P450</t>
-  </si>
-  <si>
-    <t>E521,E2919,E2568,E2336,E178,E1274,E940</t>
-  </si>
-  <si>
-    <t>,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$</t>
-  </si>
-  <si>
-    <t>Hexose phosphorylation</t>
-  </si>
-  <si>
-    <t>E785,E830,E784</t>
-  </si>
-  <si>
-    <t>,,</t>
-  </si>
-  <si>
-    <t>$$</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>E1895</t>
-  </si>
-  <si>
-    <t>CE2202/C17335</t>
-  </si>
-  <si>
-    <t>23S,25,26-trihydroxyvitamin D3/</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>E3034</t>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2263,E2796,E2141,E2269,E3018,E1954,E422</t>
+  </si>
+  <si>
+    <t>,C00021,,,,,</t>
+  </si>
+  <si>
+    <t>$S-Adenosyl-L-homocysteine$$$$$</t>
+  </si>
+  <si>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E3065,E2525,E256</t>
+  </si>
+  <si>
+    <t>,C00020/C00362,C00219</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP$arachidonic acid</t>
+  </si>
+  <si>
+    <t>Purine metabolism</t>
+  </si>
+  <si>
+    <t>E1671,E2525,E1677</t>
+  </si>
+  <si>
+    <t>Hyaluronan Metabolism</t>
+  </si>
+  <si>
+    <t>R Group Synthesis</t>
+  </si>
+  <si>
+    <t>C5-Branched dibasic acid metabolism</t>
+  </si>
+  <si>
+    <t>Pyruvate Metabolism</t>
+  </si>
+  <si>
+    <t>Chondroitin sulfate degradation</t>
+  </si>
+  <si>
+    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
   </si>
   <si>
     <t>Keratan sulfate degradation</t>
   </si>
   <si>
-    <t>E35</t>
-  </si>
-  <si>
-    <t>Hyaluronan Metabolism</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+    <t>Glycerolipid metabolism</t>
+  </si>
+  <si>
+    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
+  </si>
+  <si>
+    <t>Parathio degradation</t>
+  </si>
+  <si>
+    <t>Electron transport chain</t>
+  </si>
+  <si>
+    <t>Heparan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin B9 (folate) metabolism</t>
+  </si>
+  <si>
+    <t>Glyoxylate and Dicarboxylate Metabolism</t>
+  </si>
+  <si>
+    <t>Glycosaminoglycan degradation</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation</t>
+  </si>
+  <si>
+    <t>ROS Detoxification</t>
+  </si>
+  <si>
+    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
+  </si>
+  <si>
+    <t>Geraniol degradation</t>
+  </si>
+  <si>
+    <t>Vitamin D</t>
+  </si>
+  <si>
+    <t>Dynorphin metabolism</t>
   </si>
   <si>
     <t>Heparan sulfate degradation</t>
   </si>
   <si>
-    <t>Alanine and Aspartate Metabolism</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>E1239,E2525</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E26,E2525</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E3065,E1331,E2525,E256</t>
-  </si>
-  <si>
-    <t>,,C00020/C00362,C00219</t>
-  </si>
-  <si>
-    <t>$$AMP/dGMP$arachidonic acid</t>
-  </si>
-  <si>
-    <t>Tryptophan metabolism</t>
-  </si>
-  <si>
-    <t>E666,E877,E889,E760,E890,E2103,E1186,E126,E632,E1187,E737,E2747,E846,E738,E1735,E2525,E651,E705,E2750,E767</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,,C00020/C00362,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$$AMP/dGMP$$$$</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
-  </si>
-  <si>
-    <t>Limonene and pinene degradation</t>
-  </si>
-  <si>
-    <t>E265</t>
-  </si>
-  <si>
-    <t>Arginine and Proline Metabolism</t>
-  </si>
-  <si>
-    <t>E26</t>
-  </si>
-  <si>
-    <t>Urea cycle/amino group metabolism</t>
-  </si>
-  <si>
-    <t>E26,E412,E1529,E175,E1535,E413</t>
-  </si>
-  <si>
-    <t>,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E2442</t>
-  </si>
-  <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2263,E2141,E2269,E3018,E1954,E422</t>
-  </si>
-  <si>
-    <t>Purine metabolism</t>
-  </si>
-  <si>
-    <t>E1671,E2525,E1677</t>
-  </si>
-  <si>
-    <t>R Group Synthesis</t>
-  </si>
-  <si>
-    <t>C5-Branched dibasic acid metabolism</t>
-  </si>
-  <si>
-    <t>Pyruvate Metabolism</t>
-  </si>
-  <si>
-    <t>Chondroitin sulfate degradation</t>
-  </si>
-  <si>
-    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
-  </si>
-  <si>
-    <t>Glycerolipid metabolism</t>
-  </si>
-  <si>
-    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
-  </si>
-  <si>
-    <t>Parathio degradation</t>
-  </si>
-  <si>
-    <t>Electron transport chain</t>
-  </si>
-  <si>
-    <t>Caffeine metabolism</t>
-  </si>
-  <si>
-    <t>Lipoate metabolism</t>
-  </si>
-  <si>
-    <t>Heparan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin B9 (folate) metabolism</t>
-  </si>
-  <si>
-    <t>Glyoxylate and Dicarboxylate Metabolism</t>
-  </si>
-  <si>
-    <t>Glycosaminoglycan degradation</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation</t>
-  </si>
-  <si>
-    <t>ROS Detoxification</t>
-  </si>
-  <si>
-    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
-  </si>
-  <si>
-    <t>Geraniol degradation</t>
-  </si>
-  <si>
-    <t>Vitamin D</t>
-  </si>
-  <si>
-    <t>Dynorphin metabolism</t>
-  </si>
-  <si>
     <t>Fatty acid oxidation, peroxisome</t>
   </si>
   <si>
@@ -742,9 +829,6 @@
     <t>Atrazine degradation</t>
   </si>
   <si>
-    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
-  </si>
-  <si>
     <t>Carbon fixation</t>
   </si>
   <si>
@@ -758,9 +842,6 @@
   </si>
   <si>
     <t>Prostaglandin formation from dihomo gama-linoleic acid</t>
-  </si>
-  <si>
-    <t>Starch and Sucrose Metabolism</t>
   </si>
   <si>
     <t>Trihydroxycoprostanoyl-CoA beta-oxidation</t>
@@ -1132,7 +1213,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.0114956051158804</v>
+        <v>0.01100821834927144</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1155,7 +1236,7 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>0.01470563519940841</v>
+        <v>0.01408379691097629</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1172,13 +1253,13 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>0.0187223744138754</v>
+        <v>0.01742827851632746</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1195,13 +1276,13 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>0.03307507436849801</v>
+        <v>0.01768037511974588</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1218,13 +1299,13 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>0.03457084754878069</v>
+        <v>0.02327691971563503</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1241,13 +1322,13 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>0.03621787869111444</v>
+        <v>0.031310398144569</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1264,13 +1345,13 @@
         <v>31</v>
       </c>
       <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
         <v>6</v>
       </c>
-      <c r="C8">
-        <v>18</v>
-      </c>
       <c r="D8">
-        <v>0.04566309809919161</v>
+        <v>0.031310398144569</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1287,13 +1368,13 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D9">
-        <v>0.04574713030033109</v>
+        <v>0.03267171980302852</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1310,13 +1391,13 @@
         <v>39</v>
       </c>
       <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
       <c r="D10">
-        <v>0.05099073965143443</v>
+        <v>0.03268852624325642</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1333,13 +1414,13 @@
         <v>43</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D11">
-        <v>0.05616712324162619</v>
+        <v>0.04115897211811567</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1356,13 +1437,13 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>0.06564595553015916</v>
+        <v>0.04759583872539958</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1379,13 +1460,13 @@
         <v>51</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>0.07231811230063361</v>
+        <v>0.05371338296835347</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1402,13 +1483,13 @@
         <v>55</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>0.07231811230063361</v>
+        <v>0.0625871834086822</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1431,62 +1512,62 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>0.07231811230063361</v>
+        <v>0.07001562998941194</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>0.07477185257390633</v>
+        <v>0.07001562998941194</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0.07001562998941194</v>
+      </c>
+      <c r="E17" t="s">
         <v>64</v>
       </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17">
-        <v>13</v>
-      </c>
-      <c r="D17">
-        <v>0.1006033512041814</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>65</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>66</v>
-      </c>
-      <c r="G17" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1494,13 +1575,13 @@
         <v>68</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>0.1029562528360868</v>
+        <v>0.07001562998941194</v>
       </c>
       <c r="E18" t="s">
         <v>69</v>
@@ -1517,13 +1598,13 @@
         <v>72</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>0.1053763802289037</v>
+        <v>0.07181391909379674</v>
       </c>
       <c r="E19" t="s">
         <v>73</v>
@@ -1540,13 +1621,13 @@
         <v>76</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="D20">
-        <v>0.1053763802289037</v>
+        <v>0.09053629350767214</v>
       </c>
       <c r="E20" t="s">
         <v>77</v>
@@ -1563,13 +1644,13 @@
         <v>80</v>
       </c>
       <c r="B21">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="D21">
-        <v>0.1154266314851851</v>
+        <v>0.0946370649232786</v>
       </c>
       <c r="E21" t="s">
         <v>81</v>
@@ -1586,13 +1667,13 @@
         <v>84</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C22">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="D22">
-        <v>0.1251743668173644</v>
+        <v>0.09835128821364347</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
@@ -1609,142 +1690,142 @@
         <v>88</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>0.1313087175005462</v>
+        <v>0.1007882220466883</v>
       </c>
       <c r="E23" t="s">
         <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>0.1389556478042386</v>
+        <v>0.1007882220466883</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D25">
-        <v>0.1389556478042386</v>
+        <v>0.1137123745819398</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="G25" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B26">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C26">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D26">
-        <v>0.1419303877245761</v>
+        <v>0.1277121392917766</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F26" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>0.143224483622124</v>
+        <v>0.1352918438345574</v>
       </c>
       <c r="E27" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F27" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G27" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>0.143224483622124</v>
+        <v>0.1352918438345574</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -1753,15 +1834,21 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <v>0.143224483622124</v>
+        <v>0.1403673887833818</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>113</v>
+      </c>
+      <c r="F29" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -1770,136 +1857,130 @@
         <v>2</v>
       </c>
       <c r="D30">
-        <v>0.143224483622124</v>
+        <v>0.1403673887833818</v>
       </c>
       <c r="E30" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G30" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>0.1556444429505386</v>
+        <v>0.1403673887833818</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" t="s">
-        <v>41</v>
-      </c>
-      <c r="G31" t="s">
-        <v>42</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>0.1556444429505386</v>
+        <v>0.1403673887833818</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="G32" t="s">
-        <v>42</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D33">
-        <v>0.1899968067763567</v>
+        <v>0.1499974790339658</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="F33" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B34">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D34">
-        <v>0.1956269642527016</v>
+        <v>0.1814927480210416</v>
       </c>
       <c r="E34" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F34" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G34" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C35">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D35">
-        <v>0.1982319624880254</v>
+        <v>0.1826691988369943</v>
       </c>
       <c r="E35" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F35" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1908,790 +1989,814 @@
         <v>17</v>
       </c>
       <c r="D36">
-        <v>0.1982319624880254</v>
+        <v>0.1890724525638225</v>
       </c>
       <c r="E36" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D37">
-        <v>0.2163493050536966</v>
+        <v>0.1890724525638225</v>
       </c>
       <c r="E37" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D38">
-        <v>0.2163493050536966</v>
+        <v>0.1890724525638225</v>
       </c>
       <c r="E38" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D39">
-        <v>0.2163493050536966</v>
+        <v>0.1981983496075696</v>
       </c>
       <c r="E39" t="s">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="G39" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>0.2578107930959144</v>
+        <v>0.2108704055394027</v>
       </c>
       <c r="E40" t="s">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
+        <v>65</v>
+      </c>
+      <c r="G40" t="s">
         <v>66</v>
-      </c>
-      <c r="G40" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>0.2676929799499168</v>
+        <v>0.2108704055394027</v>
       </c>
       <c r="E41" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="F41" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="G41" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>0.2885497722727349</v>
+        <v>0.2108704055394027</v>
       </c>
       <c r="E42" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="F42" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="G42" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>0.2885497722727349</v>
+        <v>0.2108704055394027</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="F43" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="G43" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>0.3359943530360834</v>
+        <v>0.2108704055394027</v>
       </c>
       <c r="E44" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F44" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G44" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D45">
-        <v>0.3395573183643972</v>
+        <v>0.2180971748373977</v>
       </c>
       <c r="E45" t="s">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="F45" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="G45" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D46">
-        <v>0.3395573183643972</v>
+        <v>0.2208198181543167</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="F46" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="G46" t="s">
-        <v>103</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D47">
-        <v>0.3395573183643972</v>
+        <v>0.2459286398547924</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>162</v>
       </c>
       <c r="F47" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="G47" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D48">
-        <v>0.3395573183643972</v>
+        <v>0.2483151543671535</v>
       </c>
       <c r="E48" t="s">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="F48" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="G48" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>0.3451538629602864</v>
+        <v>0.2529537318700526</v>
       </c>
       <c r="E49" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="F49" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="G49" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D50">
-        <v>0.3557587267440883</v>
+        <v>0.2529537318700526</v>
       </c>
       <c r="E50" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="F50" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="G50" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="B51">
         <v>2</v>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D51">
-        <v>0.3759768743382464</v>
+        <v>0.2611048553805818</v>
       </c>
       <c r="E51" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="F51" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="B52">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D52">
-        <v>0.3780608729265054</v>
+        <v>0.2611048553805818</v>
       </c>
       <c r="E52" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="F52" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="G52" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D53">
-        <v>0.3804641938790945</v>
+        <v>0.2611048553805818</v>
       </c>
       <c r="E53" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F53" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G53" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D54">
-        <v>0.381657451135275</v>
+        <v>0.2835750659652779</v>
       </c>
       <c r="E54" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="F54" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="G54" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D55">
-        <v>0.381657451135275</v>
+        <v>0.2835750659652779</v>
       </c>
       <c r="E55" t="s">
-        <v>167</v>
+        <v>113</v>
+      </c>
+      <c r="F55" t="s">
+        <v>114</v>
+      </c>
+      <c r="G55" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D56">
-        <v>0.381657451135275</v>
+        <v>0.3126670139997647</v>
       </c>
       <c r="E56" t="s">
-        <v>169</v>
+        <v>93</v>
+      </c>
+      <c r="F56" t="s">
+        <v>94</v>
+      </c>
+      <c r="G56" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D57">
-        <v>0.4250516798037008</v>
+        <v>0.3126670139997647</v>
       </c>
       <c r="E57" t="s">
-        <v>169</v>
+        <v>184</v>
+      </c>
+      <c r="F57" t="s">
+        <v>185</v>
+      </c>
+      <c r="G57" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="D58">
-        <v>0.4250516798037008</v>
+        <v>0.326112166182081</v>
       </c>
       <c r="E58" t="s">
-        <v>56</v>
+        <v>188</v>
       </c>
       <c r="F58" t="s">
-        <v>57</v>
+        <v>189</v>
       </c>
       <c r="G58" t="s">
-        <v>58</v>
+        <v>190</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D59">
-        <v>0.4250516798037008</v>
+        <v>0.3300280667551806</v>
       </c>
       <c r="E59" t="s">
-        <v>169</v>
+        <v>192</v>
+      </c>
+      <c r="F59" t="s">
+        <v>193</v>
+      </c>
+      <c r="G59" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D60">
-        <v>0.4250516798037008</v>
+        <v>0.3354901598292466</v>
       </c>
       <c r="E60" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F60" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="G60" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D61">
-        <v>0.4383119611435102</v>
+        <v>0.3354901598292466</v>
       </c>
       <c r="E61" t="s">
-        <v>175</v>
+        <v>113</v>
       </c>
       <c r="F61" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="G61" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D62">
-        <v>0.4383119611435102</v>
+        <v>0.3354901598292466</v>
       </c>
       <c r="E62" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="F62" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="G62" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D63">
-        <v>0.4624628157509958</v>
+        <v>0.3354901598292466</v>
       </c>
       <c r="E63" t="s">
-        <v>101</v>
-      </c>
-      <c r="F63" t="s">
-        <v>102</v>
-      </c>
-      <c r="G63" t="s">
-        <v>103</v>
+        <v>199</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C64">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D64">
-        <v>0.4921261827532311</v>
+        <v>0.3680610409909077</v>
       </c>
       <c r="E64" t="s">
-        <v>101</v>
+        <v>201</v>
       </c>
       <c r="F64" t="s">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="G64" t="s">
-        <v>103</v>
+        <v>203</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="B65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D65">
-        <v>0.4921261827532311</v>
+        <v>0.3697921043343809</v>
       </c>
       <c r="E65" t="s">
-        <v>169</v>
+        <v>205</v>
+      </c>
+      <c r="F65" t="s">
+        <v>106</v>
+      </c>
+      <c r="G65" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D66">
-        <v>0.4921261827532311</v>
+        <v>0.3770188736323759</v>
       </c>
       <c r="E66" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="F66" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="G66" t="s">
-        <v>103</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D67">
-        <v>0.4939916976185274</v>
+        <v>0.3770188736323759</v>
       </c>
       <c r="E67" t="s">
-        <v>183</v>
-      </c>
-      <c r="F67" t="s">
-        <v>184</v>
-      </c>
-      <c r="G67" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="B68">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="D68">
-        <v>0.5082939782524664</v>
+        <v>0.4213878758340196</v>
       </c>
       <c r="E68" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="F68" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
       <c r="G68" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D69">
-        <v>0.5164787146434514</v>
+        <v>0.4213878758340196</v>
       </c>
       <c r="E69" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="F69" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="G69" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D70">
-        <v>0.5164787146434514</v>
+        <v>0.4338750609233458</v>
       </c>
       <c r="E70" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="F70" t="s">
-        <v>102</v>
+        <v>216</v>
       </c>
       <c r="G70" t="s">
-        <v>103</v>
+        <v>217</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D71">
-        <v>0.5164787146434514</v>
+        <v>0.4916051831061663</v>
       </c>
       <c r="E71" t="s">
-        <v>193</v>
+        <v>148</v>
+      </c>
+      <c r="F71" t="s">
+        <v>149</v>
+      </c>
+      <c r="G71" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -2700,38 +2805,32 @@
         <v>10</v>
       </c>
       <c r="D72">
-        <v>0.5164787146434514</v>
+        <v>0.5166299726055025</v>
       </c>
       <c r="E72" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="B73">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D73">
-        <v>0.5193190030419657</v>
+        <v>0.5166299726055025</v>
       </c>
       <c r="E73" t="s">
-        <v>197</v>
-      </c>
-      <c r="F73" t="s">
-        <v>198</v>
-      </c>
-      <c r="G73" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -2740,143 +2839,164 @@
         <v>11</v>
       </c>
       <c r="D74">
-        <v>0.5333859935127141</v>
+        <v>0.5340918640022857</v>
       </c>
       <c r="E74" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F74" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G74" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D75">
-        <v>0.5621586191828709</v>
+        <v>0.5340918640022857</v>
       </c>
       <c r="E75" t="s">
-        <v>169</v>
+        <v>64</v>
+      </c>
+      <c r="F75" t="s">
+        <v>65</v>
+      </c>
+      <c r="G75" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C76">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D76">
-        <v>0.5751668039192619</v>
+        <v>0.535638056503252</v>
       </c>
       <c r="E76" t="s">
-        <v>203</v>
+        <v>226</v>
+      </c>
+      <c r="F76" t="s">
+        <v>227</v>
+      </c>
+      <c r="G76" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="B77">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D77">
-        <v>0.5826624762609032</v>
+        <v>0.5616376195358062</v>
       </c>
       <c r="E77" t="s">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="F77" t="s">
-        <v>198</v>
+        <v>149</v>
       </c>
       <c r="G77" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="B78">
         <v>3</v>
       </c>
       <c r="C78">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D78">
-        <v>0.5977378531453252</v>
+        <v>0.5678223895396716</v>
       </c>
       <c r="E78" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="F78" t="s">
-        <v>41</v>
+        <v>232</v>
       </c>
       <c r="G78" t="s">
-        <v>42</v>
+        <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D79">
-        <v>0.6136535520411421</v>
+        <v>0.5968807246937027</v>
+      </c>
+      <c r="E79" t="s">
+        <v>235</v>
+      </c>
+      <c r="F79" t="s">
+        <v>102</v>
+      </c>
+      <c r="G79" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D80">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -2885,40 +3005,40 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2927,26 +3047,26 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="B86">
         <v>0</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D86">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2955,166 +3075,166 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D88">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="B92">
         <v>0</v>
       </c>
       <c r="C92">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D93">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="B96">
         <v>0</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D96">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D98">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -3123,12 +3243,12 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -3137,12 +3257,12 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3151,40 +3271,40 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D102">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3193,26 +3313,26 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="B105">
         <v>0</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D105">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3221,82 +3341,82 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="B108">
         <v>0</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="B109">
         <v>0</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3305,26 +3425,26 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="B113">
         <v>0</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D113">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3333,12 +3453,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3347,12 +3467,12 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3361,12 +3481,12 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3375,26 +3495,26 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B118">
         <v>0</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3403,12 +3523,12 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3417,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0.6136535520411421</v>
+        <v>0.6138888422043327</v>
       </c>
     </row>
   </sheetData>

--- a/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
+++ b/results/pathways/BC_vs_Control/mcg_pathwayanalysis_BC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="277">
   <si>
     <t>pathway</t>
   </si>
@@ -76,13 +76,13 @@
     <t>Vitamin B2 (riboflavin) metabolism</t>
   </si>
   <si>
-    <t>E276,E2525,E1373,E3036</t>
-  </si>
-  <si>
-    <t>C01847,C00020/C00362,C00255,C00061</t>
-  </si>
-  <si>
-    <t>Reduced FMN; FMNH2$AMP/dGMP$Riboflavin$FMN</t>
+    <t>E2525,E276,E1373,E3036</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C01847,C00255,C00061</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$Reduced FMN; FMNH2$Riboflavin$FMN</t>
   </si>
   <si>
     <t>Glycerophospholipid metabolism</t>
@@ -145,6 +145,18 @@
     <t>AMP/dGMP$arachidonic acid</t>
   </si>
   <si>
+    <t>Butanoate metabolism</t>
+  </si>
+  <si>
+    <t>E1046,E1044,E2525,E1045</t>
+  </si>
+  <si>
+    <t>C02727,C02727,C00020/C00362,C02727</t>
+  </si>
+  <si>
+    <t>N6-Acetyl-L-lysine$N6-Acetyl-L-lysine$AMP/dGMP$N6-Acetyl-L-lysine</t>
+  </si>
+  <si>
     <t>Histidine metabolism</t>
   </si>
   <si>
@@ -157,6 +169,18 @@
     <t>S-Adenosyl-L-homocysteine$(6R)-6-(L-erythro-1,2-Dihydroxypropyl)-5,6,7,8-tetrahydro-4a-/Carnosine; Nalpha-(beta-alanyl)-L-histidine$L-Histidine$acetylcarnosine$AMP/dGMP</t>
   </si>
   <si>
+    <t>Vitamin A (retinol) metabolism</t>
+  </si>
+  <si>
+    <t>E2525,E2283,E2485,E3147,E2278,E2513</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C16679/C16677/C16680,CE5594/CE1617,CE2962,CE5014,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$all-trans-18-Hydroxyretinoic acid/all-trans-4-Hydroxyretinoic acid/all-trans-5,6-Epoxyretinoic acid; all-trans-5,6-Epoxy-5,6-dihydroretinoic acid$9,13-cis-retinoate/9-cis-retinoate$rac-4-hydroxy-4-O-(beta-D-glucuronide)-all-trans-retinyl acetate$anhydroretinol$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
+  </si>
+  <si>
     <t>CoA Catabolism</t>
   </si>
   <si>
@@ -172,13 +196,13 @@
     <t>Lysine metabolism</t>
   </si>
   <si>
-    <t>E2796,E2525,E2108,E1926</t>
-  </si>
-  <si>
-    <t>C00021,C00020/C00362,,</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$AMP/dGMP$$</t>
+    <t>E2525,E2796,E2108,E1926</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C00021,,</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$S-Adenosyl-L-homocysteine$$</t>
   </si>
   <si>
     <t>Fatty Acid Metabolism</t>
@@ -268,460 +292,436 @@
     <t>$$$</t>
   </si>
   <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>E2108,E2525</t>
+  </si>
+  <si>
+    <t>,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - globoseries</t>
+  </si>
+  <si>
+    <t>E740,E2558</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00055</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$CMP</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E1900,E1301,E1286,E2899,E1287,E256,E1666,E1899,E2525,E2295</t>
+  </si>
+  <si>
+    <t>,,,,,C00219,,,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$$$$$arachidonic acid$$$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E1403,E347</t>
+  </si>
+  <si>
+    <t>C06486/C00386,C00135</t>
+  </si>
+  <si>
+    <t>(6R)-6-(L-erythro-1,2-Dihydroxypropyl)-5,6,7,8-tetrahydro-4a-/Carnosine; Nalpha-(beta-alanyl)-L-histidine$L-Histidine</t>
+  </si>
+  <si>
+    <t>Valine, leucine and isoleucine degradation</t>
+  </si>
+  <si>
+    <t>E2525</t>
+  </si>
+  <si>
+    <t>C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Mono-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E1074</t>
+  </si>
+  <si>
+    <t>Phytanic acid peroxisomal oxidation</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
     <t>Tyrosine metabolism</t>
   </si>
   <si>
-    <t>E918,E227,E412,E190,E1975,E889,E145,E413,E191,E890,E680,E2796,E1222,E432,E175,E160,E632,E912,E209,E336,E1059,E830,E931,E166,E1735,E178,E914,E2525,E186,E281,E65,E168,E66,E170</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,C00021,,,,,,,,,,,,,,,,C00020/C00362,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$S-Adenosyl-L-homocysteine$$$$$$$$$$$$$$$$AMP/dGMP$$$$$$</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>E2108,E2525</t>
-  </si>
-  <si>
-    <t>,C00020/C00362</t>
-  </si>
-  <si>
-    <t>$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - globoseries</t>
-  </si>
-  <si>
-    <t>E740,E2558</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00055</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$CMP</t>
-  </si>
-  <si>
-    <t>Vitamin A (retinol) metabolism</t>
-  </si>
-  <si>
-    <t>E2283,E2485,E2513,E3147,E2525</t>
-  </si>
-  <si>
-    <t>,,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,,C00020/C00362</t>
-  </si>
-  <si>
-    <t>$$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Butanoate metabolism</t>
-  </si>
-  <si>
-    <t>E1044,E2525,E1045</t>
+    <t>E918,E227,E412,E190,E1975,E285,E889,E413,E191,E890,E680,E2796,E1222,E432,E175,E632,E912,E209,E336,E1059,E830,E931,E166,E1735,E178,E914,E2525,E186,E168,E65,E66,E170</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,C00021,,,,,,,,,,,,,,,C00020/C00362,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$S-Adenosyl-L-homocysteine$$$$$$$$$$$$$$$AMP/dGMP$$$$$</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>E740,E2558,E2970</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00055,</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$CMP$</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E2796,E227,E2525,E830</t>
+  </si>
+  <si>
+    <t>C00021,,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>E445,E2558,E2525,E1039</t>
+  </si>
+  <si>
+    <t>,C00055,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$CMP$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E1353,E1475,E2525,E1074</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>E1129,E3004,E3062,E2859,E1128,E3153</t>
+  </si>
+  <si>
+    <t>,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - lactoseries</t>
+  </si>
+  <si>
+    <t>Blood Group Biosynthesis</t>
+  </si>
+  <si>
+    <t>Caffeine metabolism</t>
+  </si>
+  <si>
+    <t>E740</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
+  </si>
+  <si>
+    <t>Starch and Sucrose Metabolism</t>
+  </si>
+  <si>
+    <t>Glycolysis and Gluconeogenesis</t>
+  </si>
+  <si>
+    <t>E740,E2525</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00020/C00362</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Hexose phosphorylation</t>
+  </si>
+  <si>
+    <t>E740,E785,E830,E784</t>
+  </si>
+  <si>
+    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,,,</t>
+  </si>
+  <si>
+    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$$$</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E92,E2525,E256,E2513,E2295</t>
+  </si>
+  <si>
+    <t>C06426/C06427,C00020/C00362,C00219,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,</t>
+  </si>
+  <si>
+    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP$arachidonic acid$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$</t>
+  </si>
+  <si>
+    <t>Biopterin metabolism</t>
+  </si>
+  <si>
+    <t>E912,E1455,E1459,E1735</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E1239,E2525</t>
+  </si>
+  <si>
+    <t>C00021,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>E26,E2796,E2525</t>
+  </si>
+  <si>
+    <t>,C00021,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$S-Adenosyl-L-homocysteine$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>E315,E2525</t>
+  </si>
+  <si>
+    <t>D4&amp;E4-neuroprostanes formation</t>
+  </si>
+  <si>
+    <t>E2895,E1408</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Selenoamino acid metabolism</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
+  </si>
+  <si>
+    <t>E2796,E2525</t>
+  </si>
+  <si>
+    <t>C00021,C00020/C00362</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin H (biotin) metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
+  </si>
+  <si>
+    <t>Drug metabolism - other enzymes</t>
+  </si>
+  <si>
+    <t>E1536</t>
+  </si>
+  <si>
+    <t>Drug metabolism - cytochrome P450</t>
+  </si>
+  <si>
+    <t>E521,E2919,E2568,E2336,E178,E1274,E940</t>
+  </si>
+  <si>
+    <t>,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$</t>
+  </si>
+  <si>
+    <t>Vitamin B6 (pyridoxine) metabolism</t>
+  </si>
+  <si>
+    <t>E383,E384</t>
+  </si>
+  <si>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>E1895</t>
+  </si>
+  <si>
+    <t>CE2202/C17335</t>
+  </si>
+  <si>
+    <t>23S,25,26-trihydroxyvitamin D3/</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>E3034</t>
+  </si>
+  <si>
+    <t>Lipoate metabolism</t>
+  </si>
+  <si>
+    <t>E2411</t>
+  </si>
+  <si>
+    <t>Urea cycle/amino group metabolism</t>
+  </si>
+  <si>
+    <t>E26,E2796,E412,E1529,E175,E1535,E413</t>
+  </si>
+  <si>
+    <t>,C00021,,,,,</t>
+  </si>
+  <si>
+    <t>$S-Adenosyl-L-homocysteine$$$$$</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+  </si>
+  <si>
+    <t>Alanine and Aspartate Metabolism</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E2442,E740</t>
+  </si>
+  <si>
+    <t>,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480</t>
+  </si>
+  <si>
+    <t>$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/</t>
+  </si>
+  <si>
+    <t>Tryptophan metabolism</t>
+  </si>
+  <si>
+    <t>E666,E877,E889,E760,E890,E2103,E2796,E1186,E126,E632,E1187,E737,E2747,E846,E1735,E2525,E651,E705,E2750,E767</t>
+  </si>
+  <si>
+    <t>,,,,,,C00021,,,,,,,,,C00020/C00362,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$S-Adenosyl-L-homocysteine$$$$$$$$$AMP/dGMP$$$$</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>Limonene and pinene degradation</t>
+  </si>
+  <si>
+    <t>E265</t>
+  </si>
+  <si>
+    <t>Arginine and Proline Metabolism</t>
+  </si>
+  <si>
+    <t>E26</t>
+  </si>
+  <si>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E2263,E2796,E2141,E2269,E3018,E1954,E422</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
+  </si>
+  <si>
+    <t>Aminosugars metabolism</t>
+  </si>
+  <si>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E3065,E2525,E256</t>
+  </si>
+  <si>
+    <t>,C00020/C00362,C00219</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP$arachidonic acid</t>
+  </si>
+  <si>
+    <t>Purine metabolism</t>
+  </si>
+  <si>
+    <t>E1671,E2525,E1677</t>
   </si>
   <si>
     <t>,C00020/C00362,</t>
   </si>
   <si>
     <t>$AMP/dGMP$</t>
-  </si>
-  <si>
-    <t>Lipoate metabolism</t>
-  </si>
-  <si>
-    <t>E2411,E2412</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E1403,E347</t>
-  </si>
-  <si>
-    <t>C06486/C00386,C00135</t>
-  </si>
-  <si>
-    <t>(6R)-6-(L-erythro-1,2-Dihydroxypropyl)-5,6,7,8-tetrahydro-4a-/Carnosine; Nalpha-(beta-alanyl)-L-histidine$L-Histidine</t>
-  </si>
-  <si>
-    <t>Valine, leucine and isoleucine degradation</t>
-  </si>
-  <si>
-    <t>E2525</t>
-  </si>
-  <si>
-    <t>C00020/C00362</t>
-  </si>
-  <si>
-    <t>AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Mono-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>E1074</t>
-  </si>
-  <si>
-    <t>Phytanic acid peroxisomal oxidation</t>
-  </si>
-  <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E740,E2558,E2970</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00055,</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$CMP$</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E1900,E1301,E1286,E2899,E1666,E256,E1899,E2525,E2295</t>
-  </si>
-  <si>
-    <t>,,,,,C00219,,C00020/C00362,</t>
-  </si>
-  <si>
-    <t>$$$$$arachidonic acid$$AMP/dGMP$</t>
-  </si>
-  <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E830,E2796,E227,E2525</t>
-  </si>
-  <si>
-    <t>,C00021,,C00020/C00362</t>
-  </si>
-  <si>
-    <t>$S-Adenosyl-L-homocysteine$$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>E445,E2558,E2525,E1039</t>
-  </si>
-  <si>
-    <t>,C00055,C00020/C00362,</t>
-  </si>
-  <si>
-    <t>$CMP$AMP/dGMP$</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E1353,E1475,E2525,E1074</t>
-  </si>
-  <si>
-    <t>,,C00020/C00362,</t>
-  </si>
-  <si>
-    <t>$$AMP/dGMP$</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E1129,E3004,E3062,E2859,E1128,E3153</t>
-  </si>
-  <si>
-    <t>,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - lactoseries</t>
-  </si>
-  <si>
-    <t>Blood Group Biosynthesis</t>
-  </si>
-  <si>
-    <t>Caffeine metabolism</t>
-  </si>
-  <si>
-    <t>E740</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - neolactoseries</t>
-  </si>
-  <si>
-    <t>Starch and Sucrose Metabolism</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>E740,E2525</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,C00020/C00362</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Hexose phosphorylation</t>
-  </si>
-  <si>
-    <t>E740,E785,E830,E784</t>
-  </si>
-  <si>
-    <t>C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480,,,</t>
-  </si>
-  <si>
-    <t>D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/$$$</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E92,E2525,E256,E2513,E2295</t>
-  </si>
-  <si>
-    <t>C06426/C06427,C00020/C00362,C00219,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,</t>
-  </si>
-  <si>
-    <t>(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP$arachidonic acid$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$</t>
-  </si>
-  <si>
-    <t>Biopterin metabolism</t>
-  </si>
-  <si>
-    <t>E912,E1455,E1459,E1735</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>E2796,E1239,E2525</t>
-  </si>
-  <si>
-    <t>C00021,,C00020/C00362</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E26,E2796,E2525</t>
-  </si>
-  <si>
-    <t>,C00021,C00020/C00362</t>
-  </si>
-  <si>
-    <t>$S-Adenosyl-L-homocysteine$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>E315,E2525</t>
-  </si>
-  <si>
-    <t>D4&amp;E4-neuroprostanes formation</t>
-  </si>
-  <si>
-    <t>E2895,E1408</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Selenoamino acid metabolism</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
-  </si>
-  <si>
-    <t>E2796,E2525</t>
-  </si>
-  <si>
-    <t>C00021,C00020/C00362</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Tryptophan metabolism</t>
-  </si>
-  <si>
-    <t>E666,E877,E889,E760,E890,E2103,E2796,E700,E610,E1186,E126,E632,E693,E737,E2747,E846,E1735,E2525,E651,E705,E2750,E767,E706</t>
-  </si>
-  <si>
-    <t>,,,,,,C00021,,,,,,,,,,,C00020/C00362,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$S-Adenosyl-L-homocysteine$$$$$$$$$$$AMP/dGMP$$$$$</t>
-  </si>
-  <si>
-    <t>Urea cycle/amino group metabolism</t>
-  </si>
-  <si>
-    <t>E26,E2796,E412,E1529,E175,E1535,E145,E413</t>
-  </si>
-  <si>
-    <t>,C00021,,,,,,</t>
-  </si>
-  <si>
-    <t>$S-Adenosyl-L-homocysteine$$$$$$</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
-  </si>
-  <si>
-    <t>Drug metabolism - other enzymes</t>
-  </si>
-  <si>
-    <t>E1536</t>
-  </si>
-  <si>
-    <t>Drug metabolism - cytochrome P450</t>
-  </si>
-  <si>
-    <t>E521,E2919,E2568,E2336,E178,E1274,E940</t>
-  </si>
-  <si>
-    <t>,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (pyridoxine) metabolism</t>
-  </si>
-  <si>
-    <t>E383,E384</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>E1895</t>
-  </si>
-  <si>
-    <t>CE2202/C17335</t>
-  </si>
-  <si>
-    <t>23S,25,26-trihydroxyvitamin D3/</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>E3034</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
-  </si>
-  <si>
-    <t>Alanine and Aspartate Metabolism</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E2442,E740</t>
-  </si>
-  <si>
-    <t>,C00031/C00221/C02336/C00267/C00962/C00795/C00137/C00984/C00159/C13747/C07480</t>
-  </si>
-  <si>
-    <t>$D-Glucose/beta-D-Glucose/beta-D-Fructose; beta-Fruit sugar; beta-D-arabino-Hexulose; beta-Levulose; Fructose/alpha-D-Glucose/beta-D-Galactose/D-Tagatose; lyxo-Hexulose/myo-Inositol/alpha-D-Galactose/D-Mannose/1,7-Dimethylxanthine; Paraxanthine/</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>Limonene and pinene degradation</t>
-  </si>
-  <si>
-    <t>E265</t>
-  </si>
-  <si>
-    <t>Arginine and Proline Metabolism</t>
-  </si>
-  <si>
-    <t>E26</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>Aminosugars metabolism</t>
-  </si>
-  <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2263,E2796,E2141,E2269,E3018,E1954,E422</t>
-  </si>
-  <si>
-    <t>,C00021,,,,,</t>
-  </si>
-  <si>
-    <t>$S-Adenosyl-L-homocysteine$$$$$</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E3065,E2525,E256</t>
-  </si>
-  <si>
-    <t>,C00020/C00362,C00219</t>
-  </si>
-  <si>
-    <t>$AMP/dGMP$arachidonic acid</t>
-  </si>
-  <si>
-    <t>Purine metabolism</t>
-  </si>
-  <si>
-    <t>E1671,E2525,E1677</t>
   </si>
   <si>
     <t>Hyaluronan Metabolism</t>
@@ -1213,7 +1213,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.01100821834927144</v>
+        <v>0.01057125090334616</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1236,7 +1236,7 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <v>0.01408379691097629</v>
+        <v>0.01317624913866994</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1259,7 +1259,7 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>0.01742827851632746</v>
+        <v>0.01658795650493269</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1282,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>0.01768037511974588</v>
+        <v>0.01710895615199744</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1305,7 +1305,7 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>0.02327691971563503</v>
+        <v>0.02147863061125023</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1328,7 +1328,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>0.031310398144569</v>
+        <v>0.0305877212147695</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1351,7 +1351,7 @@
         <v>6</v>
       </c>
       <c r="D8">
-        <v>0.031310398144569</v>
+        <v>0.0305877212147695</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1374,7 +1374,7 @@
         <v>37</v>
       </c>
       <c r="D9">
-        <v>0.03267171980302852</v>
+        <v>0.03082301137796004</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1397,7 +1397,7 @@
         <v>3</v>
       </c>
       <c r="D10">
-        <v>0.03268852624325642</v>
+        <v>0.0324028167593822</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
@@ -1414,13 +1414,13 @@
         <v>43</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>0.04115897211811567</v>
+        <v>0.03756239390934606</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1437,13 +1437,13 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D12">
-        <v>0.04759583872539958</v>
+        <v>0.04008335994353036</v>
       </c>
       <c r="E12" t="s">
         <v>48</v>
@@ -1460,13 +1460,13 @@
         <v>51</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D13">
-        <v>0.05371338296835347</v>
+        <v>0.04110855279743197</v>
       </c>
       <c r="E13" t="s">
         <v>52</v>
@@ -1483,13 +1483,13 @@
         <v>55</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>0.0625871834086822</v>
+        <v>0.04732693568175324</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1506,13 +1506,13 @@
         <v>59</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>0.07001562998941194</v>
+        <v>0.05188148098351288</v>
       </c>
       <c r="E15" t="s">
         <v>60</v>
@@ -1529,13 +1529,13 @@
         <v>63</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>0.07001562998941194</v>
+        <v>0.06078889430429741</v>
       </c>
       <c r="E16" t="s">
         <v>64</v>
@@ -1558,21 +1558,21 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>0.07001562998941194</v>
+        <v>0.06897363069528244</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1581,39 +1581,39 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>0.07001562998941194</v>
+        <v>0.06897363069528244</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0.06897363069528244</v>
+      </c>
+      <c r="E19" t="s">
         <v>72</v>
       </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-      <c r="C19">
-        <v>8</v>
-      </c>
-      <c r="D19">
-        <v>0.07181391909379674</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>73</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>74</v>
-      </c>
-      <c r="G19" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1621,13 +1621,13 @@
         <v>76</v>
       </c>
       <c r="B20">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0.09053629350767214</v>
+        <v>0.06897363069528244</v>
       </c>
       <c r="E20" t="s">
         <v>77</v>
@@ -1644,13 +1644,13 @@
         <v>80</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>0.0946370649232786</v>
+        <v>0.06937698526075192</v>
       </c>
       <c r="E21" t="s">
         <v>81</v>
@@ -1667,13 +1667,13 @@
         <v>84</v>
       </c>
       <c r="B22">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="D22">
-        <v>0.09835128821364347</v>
+        <v>0.08201542831212921</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
@@ -1690,13 +1690,13 @@
         <v>88</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D23">
-        <v>0.1007882220466883</v>
+        <v>0.08846910135964102</v>
       </c>
       <c r="E23" t="s">
         <v>89</v>
@@ -1719,7 +1719,7 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>0.1007882220466883</v>
+        <v>0.09527570965193863</v>
       </c>
       <c r="E24" t="s">
         <v>93</v>
@@ -1736,13 +1736,13 @@
         <v>96</v>
       </c>
       <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
         <v>5</v>
       </c>
-      <c r="C25">
-        <v>18</v>
-      </c>
       <c r="D25">
-        <v>0.1137123745819398</v>
+        <v>0.09527570965193863</v>
       </c>
       <c r="E25" t="s">
         <v>97</v>
@@ -1759,13 +1759,13 @@
         <v>100</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D26">
-        <v>0.1277121392917766</v>
+        <v>0.110788053982286</v>
       </c>
       <c r="E26" t="s">
         <v>101</v>
@@ -1788,7 +1788,7 @@
         <v>6</v>
       </c>
       <c r="D27">
-        <v>0.1352918438345574</v>
+        <v>0.1290398480697803</v>
       </c>
       <c r="E27" t="s">
         <v>105</v>
@@ -1805,13 +1805,13 @@
         <v>108</v>
       </c>
       <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
         <v>2</v>
       </c>
-      <c r="C28">
-        <v>6</v>
-      </c>
       <c r="D28">
-        <v>0.1352918438345574</v>
+        <v>0.1352246180736458</v>
       </c>
       <c r="E28" t="s">
         <v>109</v>
@@ -1834,21 +1834,21 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <v>0.1403673887833818</v>
+        <v>0.1352246180736458</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G29" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -1857,21 +1857,15 @@
         <v>2</v>
       </c>
       <c r="D30">
-        <v>0.1403673887833818</v>
+        <v>0.1352246180736458</v>
       </c>
       <c r="E30" t="s">
-        <v>113</v>
-      </c>
-      <c r="F30" t="s">
         <v>114</v>
-      </c>
-      <c r="G30" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1880,56 +1874,62 @@
         <v>2</v>
       </c>
       <c r="D31">
-        <v>0.1403673887833818</v>
+        <v>0.1352246180736458</v>
       </c>
       <c r="E31" t="s">
-        <v>118</v>
+        <v>109</v>
+      </c>
+      <c r="F31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D32">
-        <v>0.1403673887833818</v>
+        <v>0.1432749029428077</v>
       </c>
       <c r="E32" t="s">
-        <v>113</v>
+        <v>56</v>
       </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="G32" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>152</v>
+      </c>
+      <c r="D33">
+        <v>0.147560545200921</v>
+      </c>
+      <c r="E33" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" t="s">
         <v>120</v>
-      </c>
-      <c r="B33">
-        <v>3</v>
-      </c>
-      <c r="C33">
-        <v>11</v>
-      </c>
-      <c r="D33">
-        <v>0.1499974790339658</v>
-      </c>
-      <c r="E33" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" t="s">
-        <v>49</v>
-      </c>
-      <c r="G33" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1943,7 +1943,7 @@
         <v>12</v>
       </c>
       <c r="D34">
-        <v>0.1814927480210416</v>
+        <v>0.1730223021461824</v>
       </c>
       <c r="E34" t="s">
         <v>122</v>
@@ -1960,13 +1960,13 @@
         <v>125</v>
       </c>
       <c r="B35">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D35">
-        <v>0.1826691988369943</v>
+        <v>0.1783331372581974</v>
       </c>
       <c r="E35" t="s">
         <v>126</v>
@@ -1989,7 +1989,7 @@
         <v>17</v>
       </c>
       <c r="D36">
-        <v>0.1890724525638225</v>
+        <v>0.1783331372581974</v>
       </c>
       <c r="E36" t="s">
         <v>130</v>
@@ -2012,7 +2012,7 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0.1890724525638225</v>
+        <v>0.1783331372581974</v>
       </c>
       <c r="E37" t="s">
         <v>134</v>
@@ -2029,13 +2029,13 @@
         <v>137</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D38">
-        <v>0.1890724525638225</v>
+        <v>0.1856271323171039</v>
       </c>
       <c r="E38" t="s">
         <v>138</v>
@@ -2052,27 +2052,27 @@
         <v>141</v>
       </c>
       <c r="B39">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>0.1981983496075696</v>
+        <v>0.2051394094216904</v>
       </c>
       <c r="E39" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="F39" t="s">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="G39" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -2081,21 +2081,21 @@
         <v>3</v>
       </c>
       <c r="D40">
-        <v>0.2108704055394027</v>
+        <v>0.2051394094216904</v>
       </c>
       <c r="E40" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F40" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -2104,16 +2104,16 @@
         <v>3</v>
       </c>
       <c r="D41">
-        <v>0.2108704055394027</v>
+        <v>0.2051394094216904</v>
       </c>
       <c r="E41" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="G41" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2127,21 +2127,21 @@
         <v>3</v>
       </c>
       <c r="D42">
-        <v>0.2108704055394027</v>
+        <v>0.2051394094216904</v>
       </c>
       <c r="E42" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
       <c r="F42" t="s">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="G42" t="s">
-        <v>150</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -2150,39 +2150,39 @@
         <v>3</v>
       </c>
       <c r="D43">
-        <v>0.2108704055394027</v>
+        <v>0.2051394094216904</v>
       </c>
       <c r="E43" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="F43" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="G43" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44">
+        <v>8</v>
+      </c>
+      <c r="D44">
+        <v>0.2098956320061848</v>
+      </c>
+      <c r="E44" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" t="s">
+        <v>151</v>
+      </c>
+      <c r="G44" t="s">
         <v>152</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44">
-        <v>3</v>
-      </c>
-      <c r="D44">
-        <v>0.2108704055394027</v>
-      </c>
-      <c r="E44" t="s">
-        <v>148</v>
-      </c>
-      <c r="F44" t="s">
-        <v>149</v>
-      </c>
-      <c r="G44" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2190,13 +2190,13 @@
         <v>153</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D45">
-        <v>0.2180971748373977</v>
+        <v>0.2115426631485185</v>
       </c>
       <c r="E45" t="s">
         <v>154</v>
@@ -2213,13 +2213,13 @@
         <v>157</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C46">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D46">
-        <v>0.2208198181543167</v>
+        <v>0.2356935177560041</v>
       </c>
       <c r="E46" t="s">
         <v>158</v>
@@ -2236,45 +2236,45 @@
         <v>161</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D47">
-        <v>0.2459286398547924</v>
+        <v>0.2389371607199879</v>
       </c>
       <c r="E47" t="s">
         <v>162</v>
       </c>
       <c r="F47" t="s">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s">
-        <v>164</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
+        <v>163</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48">
+        <v>14</v>
+      </c>
+      <c r="D48">
+        <v>0.2435925446631149</v>
+      </c>
+      <c r="E48" t="s">
+        <v>164</v>
+      </c>
+      <c r="F48" t="s">
         <v>165</v>
       </c>
-      <c r="B48">
-        <v>4</v>
-      </c>
-      <c r="C48">
-        <v>19</v>
-      </c>
-      <c r="D48">
-        <v>0.2483151543671535</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="G48" t="s">
         <v>166</v>
-      </c>
-      <c r="F48" t="s">
-        <v>82</v>
-      </c>
-      <c r="G48" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2288,7 +2288,7 @@
         <v>14</v>
       </c>
       <c r="D49">
-        <v>0.2529537318700526</v>
+        <v>0.2435925446631149</v>
       </c>
       <c r="E49" t="s">
         <v>168</v>
@@ -2305,27 +2305,27 @@
         <v>171</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D50">
-        <v>0.2529537318700526</v>
+        <v>0.2520125712172905</v>
       </c>
       <c r="E50" t="s">
         <v>172</v>
       </c>
       <c r="F50" t="s">
-        <v>173</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -2334,16 +2334,16 @@
         <v>9</v>
       </c>
       <c r="D51">
-        <v>0.2611048553805818</v>
+        <v>0.2520125712172905</v>
       </c>
       <c r="E51" t="s">
+        <v>174</v>
+      </c>
+      <c r="F51" t="s">
+        <v>175</v>
+      </c>
+      <c r="G51" t="s">
         <v>176</v>
-      </c>
-      <c r="F51" t="s">
-        <v>90</v>
-      </c>
-      <c r="G51" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2357,44 +2357,44 @@
         <v>9</v>
       </c>
       <c r="D52">
-        <v>0.2611048553805818</v>
+        <v>0.2520125712172905</v>
       </c>
       <c r="E52" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="F52" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="G52" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D53">
-        <v>0.2611048553805818</v>
+        <v>0.2740626207962891</v>
       </c>
       <c r="E53" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="F53" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="G53" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -2403,44 +2403,44 @@
         <v>4</v>
       </c>
       <c r="D54">
-        <v>0.2835750659652779</v>
+        <v>0.2740626207962891</v>
       </c>
       <c r="E54" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F54" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G54" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D55">
-        <v>0.2835750659652779</v>
+        <v>0.3040453101628544</v>
       </c>
       <c r="E55" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="F55" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="G55" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -2449,90 +2449,90 @@
         <v>10</v>
       </c>
       <c r="D56">
-        <v>0.3126670139997647</v>
+        <v>0.3040453101628544</v>
       </c>
       <c r="E56" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="F56" t="s">
-        <v>94</v>
+        <v>183</v>
       </c>
       <c r="G56" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D57">
-        <v>0.3126670139997647</v>
+        <v>0.3269356817532478</v>
       </c>
       <c r="E57" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="F57" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B58">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>120</v>
+        <v>5</v>
       </c>
       <c r="D58">
-        <v>0.326112166182081</v>
+        <v>0.3269356817532478</v>
       </c>
       <c r="E58" t="s">
-        <v>188</v>
+        <v>109</v>
       </c>
       <c r="F58" t="s">
-        <v>189</v>
+        <v>110</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B59">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="D59">
-        <v>0.3300280667551806</v>
+        <v>0.3269356817532478</v>
       </c>
       <c r="E59" t="s">
-        <v>192</v>
+        <v>109</v>
       </c>
       <c r="F59" t="s">
-        <v>193</v>
+        <v>110</v>
       </c>
       <c r="G59" t="s">
-        <v>194</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -2541,78 +2541,78 @@
         <v>5</v>
       </c>
       <c r="D60">
-        <v>0.3354901598292466</v>
+        <v>0.3269356817532478</v>
       </c>
       <c r="E60" t="s">
-        <v>113</v>
-      </c>
-      <c r="F60" t="s">
-        <v>114</v>
-      </c>
-      <c r="G60" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D61">
-        <v>0.3354901598292466</v>
+        <v>0.3525486966605603</v>
       </c>
       <c r="E61" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="F61" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="G61" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D62">
-        <v>0.3354901598292466</v>
+        <v>0.3581788541369053</v>
       </c>
       <c r="E62" t="s">
-        <v>113</v>
+        <v>195</v>
       </c>
       <c r="F62" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="G62" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
+        <v>196</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>6</v>
+      </c>
+      <c r="D63">
+        <v>0.3658425908808255</v>
+      </c>
+      <c r="E63" t="s">
+        <v>197</v>
+      </c>
+      <c r="F63" t="s">
         <v>198</v>
       </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63">
-        <v>5</v>
-      </c>
-      <c r="D63">
-        <v>0.3354901598292466</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>199</v>
       </c>
     </row>
@@ -2621,90 +2621,84 @@
         <v>200</v>
       </c>
       <c r="B64">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="D64">
-        <v>0.3680610409909077</v>
+        <v>0.3658425908808255</v>
       </c>
       <c r="E64" t="s">
         <v>201</v>
       </c>
-      <c r="F64" t="s">
-        <v>202</v>
-      </c>
-      <c r="G64" t="s">
-        <v>203</v>
-      </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D65">
-        <v>0.3697921043343809</v>
+        <v>0.3658425908808255</v>
       </c>
       <c r="E65" t="s">
-        <v>205</v>
-      </c>
-      <c r="F65" t="s">
-        <v>106</v>
-      </c>
-      <c r="G65" t="s">
-        <v>107</v>
+        <v>203</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
+        <v>204</v>
+      </c>
+      <c r="B66">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>43</v>
+      </c>
+      <c r="D66">
+        <v>0.4082620460160333</v>
+      </c>
+      <c r="E66" t="s">
+        <v>205</v>
+      </c>
+      <c r="F66" t="s">
         <v>206</v>
       </c>
-      <c r="B66">
-        <v>1</v>
-      </c>
-      <c r="C66">
-        <v>6</v>
-      </c>
-      <c r="D66">
-        <v>0.3770188736323759</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>207</v>
-      </c>
-      <c r="F66" t="s">
-        <v>208</v>
-      </c>
-      <c r="G66" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67">
-        <v>0.3770188736323759</v>
+        <v>0.4104132703652039</v>
       </c>
       <c r="E67" t="s">
-        <v>211</v>
+        <v>72</v>
+      </c>
+      <c r="F67" t="s">
+        <v>73</v>
+      </c>
+      <c r="G67" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -2713,39 +2707,39 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>0.4213878758340196</v>
+        <v>0.4104132703652039</v>
       </c>
       <c r="E68" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="F68" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="G68" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
+        <v>210</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69">
+        <v>14</v>
+      </c>
+      <c r="D69">
+        <v>0.4228332296936186</v>
+      </c>
+      <c r="E69" t="s">
+        <v>211</v>
+      </c>
+      <c r="F69" t="s">
+        <v>212</v>
+      </c>
+      <c r="G69" t="s">
         <v>213</v>
-      </c>
-      <c r="B69">
-        <v>1</v>
-      </c>
-      <c r="C69">
-        <v>7</v>
-      </c>
-      <c r="D69">
-        <v>0.4213878758340196</v>
-      </c>
-      <c r="E69" t="s">
-        <v>113</v>
-      </c>
-      <c r="F69" t="s">
-        <v>114</v>
-      </c>
-      <c r="G69" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2753,13 +2747,13 @@
         <v>214</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C70">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="D70">
-        <v>0.4338750609233458</v>
+        <v>0.4772860960319995</v>
       </c>
       <c r="E70" t="s">
         <v>215</v>
@@ -2782,16 +2776,16 @@
         <v>9</v>
       </c>
       <c r="D71">
-        <v>0.4916051831061663</v>
+        <v>0.4800255457891464</v>
       </c>
       <c r="E71" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F71" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G71" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2805,7 +2799,7 @@
         <v>10</v>
       </c>
       <c r="D72">
-        <v>0.5166299726055025</v>
+        <v>0.5058570444194215</v>
       </c>
       <c r="E72" t="s">
         <v>220</v>
@@ -2822,7 +2816,7 @@
         <v>10</v>
       </c>
       <c r="D73">
-        <v>0.5166299726055025</v>
+        <v>0.5058570444194215</v>
       </c>
       <c r="E73" t="s">
         <v>222</v>
@@ -2833,27 +2827,27 @@
         <v>223</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C74">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="D74">
-        <v>0.5340918640022857</v>
+        <v>0.523285322935749</v>
       </c>
       <c r="E74" t="s">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="F74" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="G74" t="s">
-        <v>62</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -2862,44 +2856,44 @@
         <v>11</v>
       </c>
       <c r="D75">
-        <v>0.5340918640022857</v>
+        <v>0.5248483218769432</v>
       </c>
       <c r="E75" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F75" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G75" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B76">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D76">
-        <v>0.535638056503252</v>
+        <v>0.5248483218769432</v>
       </c>
       <c r="E76" t="s">
-        <v>226</v>
+        <v>72</v>
       </c>
       <c r="F76" t="s">
-        <v>227</v>
+        <v>73</v>
       </c>
       <c r="G76" t="s">
-        <v>228</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -2908,21 +2902,21 @@
         <v>13</v>
       </c>
       <c r="D77">
-        <v>0.5616376195358062</v>
+        <v>0.5536209475471</v>
       </c>
       <c r="E77" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F77" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G77" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B78">
         <v>3</v>
@@ -2931,21 +2925,21 @@
         <v>29</v>
       </c>
       <c r="D78">
-        <v>0.5678223895396716</v>
+        <v>0.5576544932017949</v>
       </c>
       <c r="E78" t="s">
+        <v>229</v>
+      </c>
+      <c r="F78" t="s">
+        <v>230</v>
+      </c>
+      <c r="G78" t="s">
         <v>231</v>
-      </c>
-      <c r="F78" t="s">
-        <v>232</v>
-      </c>
-      <c r="G78" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -2954,16 +2948,16 @@
         <v>35</v>
       </c>
       <c r="D79">
-        <v>0.5968807246937027</v>
+        <v>0.591368212298953</v>
       </c>
       <c r="E79" t="s">
+        <v>233</v>
+      </c>
+      <c r="F79" t="s">
+        <v>234</v>
+      </c>
+      <c r="G79" t="s">
         <v>235</v>
-      </c>
-      <c r="F79" t="s">
-        <v>102</v>
-      </c>
-      <c r="G79" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2977,7 +2971,7 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2991,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3005,7 +2999,7 @@
         <v>2</v>
       </c>
       <c r="D82">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3019,7 +3013,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3033,7 +3027,7 @@
         <v>2</v>
       </c>
       <c r="D84">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3047,7 +3041,7 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3061,7 +3055,7 @@
         <v>6</v>
       </c>
       <c r="D86">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3075,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3089,7 +3083,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3103,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3117,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3131,7 +3125,7 @@
         <v>3</v>
       </c>
       <c r="D91">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3145,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3159,7 +3153,7 @@
         <v>11</v>
       </c>
       <c r="D93">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3173,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="D94">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3187,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3201,7 +3195,7 @@
         <v>3</v>
       </c>
       <c r="D96">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3215,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3229,7 +3223,7 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3243,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3257,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3271,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3285,7 +3279,7 @@
         <v>7</v>
       </c>
       <c r="D102">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3299,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3313,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3327,7 +3321,7 @@
         <v>10</v>
       </c>
       <c r="D105">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3341,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3355,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3369,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3383,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="D109">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3397,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="D110">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3411,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3425,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3439,7 +3433,7 @@
         <v>3</v>
       </c>
       <c r="D113">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3453,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3467,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3481,7 +3475,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3495,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3509,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3523,7 +3517,7 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3537,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0.6138888422043327</v>
+        <v>0.6110989731265021</v>
       </c>
     </row>
   </sheetData>
